--- a/repair/back/doc/estimate/repair1.xlsx
+++ b/repair/back/doc/estimate/repair1.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seongjaehyeon/anb_origin2/repair/back/doc/estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02AD23-BF12-FC45-BA7D-75766744C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55BDFCD-D6E4-7345-AB56-57F1DE6DBCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="18300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="1" r:id="rId1"/>
     <sheet name="대가산출" sheetId="3" r:id="rId2"/>
     <sheet name="계약서1" sheetId="4" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_1.전기공사" localSheetId="2">#REF!</definedName>
     <definedName name="_1.전기공사">#REF!</definedName>
@@ -260,7 +257,7 @@
     <definedName name="표지3">#REF!</definedName>
     <definedName name="품명" localSheetId="2">#REF!</definedName>
     <definedName name="품명">#REF!</definedName>
-    <definedName name="한자">[1]숫자읽기!$U$3:$V$12</definedName>
+    <definedName name="한자">#REF!</definedName>
     <definedName name="합계금액" localSheetId="2">#REF!</definedName>
     <definedName name="합계금액">#REF!</definedName>
     <definedName name="형식" localSheetId="2">#REF!</definedName>
@@ -327,7 +324,7 @@
     <definedName name="phc" localSheetId="2">#REF!</definedName>
     <definedName name="phc">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">갑지!$G$1:$AH$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">계약서1!$B$1:$U$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">계약서1!$B$1:$U$111</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">대가산출!$G$1:$N$31</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI" localSheetId="2">#REF!</definedName>
@@ -379,7 +376,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="177">
   <si>
     <t xml:space="preserve">㈜ 에 이 앤 비 </t>
   </si>
@@ -514,9 +511,6 @@
     <t>절 삭 금 액</t>
   </si>
   <si>
-    <t>구조형식,용도,경과년수</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -635,9 +629,6 @@
   </si>
   <si>
     <t>부가 가치세</t>
-  </si>
-  <si>
-    <t>10% 별도</t>
   </si>
   <si>
     <t xml:space="preserve">2026   .     .     .   ~   2026 .     .     . </t>
@@ -799,9 +790,6 @@
     <t>※ 첨    부 :  1. 장기수선계획서 조정 견적서 1부 끝.</t>
   </si>
   <si>
-    <t xml:space="preserve">장기수선계획 조정 </t>
-  </si>
-  <si>
     <t>계약  기간</t>
   </si>
   <si>
@@ -842,9 +830,6 @@
   </si>
   <si>
     <t>③ 장기수선계획서 완성본은 3회(검수, 수정, 회수)까지만 수정한 후 완료하는 것으로 한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         (장기수선계획의 수립), 시행규칙 제7조(장기수선계획의 수립기준 등)의 규정에 따라</t>
   </si>
   <si>
     <t>3. 조정시에는 도면에 의한 물량산출은 하지 않는다(기존 장기수선계획서로 작성)</t>
@@ -942,12 +927,6 @@
     <t>전화 :</t>
   </si>
   <si>
-    <t xml:space="preserve"> (이하 "발주자"라 한다)와 장기수선계획 조정 대행자인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ㈜ 에이앤비 (이하 "수주자"라 한다)는 다음과같이 계약을 체결한다.</t>
-  </si>
-  <si>
     <t>무로 하는 ㈜에이앤비입니다.</t>
   </si>
   <si>
@@ -965,9 +944,6 @@
     <t>●   사업자등록번호 : 863-87-00907</t>
   </si>
   <si>
-    <t>●    주 소 : 경기도 용인시 기흥구 마북로 159 한성프라자 207호</t>
-  </si>
-  <si>
     <t>●   전화번호 : 031-283-3328     팩스번호 : 031-284-3328</t>
   </si>
   <si>
@@ -975,10 +951,6 @@
   </si>
   <si>
     <t>제1조(목적)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        「공동주택관리법」(이하 “공주법”이라 한다) 제29조(장기수선계획), 시행령 제30조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1007,34 +979,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">      </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="바탕체"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="바탕체"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>6. 용    역    비  :</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5. 아파트에서 결정해야 할 사항 (1~4번 모두 작성)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1052,30 +996,6 @@
   </si>
   <si>
     <t>나. 이 견적서의 유효기간은 30일 입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">          1. 귀 사의 무궁한 발전을 기원합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">          3. 그 동안 귀사에서 물심양면으로 도와주신 부분에 대하여 무궁한 감사 드리며, </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">          4. 시설물 개요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">          5. 용  역   범  위 : </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">          7. 참 고 사 항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">          2. 당 사는 경기도 용인시 기흥구 마북로 159, 한성프라자 207호에 위치한 업체로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1116,6 +1036,210 @@
   </si>
   <si>
     <t>나. 내업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>●   주 소 : 경기도 용인시 기흥구 마북로 159 한성프라자 207호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10% 별도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>1. 귀 사의 무궁한 발전을 기원합니다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2. 당 사는 경기도 용인시 기흥구 마북로 159, 한성프라자 207호에 위치한 업체로</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">3. 그 동안 귀사에서 물심양면으로 도와주신 부분에 대하여 무궁한 감사 드리며, </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>4. 시설물 개요</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">5. 용  역   범  위 : </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>7. 참 고 사 항</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>6. 용    역    비  :</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「공동주택관리법」(이하 “공주법”이라 한다) 제29조(장기수선계획), 시행령 제30조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(장기수선계획의 수립), 시행규칙 제7조(장기수선계획의 수립기준 등)의 규정에 따라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜ 에이앤비 (이하 "수주자"라 한다)는 다음과같이 계약을 체결한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12894,6 +13018,243 @@
     <xf numFmtId="0" fontId="112" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="101" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="21" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="44" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="28" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="27" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="27" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="27" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="26" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -12957,15 +13318,6 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="16" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="16" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="16" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13107,269 +13459,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="16" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="11" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="101" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="16" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="16" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="73" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="73" fillId="0" borderId="11" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="21" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="44" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="28" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="27" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="112" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="112" fillId="0" borderId="11" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="27" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="27" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="26" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3121">
@@ -16995,110 +17119,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="견적서(조정D)"/>
-      <sheetName val="견적서(D)"/>
-      <sheetName val="숫자읽기"/>
-      <sheetName val="산출내역(감리)"/>
-      <sheetName val="계약서1"/>
-      <sheetName val="갑지"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="3">
-          <cell r="U3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="U4">
-            <v>1</v>
-          </cell>
-          <cell r="V4" t="str">
-            <v>壹</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="U5">
-            <v>2</v>
-          </cell>
-          <cell r="V5" t="str">
-            <v>貳</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="U6">
-            <v>3</v>
-          </cell>
-          <cell r="V6" t="str">
-            <v>參</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="U7">
-            <v>4</v>
-          </cell>
-          <cell r="V7" t="str">
-            <v>四</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="U8">
-            <v>5</v>
-          </cell>
-          <cell r="V8" t="str">
-            <v>五</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="U9">
-            <v>6</v>
-          </cell>
-          <cell r="V9" t="str">
-            <v>六</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="U10">
-            <v>7</v>
-          </cell>
-          <cell r="V10" t="str">
-            <v>七</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="U11">
-            <v>8</v>
-          </cell>
-          <cell r="V11" t="str">
-            <v>八</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="U12">
-            <v>9</v>
-          </cell>
-          <cell r="V12" t="str">
-            <v>九</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -17374,36 +17394,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="7:40" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="G1" s="154" t="s">
+      <c r="G1" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="154"/>
-      <c r="AH1" s="154"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="233"/>
+      <c r="S1" s="233"/>
+      <c r="T1" s="233"/>
+      <c r="U1" s="233"/>
+      <c r="V1" s="233"/>
+      <c r="W1" s="233"/>
+      <c r="X1" s="233"/>
+      <c r="Y1" s="233"/>
+      <c r="Z1" s="233"/>
+      <c r="AA1" s="233"/>
+      <c r="AB1" s="233"/>
+      <c r="AC1" s="233"/>
+      <c r="AD1" s="233"/>
+      <c r="AE1" s="233"/>
+      <c r="AF1" s="233"/>
+      <c r="AG1" s="233"/>
+      <c r="AH1" s="233"/>
       <c r="AI1" s="1"/>
     </row>
     <row r="2" spans="7:40" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17438,36 +17458,36 @@
       <c r="AI2" s="1"/>
     </row>
     <row r="3" spans="7:40" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="G3" s="155" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-      <c r="L3" s="155"/>
-      <c r="M3" s="155"/>
-      <c r="N3" s="155"/>
-      <c r="O3" s="155"/>
-      <c r="P3" s="155"/>
-      <c r="Q3" s="155"/>
-      <c r="R3" s="155"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="155"/>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="155"/>
-      <c r="Z3" s="155"/>
-      <c r="AA3" s="155"/>
-      <c r="AB3" s="155"/>
-      <c r="AC3" s="155"/>
-      <c r="AD3" s="155"/>
-      <c r="AE3" s="155"/>
-      <c r="AF3" s="155"/>
-      <c r="AG3" s="155"/>
-      <c r="AH3" s="155"/>
+      <c r="G3" s="234" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="234"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
+      <c r="M3" s="234"/>
+      <c r="N3" s="234"/>
+      <c r="O3" s="234"/>
+      <c r="P3" s="234"/>
+      <c r="Q3" s="234"/>
+      <c r="R3" s="234"/>
+      <c r="S3" s="234"/>
+      <c r="T3" s="234"/>
+      <c r="U3" s="234"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="234"/>
+      <c r="AA3" s="234"/>
+      <c r="AB3" s="234"/>
+      <c r="AC3" s="234"/>
+      <c r="AD3" s="234"/>
+      <c r="AE3" s="234"/>
+      <c r="AF3" s="234"/>
+      <c r="AG3" s="234"/>
+      <c r="AH3" s="234"/>
       <c r="AI3" s="1"/>
     </row>
     <row r="4" spans="7:40" s="2" customFormat="1" ht="7.5" customHeight="1">
@@ -17533,26 +17553,26 @@
       <c r="AI5" s="1"/>
     </row>
     <row r="6" spans="7:40" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="G6" s="156" t="s">
+      <c r="G6" s="235" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="157" t="s">
+      <c r="H6" s="235"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="235"/>
+      <c r="K6" s="236" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="157"/>
-      <c r="M6" s="157"/>
-      <c r="N6" s="157"/>
-      <c r="O6" s="157"/>
-      <c r="P6" s="157"/>
-      <c r="Q6" s="157"/>
-      <c r="R6" s="157"/>
-      <c r="S6" s="157"/>
-      <c r="T6" s="157"/>
-      <c r="U6" s="157"/>
-      <c r="V6" s="157"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="236"/>
+      <c r="N6" s="236"/>
+      <c r="O6" s="236"/>
+      <c r="P6" s="236"/>
+      <c r="Q6" s="236"/>
+      <c r="R6" s="236"/>
+      <c r="S6" s="236"/>
+      <c r="T6" s="236"/>
+      <c r="U6" s="236"/>
+      <c r="V6" s="236"/>
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
@@ -17568,26 +17588,26 @@
       <c r="AI6" s="1"/>
     </row>
     <row r="7" spans="7:40" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="G7" s="156" t="s">
+      <c r="G7" s="235" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="158" t="s">
+      <c r="H7" s="235"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="235"/>
+      <c r="K7" s="237" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="158"/>
-      <c r="M7" s="158"/>
-      <c r="N7" s="158"/>
-      <c r="O7" s="158"/>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="158"/>
-      <c r="R7" s="158"/>
-      <c r="S7" s="158"/>
-      <c r="T7" s="158"/>
-      <c r="U7" s="158"/>
-      <c r="V7" s="158"/>
+      <c r="L7" s="237"/>
+      <c r="M7" s="237"/>
+      <c r="N7" s="237"/>
+      <c r="O7" s="237"/>
+      <c r="P7" s="237"/>
+      <c r="Q7" s="237"/>
+      <c r="R7" s="237"/>
+      <c r="S7" s="237"/>
+      <c r="T7" s="237"/>
+      <c r="U7" s="237"/>
+      <c r="V7" s="237"/>
       <c r="W7" s="10"/>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
@@ -17603,47 +17623,47 @@
       <c r="AI7" s="1"/>
     </row>
     <row r="8" spans="7:40" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="G8" s="156" t="s">
+      <c r="G8" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="157" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="157"/>
-      <c r="M8" s="157"/>
-      <c r="N8" s="157"/>
-      <c r="O8" s="157"/>
-      <c r="P8" s="157"/>
-      <c r="Q8" s="157"/>
-      <c r="R8" s="157"/>
-      <c r="S8" s="157"/>
-      <c r="T8" s="157"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="157"/>
-      <c r="W8" s="157"/>
-      <c r="X8" s="157"/>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="157"/>
-      <c r="AA8" s="157"/>
-      <c r="AB8" s="157"/>
-      <c r="AC8" s="157"/>
-      <c r="AD8" s="157"/>
-      <c r="AE8" s="157"/>
-      <c r="AF8" s="157"/>
-      <c r="AG8" s="157"/>
-      <c r="AH8" s="157"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="236" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="236"/>
+      <c r="U8" s="236"/>
+      <c r="V8" s="236"/>
+      <c r="W8" s="236"/>
+      <c r="X8" s="236"/>
+      <c r="Y8" s="236"/>
+      <c r="Z8" s="236"/>
+      <c r="AA8" s="236"/>
+      <c r="AB8" s="236"/>
+      <c r="AC8" s="236"/>
+      <c r="AD8" s="236"/>
+      <c r="AE8" s="236"/>
+      <c r="AF8" s="236"/>
+      <c r="AG8" s="236"/>
+      <c r="AH8" s="236"/>
       <c r="AI8" s="1"/>
     </row>
     <row r="9" spans="7:40" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="G9" s="156" t="s">
+      <c r="G9" s="235" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="156"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
       <c r="K9" s="10" t="s">
         <v>5</v>
       </c>
@@ -17673,38 +17693,38 @@
       <c r="AI9" s="1"/>
     </row>
     <row r="10" spans="7:40" s="2" customFormat="1" ht="23.25" customHeight="1">
-      <c r="G10" s="156" t="s">
+      <c r="G10" s="235" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="157" t="s">
-        <v>69</v>
-      </c>
-      <c r="L10" s="157"/>
-      <c r="M10" s="157"/>
-      <c r="N10" s="157"/>
-      <c r="O10" s="157"/>
-      <c r="P10" s="157"/>
-      <c r="Q10" s="157"/>
-      <c r="R10" s="157"/>
-      <c r="S10" s="157"/>
-      <c r="T10" s="157"/>
-      <c r="U10" s="157"/>
-      <c r="V10" s="157"/>
-      <c r="W10" s="157"/>
-      <c r="X10" s="157"/>
-      <c r="Y10" s="157"/>
-      <c r="Z10" s="157"/>
-      <c r="AA10" s="157"/>
-      <c r="AB10" s="157"/>
-      <c r="AC10" s="157"/>
-      <c r="AD10" s="157"/>
-      <c r="AE10" s="157"/>
-      <c r="AF10" s="157"/>
-      <c r="AG10" s="157"/>
-      <c r="AH10" s="157"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="236" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="236"/>
+      <c r="U10" s="236"/>
+      <c r="V10" s="236"/>
+      <c r="W10" s="236"/>
+      <c r="X10" s="236"/>
+      <c r="Y10" s="236"/>
+      <c r="Z10" s="236"/>
+      <c r="AA10" s="236"/>
+      <c r="AB10" s="236"/>
+      <c r="AC10" s="236"/>
+      <c r="AD10" s="236"/>
+      <c r="AE10" s="236"/>
+      <c r="AF10" s="236"/>
+      <c r="AG10" s="236"/>
+      <c r="AH10" s="236"/>
       <c r="AI10" s="1"/>
     </row>
     <row r="11" spans="7:40" s="2" customFormat="1" ht="7.5" customHeight="1">
@@ -17770,36 +17790,36 @@
       <c r="AI12" s="1"/>
     </row>
     <row r="13" spans="7:40" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="G13" s="157" t="s">
-        <v>164</v>
-      </c>
-      <c r="H13" s="157"/>
-      <c r="I13" s="157"/>
-      <c r="J13" s="157"/>
-      <c r="K13" s="157"/>
-      <c r="L13" s="157"/>
-      <c r="M13" s="157"/>
-      <c r="N13" s="157"/>
-      <c r="O13" s="157"/>
-      <c r="P13" s="157"/>
-      <c r="Q13" s="157"/>
-      <c r="R13" s="157"/>
-      <c r="S13" s="157"/>
-      <c r="T13" s="157"/>
-      <c r="U13" s="157"/>
-      <c r="V13" s="157"/>
-      <c r="W13" s="157"/>
-      <c r="X13" s="157"/>
-      <c r="Y13" s="157"/>
-      <c r="Z13" s="157"/>
-      <c r="AA13" s="157"/>
-      <c r="AB13" s="157"/>
-      <c r="AC13" s="157"/>
-      <c r="AD13" s="157"/>
-      <c r="AE13" s="157"/>
-      <c r="AF13" s="157"/>
-      <c r="AG13" s="157"/>
-      <c r="AH13" s="157"/>
+      <c r="G13" s="236" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="236"/>
+      <c r="O13" s="236"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="236"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
+      <c r="T13" s="236"/>
+      <c r="U13" s="236"/>
+      <c r="V13" s="236"/>
+      <c r="W13" s="236"/>
+      <c r="X13" s="236"/>
+      <c r="Y13" s="236"/>
+      <c r="Z13" s="236"/>
+      <c r="AA13" s="236"/>
+      <c r="AB13" s="236"/>
+      <c r="AC13" s="236"/>
+      <c r="AD13" s="236"/>
+      <c r="AE13" s="236"/>
+      <c r="AF13" s="236"/>
+      <c r="AG13" s="236"/>
+      <c r="AH13" s="236"/>
       <c r="AI13" s="1"/>
     </row>
     <row r="14" spans="7:40" s="2" customFormat="1" ht="16" customHeight="1">
@@ -17834,36 +17854,36 @@
       <c r="AI14" s="1"/>
     </row>
     <row r="15" spans="7:40" s="45" customFormat="1" ht="16" customHeight="1">
-      <c r="G15" s="159" t="s">
-        <v>169</v>
-      </c>
-      <c r="H15" s="159"/>
-      <c r="I15" s="159"/>
-      <c r="J15" s="159"/>
-      <c r="K15" s="159"/>
-      <c r="L15" s="159"/>
-      <c r="M15" s="159"/>
-      <c r="N15" s="159"/>
-      <c r="O15" s="159"/>
-      <c r="P15" s="159"/>
-      <c r="Q15" s="159"/>
-      <c r="R15" s="159"/>
-      <c r="S15" s="159"/>
-      <c r="T15" s="159"/>
-      <c r="U15" s="159"/>
-      <c r="V15" s="159"/>
-      <c r="W15" s="159"/>
-      <c r="X15" s="159"/>
-      <c r="Y15" s="159"/>
-      <c r="Z15" s="159"/>
-      <c r="AA15" s="159"/>
-      <c r="AB15" s="159"/>
-      <c r="AC15" s="159"/>
-      <c r="AD15" s="159"/>
-      <c r="AE15" s="159"/>
-      <c r="AF15" s="159"/>
-      <c r="AG15" s="159"/>
-      <c r="AH15" s="159"/>
+      <c r="G15" s="238" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" s="238"/>
+      <c r="I15" s="238"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="238"/>
+      <c r="L15" s="238"/>
+      <c r="M15" s="238"/>
+      <c r="N15" s="238"/>
+      <c r="O15" s="238"/>
+      <c r="P15" s="238"/>
+      <c r="Q15" s="238"/>
+      <c r="R15" s="238"/>
+      <c r="S15" s="238"/>
+      <c r="T15" s="238"/>
+      <c r="U15" s="238"/>
+      <c r="V15" s="238"/>
+      <c r="W15" s="238"/>
+      <c r="X15" s="238"/>
+      <c r="Y15" s="238"/>
+      <c r="Z15" s="238"/>
+      <c r="AA15" s="238"/>
+      <c r="AB15" s="238"/>
+      <c r="AC15" s="238"/>
+      <c r="AD15" s="238"/>
+      <c r="AE15" s="238"/>
+      <c r="AF15" s="238"/>
+      <c r="AG15" s="238"/>
+      <c r="AH15" s="238"/>
       <c r="AI15" s="47"/>
       <c r="AJ15" s="47"/>
       <c r="AK15" s="47"/>
@@ -17872,36 +17892,36 @@
       <c r="AN15" s="50"/>
     </row>
     <row r="16" spans="7:40" s="46" customFormat="1" ht="16" customHeight="1">
-      <c r="G16" s="159" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="159"/>
-      <c r="I16" s="159"/>
-      <c r="J16" s="159"/>
-      <c r="K16" s="159"/>
-      <c r="L16" s="159"/>
-      <c r="M16" s="159"/>
-      <c r="N16" s="159"/>
-      <c r="O16" s="159"/>
-      <c r="P16" s="159"/>
-      <c r="Q16" s="159"/>
-      <c r="R16" s="159"/>
-      <c r="S16" s="159"/>
-      <c r="T16" s="159"/>
-      <c r="U16" s="159"/>
-      <c r="V16" s="159"/>
-      <c r="W16" s="159"/>
-      <c r="X16" s="159"/>
-      <c r="Y16" s="159"/>
-      <c r="Z16" s="159"/>
-      <c r="AA16" s="159"/>
-      <c r="AB16" s="159"/>
-      <c r="AC16" s="159"/>
-      <c r="AD16" s="159"/>
-      <c r="AE16" s="159"/>
-      <c r="AF16" s="159"/>
-      <c r="AG16" s="159"/>
-      <c r="AH16" s="159"/>
+      <c r="G16" s="238" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="238"/>
+      <c r="I16" s="238"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="238"/>
+      <c r="L16" s="238"/>
+      <c r="M16" s="238"/>
+      <c r="N16" s="238"/>
+      <c r="O16" s="238"/>
+      <c r="P16" s="238"/>
+      <c r="Q16" s="238"/>
+      <c r="R16" s="238"/>
+      <c r="S16" s="238"/>
+      <c r="T16" s="238"/>
+      <c r="U16" s="238"/>
+      <c r="V16" s="238"/>
+      <c r="W16" s="238"/>
+      <c r="X16" s="238"/>
+      <c r="Y16" s="238"/>
+      <c r="Z16" s="238"/>
+      <c r="AA16" s="238"/>
+      <c r="AB16" s="238"/>
+      <c r="AC16" s="238"/>
+      <c r="AD16" s="238"/>
+      <c r="AE16" s="238"/>
+      <c r="AF16" s="238"/>
+      <c r="AG16" s="238"/>
+      <c r="AH16" s="238"/>
       <c r="AI16" s="48"/>
       <c r="AJ16" s="48"/>
       <c r="AK16" s="48"/>
@@ -17910,36 +17930,36 @@
       <c r="AN16" s="50"/>
     </row>
     <row r="17" spans="6:61" s="46" customFormat="1" ht="16" customHeight="1">
-      <c r="G17" s="159" t="s">
-        <v>170</v>
-      </c>
-      <c r="H17" s="159"/>
-      <c r="I17" s="159"/>
-      <c r="J17" s="159"/>
-      <c r="K17" s="159"/>
-      <c r="L17" s="159"/>
-      <c r="M17" s="159"/>
-      <c r="N17" s="159"/>
-      <c r="O17" s="159"/>
-      <c r="P17" s="159"/>
-      <c r="Q17" s="159"/>
-      <c r="R17" s="159"/>
-      <c r="S17" s="159"/>
-      <c r="T17" s="159"/>
-      <c r="U17" s="159"/>
-      <c r="V17" s="159"/>
-      <c r="W17" s="159"/>
-      <c r="X17" s="159"/>
-      <c r="Y17" s="159"/>
-      <c r="Z17" s="159"/>
-      <c r="AA17" s="159"/>
-      <c r="AB17" s="159"/>
-      <c r="AC17" s="159"/>
-      <c r="AD17" s="159"/>
-      <c r="AE17" s="159"/>
-      <c r="AF17" s="159"/>
-      <c r="AG17" s="159"/>
-      <c r="AH17" s="159"/>
+      <c r="G17" s="238" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="238"/>
+      <c r="I17" s="238"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="238"/>
+      <c r="L17" s="238"/>
+      <c r="M17" s="238"/>
+      <c r="N17" s="238"/>
+      <c r="O17" s="238"/>
+      <c r="P17" s="238"/>
+      <c r="Q17" s="238"/>
+      <c r="R17" s="238"/>
+      <c r="S17" s="238"/>
+      <c r="T17" s="238"/>
+      <c r="U17" s="238"/>
+      <c r="V17" s="238"/>
+      <c r="W17" s="238"/>
+      <c r="X17" s="238"/>
+      <c r="Y17" s="238"/>
+      <c r="Z17" s="238"/>
+      <c r="AA17" s="238"/>
+      <c r="AB17" s="238"/>
+      <c r="AC17" s="238"/>
+      <c r="AD17" s="238"/>
+      <c r="AE17" s="238"/>
+      <c r="AF17" s="238"/>
+      <c r="AG17" s="238"/>
+      <c r="AH17" s="238"/>
       <c r="AI17" s="49"/>
       <c r="AJ17" s="49"/>
       <c r="AK17" s="49"/>
@@ -17948,36 +17968,36 @@
       <c r="AN17" s="50"/>
     </row>
     <row r="18" spans="6:61" s="46" customFormat="1" ht="16" customHeight="1">
-      <c r="G18" s="159" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="159"/>
-      <c r="I18" s="159"/>
-      <c r="J18" s="159"/>
-      <c r="K18" s="159"/>
-      <c r="L18" s="159"/>
-      <c r="M18" s="159"/>
-      <c r="N18" s="159"/>
-      <c r="O18" s="159"/>
-      <c r="P18" s="159"/>
-      <c r="Q18" s="159"/>
-      <c r="R18" s="159"/>
-      <c r="S18" s="159"/>
-      <c r="T18" s="159"/>
-      <c r="U18" s="159"/>
-      <c r="V18" s="159"/>
-      <c r="W18" s="159"/>
-      <c r="X18" s="159"/>
-      <c r="Y18" s="159"/>
-      <c r="Z18" s="159"/>
-      <c r="AA18" s="159"/>
-      <c r="AB18" s="159"/>
-      <c r="AC18" s="159"/>
-      <c r="AD18" s="159"/>
-      <c r="AE18" s="159"/>
-      <c r="AF18" s="159"/>
-      <c r="AG18" s="159"/>
-      <c r="AH18" s="159"/>
+      <c r="G18" s="238" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="238"/>
+      <c r="I18" s="238"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="238"/>
+      <c r="L18" s="238"/>
+      <c r="M18" s="238"/>
+      <c r="N18" s="238"/>
+      <c r="O18" s="238"/>
+      <c r="P18" s="238"/>
+      <c r="Q18" s="238"/>
+      <c r="R18" s="238"/>
+      <c r="S18" s="238"/>
+      <c r="T18" s="238"/>
+      <c r="U18" s="238"/>
+      <c r="V18" s="238"/>
+      <c r="W18" s="238"/>
+      <c r="X18" s="238"/>
+      <c r="Y18" s="238"/>
+      <c r="Z18" s="238"/>
+      <c r="AA18" s="238"/>
+      <c r="AB18" s="238"/>
+      <c r="AC18" s="238"/>
+      <c r="AD18" s="238"/>
+      <c r="AE18" s="238"/>
+      <c r="AF18" s="238"/>
+      <c r="AG18" s="238"/>
+      <c r="AH18" s="238"/>
       <c r="AI18" s="49"/>
       <c r="AJ18" s="49"/>
       <c r="AK18" s="49"/>
@@ -18017,102 +18037,102 @@
       <c r="AI19" s="1"/>
     </row>
     <row r="20" spans="6:61" s="12" customFormat="1" ht="16" customHeight="1">
-      <c r="G20" s="160" t="s">
-        <v>165</v>
-      </c>
-      <c r="H20" s="160"/>
-      <c r="I20" s="160"/>
-      <c r="J20" s="160"/>
-      <c r="K20" s="160"/>
-      <c r="L20" s="160"/>
-      <c r="M20" s="160"/>
-      <c r="N20" s="160"/>
-      <c r="O20" s="160"/>
-      <c r="P20" s="160"/>
-      <c r="Q20" s="160"/>
-      <c r="R20" s="160"/>
-      <c r="S20" s="160"/>
-      <c r="T20" s="160"/>
-      <c r="U20" s="160"/>
-      <c r="V20" s="160"/>
-      <c r="W20" s="160"/>
-      <c r="X20" s="160"/>
-      <c r="Y20" s="160"/>
-      <c r="Z20" s="160"/>
-      <c r="AA20" s="160"/>
-      <c r="AB20" s="160"/>
-      <c r="AC20" s="160"/>
-      <c r="AD20" s="160"/>
-      <c r="AE20" s="160"/>
-      <c r="AF20" s="160"/>
-      <c r="AG20" s="160"/>
-      <c r="AH20" s="160"/>
+      <c r="G20" s="239" t="s">
+        <v>169</v>
+      </c>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="239"/>
+      <c r="K20" s="239"/>
+      <c r="L20" s="239"/>
+      <c r="M20" s="239"/>
+      <c r="N20" s="239"/>
+      <c r="O20" s="239"/>
+      <c r="P20" s="239"/>
+      <c r="Q20" s="239"/>
+      <c r="R20" s="239"/>
+      <c r="S20" s="239"/>
+      <c r="T20" s="239"/>
+      <c r="U20" s="239"/>
+      <c r="V20" s="239"/>
+      <c r="W20" s="239"/>
+      <c r="X20" s="239"/>
+      <c r="Y20" s="239"/>
+      <c r="Z20" s="239"/>
+      <c r="AA20" s="239"/>
+      <c r="AB20" s="239"/>
+      <c r="AC20" s="239"/>
+      <c r="AD20" s="239"/>
+      <c r="AE20" s="239"/>
+      <c r="AF20" s="239"/>
+      <c r="AG20" s="239"/>
+      <c r="AH20" s="239"/>
       <c r="AI20" s="13"/>
     </row>
     <row r="21" spans="6:61" s="12" customFormat="1" ht="16" customHeight="1">
-      <c r="G21" s="160" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" s="160"/>
-      <c r="I21" s="160"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="160"/>
-      <c r="L21" s="160"/>
-      <c r="M21" s="160"/>
-      <c r="N21" s="160"/>
-      <c r="O21" s="160"/>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
-      <c r="R21" s="160"/>
-      <c r="S21" s="160"/>
-      <c r="T21" s="160"/>
-      <c r="U21" s="160"/>
-      <c r="V21" s="160"/>
-      <c r="W21" s="160"/>
-      <c r="X21" s="160"/>
-      <c r="Y21" s="160"/>
-      <c r="Z21" s="160"/>
-      <c r="AA21" s="160"/>
-      <c r="AB21" s="160"/>
-      <c r="AC21" s="160"/>
-      <c r="AD21" s="160"/>
-      <c r="AE21" s="160"/>
-      <c r="AF21" s="160"/>
-      <c r="AG21" s="160"/>
-      <c r="AH21" s="160"/>
+      <c r="G21" s="239" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="239"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
+      <c r="M21" s="239"/>
+      <c r="N21" s="239"/>
+      <c r="O21" s="239"/>
+      <c r="P21" s="239"/>
+      <c r="Q21" s="239"/>
+      <c r="R21" s="239"/>
+      <c r="S21" s="239"/>
+      <c r="T21" s="239"/>
+      <c r="U21" s="239"/>
+      <c r="V21" s="239"/>
+      <c r="W21" s="239"/>
+      <c r="X21" s="239"/>
+      <c r="Y21" s="239"/>
+      <c r="Z21" s="239"/>
+      <c r="AA21" s="239"/>
+      <c r="AB21" s="239"/>
+      <c r="AC21" s="239"/>
+      <c r="AD21" s="239"/>
+      <c r="AE21" s="239"/>
+      <c r="AF21" s="239"/>
+      <c r="AG21" s="239"/>
+      <c r="AH21" s="239"/>
       <c r="AI21" s="13"/>
     </row>
     <row r="22" spans="6:61" s="12" customFormat="1" ht="16" customHeight="1">
-      <c r="G22" s="160" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="160"/>
-      <c r="I22" s="160"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="160"/>
-      <c r="N22" s="160"/>
-      <c r="O22" s="160"/>
-      <c r="P22" s="160"/>
-      <c r="Q22" s="160"/>
-      <c r="R22" s="160"/>
-      <c r="S22" s="160"/>
-      <c r="T22" s="160"/>
-      <c r="U22" s="160"/>
-      <c r="V22" s="160"/>
-      <c r="W22" s="160"/>
-      <c r="X22" s="160"/>
-      <c r="Y22" s="160"/>
-      <c r="Z22" s="160"/>
-      <c r="AA22" s="160"/>
-      <c r="AB22" s="160"/>
-      <c r="AC22" s="160"/>
-      <c r="AD22" s="160"/>
-      <c r="AE22" s="160"/>
-      <c r="AF22" s="160"/>
-      <c r="AG22" s="160"/>
-      <c r="AH22" s="160"/>
+      <c r="G22" s="239" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="239"/>
+      <c r="M22" s="239"/>
+      <c r="N22" s="239"/>
+      <c r="O22" s="239"/>
+      <c r="P22" s="239"/>
+      <c r="Q22" s="239"/>
+      <c r="R22" s="239"/>
+      <c r="S22" s="239"/>
+      <c r="T22" s="239"/>
+      <c r="U22" s="239"/>
+      <c r="V22" s="239"/>
+      <c r="W22" s="239"/>
+      <c r="X22" s="239"/>
+      <c r="Y22" s="239"/>
+      <c r="Z22" s="239"/>
+      <c r="AA22" s="239"/>
+      <c r="AB22" s="239"/>
+      <c r="AC22" s="239"/>
+      <c r="AD22" s="239"/>
+      <c r="AE22" s="239"/>
+      <c r="AF22" s="239"/>
+      <c r="AG22" s="239"/>
+      <c r="AH22" s="239"/>
       <c r="AI22" s="13"/>
     </row>
     <row r="23" spans="6:61" s="2" customFormat="1" ht="16" customHeight="1">
@@ -18145,85 +18165,85 @@
       <c r="AG23" s="10"/>
       <c r="AH23" s="10"/>
       <c r="AI23" s="1"/>
-      <c r="AN23" s="161"/>
-      <c r="AO23" s="161"/>
-      <c r="AP23" s="161"/>
-      <c r="AQ23" s="161"/>
-      <c r="AR23" s="161"/>
-      <c r="AS23" s="161"/>
-      <c r="AT23" s="161"/>
-      <c r="AU23" s="161"/>
-      <c r="AV23" s="161"/>
-      <c r="AW23" s="161"/>
-      <c r="AX23" s="161"/>
-      <c r="AY23" s="161"/>
-      <c r="AZ23" s="161"/>
-      <c r="BA23" s="161"/>
-      <c r="BB23" s="161"/>
-      <c r="BC23" s="161"/>
-      <c r="BD23" s="161"/>
-      <c r="BE23" s="161"/>
-      <c r="BF23" s="161"/>
-      <c r="BG23" s="161"/>
-      <c r="BH23" s="161"/>
-      <c r="BI23" s="161"/>
+      <c r="AN23" s="240"/>
+      <c r="AO23" s="240"/>
+      <c r="AP23" s="240"/>
+      <c r="AQ23" s="240"/>
+      <c r="AR23" s="240"/>
+      <c r="AS23" s="240"/>
+      <c r="AT23" s="240"/>
+      <c r="AU23" s="240"/>
+      <c r="AV23" s="240"/>
+      <c r="AW23" s="240"/>
+      <c r="AX23" s="240"/>
+      <c r="AY23" s="240"/>
+      <c r="AZ23" s="240"/>
+      <c r="BA23" s="240"/>
+      <c r="BB23" s="240"/>
+      <c r="BC23" s="240"/>
+      <c r="BD23" s="240"/>
+      <c r="BE23" s="240"/>
+      <c r="BF23" s="240"/>
+      <c r="BG23" s="240"/>
+      <c r="BH23" s="240"/>
+      <c r="BI23" s="240"/>
     </row>
     <row r="24" spans="6:61" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="F24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="157" t="s">
-        <v>166</v>
-      </c>
-      <c r="H24" s="157"/>
-      <c r="I24" s="157"/>
-      <c r="J24" s="157"/>
-      <c r="K24" s="157"/>
-      <c r="L24" s="157"/>
-      <c r="M24" s="157"/>
-      <c r="N24" s="157"/>
-      <c r="O24" s="157"/>
-      <c r="P24" s="157"/>
-      <c r="Q24" s="157"/>
-      <c r="R24" s="157"/>
-      <c r="S24" s="157"/>
-      <c r="T24" s="157"/>
-      <c r="U24" s="157"/>
-      <c r="V24" s="157"/>
-      <c r="W24" s="157"/>
-      <c r="X24" s="157"/>
-      <c r="Y24" s="157"/>
-      <c r="Z24" s="157"/>
-      <c r="AA24" s="157"/>
-      <c r="AB24" s="157"/>
-      <c r="AC24" s="157"/>
-      <c r="AD24" s="157"/>
-      <c r="AE24" s="157"/>
-      <c r="AF24" s="157"/>
-      <c r="AG24" s="157"/>
-      <c r="AH24" s="157"/>
-      <c r="AM24" s="162"/>
-      <c r="AN24" s="162"/>
-      <c r="AO24" s="162"/>
-      <c r="AP24" s="162"/>
-      <c r="AQ24" s="162"/>
-      <c r="AR24" s="162"/>
-      <c r="AS24" s="162"/>
-      <c r="AT24" s="162"/>
-      <c r="AU24" s="162"/>
-      <c r="AV24" s="162"/>
-      <c r="AW24" s="162"/>
-      <c r="AX24" s="162"/>
-      <c r="AY24" s="162"/>
-      <c r="AZ24" s="162"/>
-      <c r="BA24" s="162"/>
-      <c r="BB24" s="162"/>
-      <c r="BC24" s="162"/>
-      <c r="BD24" s="162"/>
-      <c r="BE24" s="162"/>
-      <c r="BF24" s="162"/>
-      <c r="BG24" s="162"/>
-      <c r="BH24" s="162"/>
+      <c r="G24" s="236" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="236"/>
+      <c r="I24" s="236"/>
+      <c r="J24" s="236"/>
+      <c r="K24" s="236"/>
+      <c r="L24" s="236"/>
+      <c r="M24" s="236"/>
+      <c r="N24" s="236"/>
+      <c r="O24" s="236"/>
+      <c r="P24" s="236"/>
+      <c r="Q24" s="236"/>
+      <c r="R24" s="236"/>
+      <c r="S24" s="236"/>
+      <c r="T24" s="236"/>
+      <c r="U24" s="236"/>
+      <c r="V24" s="236"/>
+      <c r="W24" s="236"/>
+      <c r="X24" s="236"/>
+      <c r="Y24" s="236"/>
+      <c r="Z24" s="236"/>
+      <c r="AA24" s="236"/>
+      <c r="AB24" s="236"/>
+      <c r="AC24" s="236"/>
+      <c r="AD24" s="236"/>
+      <c r="AE24" s="236"/>
+      <c r="AF24" s="236"/>
+      <c r="AG24" s="236"/>
+      <c r="AH24" s="236"/>
+      <c r="AM24" s="241"/>
+      <c r="AN24" s="241"/>
+      <c r="AO24" s="241"/>
+      <c r="AP24" s="241"/>
+      <c r="AQ24" s="241"/>
+      <c r="AR24" s="241"/>
+      <c r="AS24" s="241"/>
+      <c r="AT24" s="241"/>
+      <c r="AU24" s="241"/>
+      <c r="AV24" s="241"/>
+      <c r="AW24" s="241"/>
+      <c r="AX24" s="241"/>
+      <c r="AY24" s="241"/>
+      <c r="AZ24" s="241"/>
+      <c r="BA24" s="241"/>
+      <c r="BB24" s="241"/>
+      <c r="BC24" s="241"/>
+      <c r="BD24" s="241"/>
+      <c r="BE24" s="241"/>
+      <c r="BF24" s="241"/>
+      <c r="BG24" s="241"/>
+      <c r="BH24" s="241"/>
     </row>
     <row r="25" spans="6:61" s="8" customFormat="1" ht="16.5" customHeight="1">
       <c r="F25" s="9"/>
@@ -18231,57 +18251,57 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
-      <c r="K25" s="157" t="s">
-        <v>173</v>
-      </c>
-      <c r="L25" s="157"/>
-      <c r="M25" s="157"/>
-      <c r="N25" s="157"/>
-      <c r="O25" s="157"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="157" t="str">
+      <c r="K25" s="236" t="s">
+        <v>158</v>
+      </c>
+      <c r="L25" s="236"/>
+      <c r="M25" s="236"/>
+      <c r="N25" s="236"/>
+      <c r="O25" s="236"/>
+      <c r="P25" s="236"/>
+      <c r="Q25" s="236" t="str">
         <f>K10</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="R25" s="157"/>
-      <c r="S25" s="157"/>
-      <c r="T25" s="157"/>
-      <c r="U25" s="157"/>
-      <c r="V25" s="157"/>
-      <c r="W25" s="157"/>
-      <c r="X25" s="157"/>
-      <c r="Y25" s="157"/>
-      <c r="Z25" s="157"/>
-      <c r="AA25" s="157"/>
-      <c r="AB25" s="157"/>
-      <c r="AC25" s="157"/>
-      <c r="AD25" s="157"/>
-      <c r="AE25" s="157"/>
-      <c r="AF25" s="157"/>
-      <c r="AG25" s="157"/>
+      <c r="R25" s="236"/>
+      <c r="S25" s="236"/>
+      <c r="T25" s="236"/>
+      <c r="U25" s="236"/>
+      <c r="V25" s="236"/>
+      <c r="W25" s="236"/>
+      <c r="X25" s="236"/>
+      <c r="Y25" s="236"/>
+      <c r="Z25" s="236"/>
+      <c r="AA25" s="236"/>
+      <c r="AB25" s="236"/>
+      <c r="AC25" s="236"/>
+      <c r="AD25" s="236"/>
+      <c r="AE25" s="236"/>
+      <c r="AF25" s="236"/>
+      <c r="AG25" s="236"/>
       <c r="AH25" s="10"/>
-      <c r="AM25" s="163"/>
-      <c r="AN25" s="163"/>
-      <c r="AO25" s="163"/>
-      <c r="AP25" s="163"/>
-      <c r="AQ25" s="163"/>
-      <c r="AR25" s="163"/>
-      <c r="AS25" s="163"/>
-      <c r="AT25" s="163"/>
-      <c r="AU25" s="163"/>
-      <c r="AV25" s="163"/>
-      <c r="AW25" s="163"/>
-      <c r="AX25" s="163"/>
-      <c r="AY25" s="163"/>
-      <c r="AZ25" s="163"/>
-      <c r="BA25" s="163"/>
-      <c r="BB25" s="163"/>
-      <c r="BC25" s="163"/>
-      <c r="BD25" s="163"/>
-      <c r="BE25" s="163"/>
-      <c r="BF25" s="163"/>
-      <c r="BG25" s="163"/>
-      <c r="BH25" s="163"/>
+      <c r="AM25" s="242"/>
+      <c r="AN25" s="242"/>
+      <c r="AO25" s="242"/>
+      <c r="AP25" s="242"/>
+      <c r="AQ25" s="242"/>
+      <c r="AR25" s="242"/>
+      <c r="AS25" s="242"/>
+      <c r="AT25" s="242"/>
+      <c r="AU25" s="242"/>
+      <c r="AV25" s="242"/>
+      <c r="AW25" s="242"/>
+      <c r="AX25" s="242"/>
+      <c r="AY25" s="242"/>
+      <c r="AZ25" s="242"/>
+      <c r="BA25" s="242"/>
+      <c r="BB25" s="242"/>
+      <c r="BC25" s="242"/>
+      <c r="BD25" s="242"/>
+      <c r="BE25" s="242"/>
+      <c r="BF25" s="242"/>
+      <c r="BG25" s="242"/>
+      <c r="BH25" s="242"/>
     </row>
     <row r="26" spans="6:61" s="8" customFormat="1" ht="16.5" customHeight="1">
       <c r="F26" s="9"/>
@@ -18289,33 +18309,33 @@
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
-      <c r="K26" s="157" t="s">
-        <v>174</v>
-      </c>
-      <c r="L26" s="157"/>
-      <c r="M26" s="157"/>
-      <c r="N26" s="157"/>
-      <c r="O26" s="157"/>
-      <c r="P26" s="157"/>
-      <c r="Q26" s="157" t="s">
+      <c r="K26" s="236" t="s">
+        <v>159</v>
+      </c>
+      <c r="L26" s="236"/>
+      <c r="M26" s="236"/>
+      <c r="N26" s="236"/>
+      <c r="O26" s="236"/>
+      <c r="P26" s="236"/>
+      <c r="Q26" s="236" t="s">
         <v>11</v>
       </c>
-      <c r="R26" s="157"/>
-      <c r="S26" s="157"/>
-      <c r="T26" s="157"/>
-      <c r="U26" s="157"/>
-      <c r="V26" s="157"/>
-      <c r="W26" s="157"/>
-      <c r="X26" s="157"/>
-      <c r="Y26" s="157"/>
-      <c r="Z26" s="157"/>
-      <c r="AA26" s="157"/>
-      <c r="AB26" s="157"/>
-      <c r="AC26" s="157"/>
-      <c r="AD26" s="157"/>
-      <c r="AE26" s="157"/>
-      <c r="AF26" s="157"/>
-      <c r="AG26" s="157"/>
+      <c r="R26" s="236"/>
+      <c r="S26" s="236"/>
+      <c r="T26" s="236"/>
+      <c r="U26" s="236"/>
+      <c r="V26" s="236"/>
+      <c r="W26" s="236"/>
+      <c r="X26" s="236"/>
+      <c r="Y26" s="236"/>
+      <c r="Z26" s="236"/>
+      <c r="AA26" s="236"/>
+      <c r="AB26" s="236"/>
+      <c r="AC26" s="236"/>
+      <c r="AD26" s="236"/>
+      <c r="AE26" s="236"/>
+      <c r="AF26" s="236"/>
+      <c r="AG26" s="236"/>
       <c r="AH26" s="10"/>
     </row>
     <row r="27" spans="6:61" s="8" customFormat="1" ht="16.5" customHeight="1">
@@ -18324,33 +18344,33 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
-      <c r="K27" s="157" t="s">
-        <v>175</v>
-      </c>
-      <c r="L27" s="157"/>
-      <c r="M27" s="157"/>
-      <c r="N27" s="157"/>
-      <c r="O27" s="157"/>
-      <c r="P27" s="157"/>
-      <c r="Q27" s="157" t="s">
-        <v>101</v>
-      </c>
-      <c r="R27" s="157"/>
-      <c r="S27" s="157"/>
-      <c r="T27" s="157"/>
-      <c r="U27" s="157"/>
-      <c r="V27" s="157"/>
-      <c r="W27" s="157"/>
-      <c r="X27" s="157"/>
-      <c r="Y27" s="157"/>
-      <c r="Z27" s="157"/>
-      <c r="AA27" s="157"/>
-      <c r="AB27" s="157"/>
-      <c r="AC27" s="157"/>
-      <c r="AD27" s="157"/>
-      <c r="AE27" s="157"/>
-      <c r="AF27" s="157"/>
-      <c r="AG27" s="157"/>
+      <c r="K27" s="236" t="s">
+        <v>160</v>
+      </c>
+      <c r="L27" s="236"/>
+      <c r="M27" s="236"/>
+      <c r="N27" s="236"/>
+      <c r="O27" s="236"/>
+      <c r="P27" s="236"/>
+      <c r="Q27" s="236" t="s">
+        <v>99</v>
+      </c>
+      <c r="R27" s="236"/>
+      <c r="S27" s="236"/>
+      <c r="T27" s="236"/>
+      <c r="U27" s="236"/>
+      <c r="V27" s="236"/>
+      <c r="W27" s="236"/>
+      <c r="X27" s="236"/>
+      <c r="Y27" s="236"/>
+      <c r="Z27" s="236"/>
+      <c r="AA27" s="236"/>
+      <c r="AB27" s="236"/>
+      <c r="AC27" s="236"/>
+      <c r="AD27" s="236"/>
+      <c r="AE27" s="236"/>
+      <c r="AF27" s="236"/>
+      <c r="AG27" s="236"/>
       <c r="AH27" s="10"/>
     </row>
     <row r="28" spans="6:61" s="8" customFormat="1" ht="16.5" customHeight="1">
@@ -18359,33 +18379,33 @@
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
-      <c r="K28" s="157" t="s">
-        <v>176</v>
-      </c>
-      <c r="L28" s="157"/>
-      <c r="M28" s="157"/>
-      <c r="N28" s="157"/>
-      <c r="O28" s="157"/>
-      <c r="P28" s="157"/>
-      <c r="Q28" s="157" t="s">
+      <c r="K28" s="236" t="s">
+        <v>161</v>
+      </c>
+      <c r="L28" s="236"/>
+      <c r="M28" s="236"/>
+      <c r="N28" s="236"/>
+      <c r="O28" s="236"/>
+      <c r="P28" s="236"/>
+      <c r="Q28" s="236" t="s">
         <v>12</v>
       </c>
-      <c r="R28" s="157"/>
-      <c r="S28" s="157"/>
-      <c r="T28" s="157"/>
-      <c r="U28" s="157"/>
-      <c r="V28" s="157"/>
-      <c r="W28" s="157"/>
-      <c r="X28" s="157"/>
-      <c r="Y28" s="157"/>
-      <c r="Z28" s="157"/>
-      <c r="AA28" s="157"/>
-      <c r="AB28" s="157"/>
-      <c r="AC28" s="157"/>
-      <c r="AD28" s="157"/>
-      <c r="AE28" s="157"/>
-      <c r="AF28" s="157"/>
-      <c r="AG28" s="157"/>
+      <c r="R28" s="236"/>
+      <c r="S28" s="236"/>
+      <c r="T28" s="236"/>
+      <c r="U28" s="236"/>
+      <c r="V28" s="236"/>
+      <c r="W28" s="236"/>
+      <c r="X28" s="236"/>
+      <c r="Y28" s="236"/>
+      <c r="Z28" s="236"/>
+      <c r="AA28" s="236"/>
+      <c r="AB28" s="236"/>
+      <c r="AC28" s="236"/>
+      <c r="AD28" s="236"/>
+      <c r="AE28" s="236"/>
+      <c r="AF28" s="236"/>
+      <c r="AG28" s="236"/>
       <c r="AH28" s="10"/>
     </row>
     <row r="29" spans="6:61" s="8" customFormat="1" ht="16.5" customHeight="1">
@@ -18394,26 +18414,26 @@
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
-      <c r="K29" s="157" t="s">
-        <v>177</v>
-      </c>
-      <c r="L29" s="157"/>
-      <c r="M29" s="157"/>
-      <c r="N29" s="157"/>
-      <c r="O29" s="157"/>
-      <c r="P29" s="157"/>
-      <c r="Q29" s="160" t="s">
-        <v>172</v>
-      </c>
-      <c r="R29" s="160"/>
-      <c r="S29" s="160"/>
-      <c r="T29" s="160"/>
-      <c r="U29" s="160"/>
-      <c r="V29" s="160"/>
-      <c r="W29" s="160"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="160"/>
-      <c r="Z29" s="160"/>
+      <c r="K29" s="236" t="s">
+        <v>162</v>
+      </c>
+      <c r="L29" s="236"/>
+      <c r="M29" s="236"/>
+      <c r="N29" s="236"/>
+      <c r="O29" s="236"/>
+      <c r="P29" s="236"/>
+      <c r="Q29" s="239" t="s">
+        <v>157</v>
+      </c>
+      <c r="R29" s="239"/>
+      <c r="S29" s="239"/>
+      <c r="T29" s="239"/>
+      <c r="U29" s="239"/>
+      <c r="V29" s="239"/>
+      <c r="W29" s="239"/>
+      <c r="X29" s="239"/>
+      <c r="Y29" s="239"/>
+      <c r="Z29" s="239"/>
       <c r="AA29" s="150"/>
       <c r="AB29" s="150"/>
       <c r="AC29" s="150"/>
@@ -18458,19 +18478,19 @@
       <c r="F31" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="157" t="s">
-        <v>167</v>
-      </c>
-      <c r="H31" s="157"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="157"/>
-      <c r="M31" s="157"/>
-      <c r="N31" s="157"/>
-      <c r="O31" s="157"/>
-      <c r="P31" s="157"/>
-      <c r="Q31" s="157"/>
+      <c r="G31" s="236" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="236"/>
+      <c r="I31" s="236"/>
+      <c r="J31" s="236"/>
+      <c r="K31" s="236"/>
+      <c r="L31" s="236"/>
+      <c r="M31" s="236"/>
+      <c r="N31" s="236"/>
+      <c r="O31" s="236"/>
+      <c r="P31" s="236"/>
+      <c r="Q31" s="236"/>
       <c r="R31" s="10"/>
       <c r="S31" s="143"/>
       <c r="T31" s="143"/>
@@ -18495,32 +18515,32 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="145"/>
-      <c r="K32" s="168" t="s">
-        <v>160</v>
-      </c>
-      <c r="L32" s="168"/>
-      <c r="M32" s="168"/>
-      <c r="N32" s="168"/>
-      <c r="O32" s="168"/>
-      <c r="P32" s="168"/>
-      <c r="Q32" s="168"/>
-      <c r="R32" s="168"/>
-      <c r="S32" s="168"/>
-      <c r="T32" s="168"/>
-      <c r="U32" s="168"/>
-      <c r="V32" s="168"/>
-      <c r="W32" s="168"/>
-      <c r="X32" s="168"/>
-      <c r="Y32" s="168"/>
-      <c r="Z32" s="168"/>
-      <c r="AA32" s="168"/>
-      <c r="AB32" s="168"/>
-      <c r="AC32" s="168"/>
-      <c r="AD32" s="168"/>
-      <c r="AE32" s="168"/>
-      <c r="AF32" s="168"/>
-      <c r="AG32" s="168"/>
-      <c r="AH32" s="168"/>
+      <c r="K32" s="247" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="247"/>
+      <c r="M32" s="247"/>
+      <c r="N32" s="247"/>
+      <c r="O32" s="247"/>
+      <c r="P32" s="247"/>
+      <c r="Q32" s="247"/>
+      <c r="R32" s="247"/>
+      <c r="S32" s="247"/>
+      <c r="T32" s="247"/>
+      <c r="U32" s="247"/>
+      <c r="V32" s="247"/>
+      <c r="W32" s="247"/>
+      <c r="X32" s="247"/>
+      <c r="Y32" s="247"/>
+      <c r="Z32" s="247"/>
+      <c r="AA32" s="247"/>
+      <c r="AB32" s="247"/>
+      <c r="AC32" s="247"/>
+      <c r="AD32" s="247"/>
+      <c r="AE32" s="247"/>
+      <c r="AF32" s="247"/>
+      <c r="AG32" s="247"/>
+      <c r="AH32" s="247"/>
     </row>
     <row r="33" spans="6:37" s="8" customFormat="1" ht="16.5" customHeight="1">
       <c r="F33" s="9"/>
@@ -18528,32 +18548,32 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
       <c r="J33" s="145"/>
-      <c r="K33" s="168" t="s">
-        <v>161</v>
-      </c>
-      <c r="L33" s="168"/>
-      <c r="M33" s="168"/>
-      <c r="N33" s="168"/>
-      <c r="O33" s="168"/>
-      <c r="P33" s="168"/>
-      <c r="Q33" s="168"/>
-      <c r="R33" s="168"/>
-      <c r="S33" s="168"/>
-      <c r="T33" s="168"/>
-      <c r="U33" s="168"/>
-      <c r="V33" s="168"/>
-      <c r="W33" s="168"/>
-      <c r="X33" s="168"/>
-      <c r="Y33" s="168"/>
-      <c r="Z33" s="168"/>
-      <c r="AA33" s="168"/>
-      <c r="AB33" s="168"/>
-      <c r="AC33" s="168"/>
-      <c r="AD33" s="168"/>
-      <c r="AE33" s="168"/>
-      <c r="AF33" s="168"/>
-      <c r="AG33" s="168"/>
-      <c r="AH33" s="168"/>
+      <c r="K33" s="247" t="s">
+        <v>152</v>
+      </c>
+      <c r="L33" s="247"/>
+      <c r="M33" s="247"/>
+      <c r="N33" s="247"/>
+      <c r="O33" s="247"/>
+      <c r="P33" s="247"/>
+      <c r="Q33" s="247"/>
+      <c r="R33" s="247"/>
+      <c r="S33" s="247"/>
+      <c r="T33" s="247"/>
+      <c r="U33" s="247"/>
+      <c r="V33" s="247"/>
+      <c r="W33" s="247"/>
+      <c r="X33" s="247"/>
+      <c r="Y33" s="247"/>
+      <c r="Z33" s="247"/>
+      <c r="AA33" s="247"/>
+      <c r="AB33" s="247"/>
+      <c r="AC33" s="247"/>
+      <c r="AD33" s="247"/>
+      <c r="AE33" s="247"/>
+      <c r="AF33" s="247"/>
+      <c r="AG33" s="247"/>
+      <c r="AH33" s="247"/>
     </row>
     <row r="34" spans="6:37" s="2" customFormat="1" ht="5" customHeight="1">
       <c r="F34" s="10"/>
@@ -18588,41 +18608,41 @@
     </row>
     <row r="35" spans="6:37" s="152" customFormat="1" ht="19.5" customHeight="1">
       <c r="F35" s="151" t="s">
-        <v>157</v>
-      </c>
-      <c r="G35" s="165" t="s">
-        <v>158</v>
-      </c>
-      <c r="H35" s="165"/>
-      <c r="I35" s="165"/>
-      <c r="J35" s="165"/>
-      <c r="K35" s="165"/>
-      <c r="L35" s="165"/>
-      <c r="M35" s="165"/>
-      <c r="N35" s="165"/>
-      <c r="O35" s="165"/>
-      <c r="P35" s="165"/>
-      <c r="Q35" s="165"/>
-      <c r="R35" s="166" t="str">
+        <v>149</v>
+      </c>
+      <c r="G35" s="244" t="s">
+        <v>173</v>
+      </c>
+      <c r="H35" s="244"/>
+      <c r="I35" s="244"/>
+      <c r="J35" s="244"/>
+      <c r="K35" s="244"/>
+      <c r="L35" s="244"/>
+      <c r="M35" s="244"/>
+      <c r="N35" s="244"/>
+      <c r="O35" s="244"/>
+      <c r="P35" s="244"/>
+      <c r="Q35" s="244"/>
+      <c r="R35" s="245" t="str">
         <f>대가산출!I3</f>
         <v>일금육십만원정 (₩600,000) - VAT별도</v>
       </c>
-      <c r="S35" s="166"/>
-      <c r="T35" s="166"/>
-      <c r="U35" s="166"/>
-      <c r="V35" s="166"/>
-      <c r="W35" s="166"/>
-      <c r="X35" s="166"/>
-      <c r="Y35" s="166"/>
-      <c r="Z35" s="166"/>
-      <c r="AA35" s="166"/>
-      <c r="AB35" s="166"/>
-      <c r="AC35" s="166"/>
-      <c r="AD35" s="166"/>
-      <c r="AE35" s="166"/>
-      <c r="AF35" s="166"/>
-      <c r="AG35" s="167"/>
-      <c r="AH35" s="167"/>
+      <c r="S35" s="245"/>
+      <c r="T35" s="245"/>
+      <c r="U35" s="245"/>
+      <c r="V35" s="245"/>
+      <c r="W35" s="245"/>
+      <c r="X35" s="245"/>
+      <c r="Y35" s="245"/>
+      <c r="Z35" s="245"/>
+      <c r="AA35" s="245"/>
+      <c r="AB35" s="245"/>
+      <c r="AC35" s="245"/>
+      <c r="AD35" s="245"/>
+      <c r="AE35" s="245"/>
+      <c r="AF35" s="245"/>
+      <c r="AG35" s="246"/>
+      <c r="AH35" s="246"/>
     </row>
     <row r="36" spans="6:37" s="2" customFormat="1" ht="5" customHeight="1">
       <c r="F36" s="10"/>
@@ -18659,19 +18679,19 @@
       <c r="F37" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="157" t="s">
-        <v>168</v>
-      </c>
-      <c r="H37" s="157"/>
-      <c r="I37" s="157"/>
-      <c r="J37" s="157"/>
-      <c r="K37" s="157"/>
-      <c r="L37" s="157"/>
-      <c r="M37" s="157"/>
-      <c r="N37" s="157"/>
-      <c r="O37" s="157"/>
-      <c r="P37" s="157"/>
-      <c r="Q37" s="157"/>
+      <c r="G37" s="236" t="s">
+        <v>172</v>
+      </c>
+      <c r="H37" s="236"/>
+      <c r="I37" s="236"/>
+      <c r="J37" s="236"/>
+      <c r="K37" s="236"/>
+      <c r="L37" s="236"/>
+      <c r="M37" s="236"/>
+      <c r="N37" s="236"/>
+      <c r="O37" s="236"/>
+      <c r="P37" s="236"/>
+      <c r="Q37" s="236"/>
       <c r="R37" s="10"/>
       <c r="S37" s="146"/>
       <c r="T37" s="146"/>
@@ -18696,32 +18716,32 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
-      <c r="K38" s="169" t="s">
-        <v>162</v>
-      </c>
-      <c r="L38" s="169"/>
-      <c r="M38" s="169"/>
-      <c r="N38" s="169"/>
-      <c r="O38" s="169"/>
-      <c r="P38" s="169"/>
-      <c r="Q38" s="169"/>
-      <c r="R38" s="169"/>
-      <c r="S38" s="169"/>
-      <c r="T38" s="169"/>
-      <c r="U38" s="169"/>
-      <c r="V38" s="169"/>
-      <c r="W38" s="169"/>
-      <c r="X38" s="169"/>
-      <c r="Y38" s="169"/>
-      <c r="Z38" s="169"/>
-      <c r="AA38" s="169"/>
-      <c r="AB38" s="169"/>
-      <c r="AC38" s="169"/>
-      <c r="AD38" s="169"/>
-      <c r="AE38" s="169"/>
-      <c r="AF38" s="169"/>
-      <c r="AG38" s="169"/>
-      <c r="AH38" s="169"/>
+      <c r="K38" s="248" t="s">
+        <v>153</v>
+      </c>
+      <c r="L38" s="248"/>
+      <c r="M38" s="248"/>
+      <c r="N38" s="248"/>
+      <c r="O38" s="248"/>
+      <c r="P38" s="248"/>
+      <c r="Q38" s="248"/>
+      <c r="R38" s="248"/>
+      <c r="S38" s="248"/>
+      <c r="T38" s="248"/>
+      <c r="U38" s="248"/>
+      <c r="V38" s="248"/>
+      <c r="W38" s="248"/>
+      <c r="X38" s="248"/>
+      <c r="Y38" s="248"/>
+      <c r="Z38" s="248"/>
+      <c r="AA38" s="248"/>
+      <c r="AB38" s="248"/>
+      <c r="AC38" s="248"/>
+      <c r="AD38" s="248"/>
+      <c r="AE38" s="248"/>
+      <c r="AF38" s="248"/>
+      <c r="AG38" s="248"/>
+      <c r="AH38" s="248"/>
       <c r="AI38" s="11"/>
       <c r="AJ38" s="11"/>
       <c r="AK38" s="11"/>
@@ -18732,32 +18752,32 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
-      <c r="K39" s="170" t="s">
-        <v>163</v>
-      </c>
-      <c r="L39" s="170"/>
-      <c r="M39" s="170"/>
-      <c r="N39" s="170"/>
-      <c r="O39" s="170"/>
-      <c r="P39" s="170"/>
-      <c r="Q39" s="170"/>
-      <c r="R39" s="170"/>
-      <c r="S39" s="170"/>
-      <c r="T39" s="170"/>
-      <c r="U39" s="170"/>
-      <c r="V39" s="170"/>
-      <c r="W39" s="170"/>
-      <c r="X39" s="170"/>
-      <c r="Y39" s="170"/>
-      <c r="Z39" s="170"/>
-      <c r="AA39" s="170"/>
-      <c r="AB39" s="170"/>
-      <c r="AC39" s="170"/>
-      <c r="AD39" s="170"/>
-      <c r="AE39" s="170"/>
-      <c r="AF39" s="170"/>
-      <c r="AG39" s="170"/>
-      <c r="AH39" s="170"/>
+      <c r="K39" s="249" t="s">
+        <v>154</v>
+      </c>
+      <c r="L39" s="249"/>
+      <c r="M39" s="249"/>
+      <c r="N39" s="249"/>
+      <c r="O39" s="249"/>
+      <c r="P39" s="249"/>
+      <c r="Q39" s="249"/>
+      <c r="R39" s="249"/>
+      <c r="S39" s="249"/>
+      <c r="T39" s="249"/>
+      <c r="U39" s="249"/>
+      <c r="V39" s="249"/>
+      <c r="W39" s="249"/>
+      <c r="X39" s="249"/>
+      <c r="Y39" s="249"/>
+      <c r="Z39" s="249"/>
+      <c r="AA39" s="249"/>
+      <c r="AB39" s="249"/>
+      <c r="AC39" s="249"/>
+      <c r="AD39" s="249"/>
+      <c r="AE39" s="249"/>
+      <c r="AF39" s="249"/>
+      <c r="AG39" s="249"/>
+      <c r="AH39" s="249"/>
     </row>
     <row r="40" spans="6:37" s="2" customFormat="1" ht="15">
       <c r="F40"/>
@@ -18854,7 +18874,7 @@
     </row>
     <row r="43" spans="6:37" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G43" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
@@ -18917,36 +18937,36 @@
       <c r="AI44" s="1"/>
     </row>
     <row r="45" spans="6:37" s="2" customFormat="1" ht="39.75" customHeight="1">
-      <c r="G45" s="164" t="s">
+      <c r="G45" s="243" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="164"/>
-      <c r="I45" s="164"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="164"/>
-      <c r="L45" s="164"/>
-      <c r="M45" s="164"/>
-      <c r="N45" s="164"/>
-      <c r="O45" s="164"/>
-      <c r="P45" s="164"/>
-      <c r="Q45" s="164"/>
-      <c r="R45" s="164"/>
-      <c r="S45" s="164"/>
-      <c r="T45" s="164"/>
-      <c r="U45" s="164"/>
-      <c r="V45" s="164"/>
-      <c r="W45" s="164"/>
-      <c r="X45" s="164"/>
-      <c r="Y45" s="164"/>
-      <c r="Z45" s="164"/>
-      <c r="AA45" s="164"/>
-      <c r="AB45" s="164"/>
-      <c r="AC45" s="164"/>
-      <c r="AD45" s="164"/>
-      <c r="AE45" s="164"/>
-      <c r="AF45" s="164"/>
-      <c r="AG45" s="164"/>
-      <c r="AH45" s="164"/>
+      <c r="H45" s="243"/>
+      <c r="I45" s="243"/>
+      <c r="J45" s="243"/>
+      <c r="K45" s="243"/>
+      <c r="L45" s="243"/>
+      <c r="M45" s="243"/>
+      <c r="N45" s="243"/>
+      <c r="O45" s="243"/>
+      <c r="P45" s="243"/>
+      <c r="Q45" s="243"/>
+      <c r="R45" s="243"/>
+      <c r="S45" s="243"/>
+      <c r="T45" s="243"/>
+      <c r="U45" s="243"/>
+      <c r="V45" s="243"/>
+      <c r="W45" s="243"/>
+      <c r="X45" s="243"/>
+      <c r="Y45" s="243"/>
+      <c r="Z45" s="243"/>
+      <c r="AA45" s="243"/>
+      <c r="AB45" s="243"/>
+      <c r="AC45" s="243"/>
+      <c r="AD45" s="243"/>
+      <c r="AE45" s="243"/>
+      <c r="AF45" s="243"/>
+      <c r="AG45" s="243"/>
+      <c r="AH45" s="243"/>
       <c r="AI45" s="3"/>
     </row>
     <row r="46" spans="6:37">
@@ -19739,16 +19759,16 @@
       <c r="D1" s="94"/>
       <c r="E1" s="94"/>
       <c r="F1" s="94"/>
-      <c r="G1" s="171" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
+      <c r="G1" s="250" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="250"/>
+      <c r="I1" s="250"/>
+      <c r="J1" s="250"/>
+      <c r="K1" s="250"/>
+      <c r="L1" s="250"/>
+      <c r="M1" s="250"/>
+      <c r="N1" s="250"/>
     </row>
     <row r="2" spans="2:14" s="21" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="B2" s="95"/>
@@ -19762,8 +19782,8 @@
       <c r="J2" s="52"/>
       <c r="K2" s="52"/>
       <c r="L2" s="52"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
+      <c r="M2" s="251"/>
+      <c r="N2" s="251"/>
     </row>
     <row r="3" spans="2:14" s="20" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
       <c r="B3" s="96"/>
@@ -19771,19 +19791,19 @@
       <c r="D3" s="97"/>
       <c r="E3" s="98"/>
       <c r="F3" s="99"/>
-      <c r="G3" s="173" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="174"/>
-      <c r="I3" s="175" t="str">
+      <c r="G3" s="252" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="253"/>
+      <c r="I3" s="301" t="str">
         <f>"일금"&amp;NUMBERSTRING(M24,1)&amp;"원정 (₩"&amp;TEXT(M24,"#,##0")&amp;") - VAT별도"</f>
         <v>일금육십만원정 (₩600,000) - VAT별도</v>
       </c>
-      <c r="J3" s="176"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="177"/>
+      <c r="J3" s="302"/>
+      <c r="K3" s="302"/>
+      <c r="L3" s="302"/>
+      <c r="M3" s="302"/>
+      <c r="N3" s="303"/>
     </row>
     <row r="4" spans="2:14" s="20" customFormat="1" ht="38.25" hidden="1" customHeight="1">
       <c r="B4" s="100"/>
@@ -19791,39 +19811,39 @@
       <c r="D4" s="102"/>
       <c r="E4" s="103"/>
       <c r="F4" s="104"/>
-      <c r="G4" s="178" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="179"/>
-      <c r="I4" s="180" t="str">
+      <c r="G4" s="254" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="255"/>
+      <c r="I4" s="256" t="str">
         <f>"일금 "&amp;NUMBERSTRING(M24,1)&amp;"원정"&amp;TEXT(M24,"(￦ #,##0)")&amp;" "</f>
         <v xml:space="preserve">일금 육십만원정(₩ 600,000) </v>
       </c>
-      <c r="J4" s="181"/>
-      <c r="K4" s="181"/>
-      <c r="L4" s="181"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="182"/>
-    </row>
-    <row r="5" spans="2:14" s="20" customFormat="1" ht="38.25" hidden="1" customHeight="1">
+      <c r="J4" s="257"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
+      <c r="M4" s="257"/>
+      <c r="N4" s="258"/>
+    </row>
+    <row r="5" spans="2:14" s="20" customFormat="1" ht="38.25" hidden="1" customHeight="1" thickBot="1">
       <c r="B5" s="105"/>
       <c r="C5" s="106"/>
       <c r="D5" s="107"/>
       <c r="E5" s="108"/>
       <c r="F5" s="109"/>
-      <c r="G5" s="183" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="184"/>
-      <c r="I5" s="185" t="e">
+      <c r="G5" s="259" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="260"/>
+      <c r="I5" s="261" t="e">
         <f>"일금 "&amp;NUMBERSTRING(M25,1)&amp;"원정"&amp;TEXT(M25,"(￦ #,##0)")&amp;" "</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J5" s="186"/>
-      <c r="K5" s="186"/>
-      <c r="L5" s="186"/>
-      <c r="M5" s="186"/>
-      <c r="N5" s="187"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="M5" s="262"/>
+      <c r="N5" s="263"/>
     </row>
     <row r="6" spans="2:14" s="20" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
       <c r="B6" s="110"/>
@@ -19831,16 +19851,16 @@
       <c r="D6" s="110"/>
       <c r="E6" s="110"/>
       <c r="F6" s="111"/>
-      <c r="G6" s="188" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="189"/>
-      <c r="I6" s="189"/>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
-      <c r="M6" s="189"/>
-      <c r="N6" s="190"/>
+      <c r="G6" s="264" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="265"/>
+      <c r="I6" s="265"/>
+      <c r="J6" s="265"/>
+      <c r="K6" s="265"/>
+      <c r="L6" s="265"/>
+      <c r="M6" s="265"/>
+      <c r="N6" s="266"/>
     </row>
     <row r="7" spans="2:14" s="19" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="B7" s="112"/>
@@ -19848,27 +19868,27 @@
       <c r="D7" s="113"/>
       <c r="E7" s="113"/>
       <c r="F7" s="114"/>
-      <c r="G7" s="191" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="192"/>
+      <c r="G7" s="267" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="268"/>
       <c r="I7" s="53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="53" t="s">
-        <v>43</v>
-      </c>
       <c r="M7" s="53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N7" s="54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="2:14" s="19" customFormat="1" ht="28" customHeight="1">
@@ -19877,10 +19897,10 @@
       <c r="D8" s="113"/>
       <c r="E8" s="113"/>
       <c r="F8" s="114"/>
-      <c r="G8" s="193" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="194"/>
+      <c r="G8" s="269" t="s">
+        <v>135</v>
+      </c>
+      <c r="H8" s="270"/>
       <c r="I8" s="55"/>
       <c r="J8" s="55"/>
       <c r="K8" s="55"/>
@@ -19899,13 +19919,13 @@
       <c r="F9" s="118"/>
       <c r="G9" s="91"/>
       <c r="H9" s="58" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J9" s="59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K9" s="59">
         <v>0</v>
@@ -19928,10 +19948,10 @@
       <c r="G10" s="92"/>
       <c r="H10" s="62"/>
       <c r="I10" s="63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J10" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K10" s="64">
         <v>0</v>
@@ -19954,10 +19974,10 @@
       <c r="G11" s="92"/>
       <c r="H11" s="62"/>
       <c r="I11" s="63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J11" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K11" s="64">
         <v>0</v>
@@ -19980,10 +20000,10 @@
       <c r="G12" s="92"/>
       <c r="H12" s="62"/>
       <c r="I12" s="63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K12" s="64">
         <v>0</v>
@@ -20005,13 +20025,13 @@
       <c r="F13" s="118"/>
       <c r="G13" s="93"/>
       <c r="H13" s="66" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I13" s="63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J13" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K13" s="64">
         <v>0</v>
@@ -20034,10 +20054,10 @@
       <c r="G14" s="92"/>
       <c r="H14" s="62"/>
       <c r="I14" s="63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K14" s="64">
         <v>1</v>
@@ -20060,10 +20080,10 @@
       <c r="G15" s="92"/>
       <c r="H15" s="62"/>
       <c r="I15" s="63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J15" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K15" s="64">
         <v>0</v>
@@ -20086,10 +20106,10 @@
       <c r="G16" s="92"/>
       <c r="H16" s="62"/>
       <c r="I16" s="63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J16" s="63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K16" s="64">
         <v>1</v>
@@ -20109,13 +20129,13 @@
       <c r="D17" s="121"/>
       <c r="E17" s="122"/>
       <c r="F17" s="123"/>
-      <c r="G17" s="195" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="196"/>
+      <c r="G17" s="271" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="272"/>
       <c r="I17" s="68"/>
       <c r="J17" s="69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K17" s="69">
         <v>10</v>
@@ -20126,7 +20146,7 @@
         <v>54634</v>
       </c>
       <c r="N17" s="72" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="2:14" s="19" customFormat="1" ht="28" customHeight="1">
@@ -20135,13 +20155,13 @@
       <c r="D18" s="121"/>
       <c r="E18" s="122"/>
       <c r="F18" s="123"/>
-      <c r="G18" s="195" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" s="196"/>
+      <c r="G18" s="271" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="272"/>
       <c r="I18" s="68"/>
       <c r="J18" s="69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K18" s="69">
         <v>10</v>
@@ -20152,7 +20172,7 @@
         <v>60098</v>
       </c>
       <c r="N18" s="72" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="2:14" s="19" customFormat="1" ht="28" customHeight="1">
@@ -20161,10 +20181,10 @@
       <c r="D19" s="121"/>
       <c r="E19" s="122"/>
       <c r="F19" s="123"/>
-      <c r="G19" s="195" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="196"/>
+      <c r="G19" s="271" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="272"/>
       <c r="I19" s="68"/>
       <c r="J19" s="69"/>
       <c r="K19" s="69"/>
@@ -20178,10 +20198,10 @@
       <c r="D20" s="125"/>
       <c r="E20" s="125"/>
       <c r="F20" s="126"/>
-      <c r="G20" s="197" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="198"/>
+      <c r="G20" s="273" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="274"/>
       <c r="I20" s="136"/>
       <c r="J20" s="137"/>
       <c r="K20" s="138"/>
@@ -20197,18 +20217,16 @@
       <c r="D21" s="121"/>
       <c r="E21" s="122"/>
       <c r="F21" s="123"/>
-      <c r="G21" s="195" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" s="196"/>
+      <c r="G21" s="271" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="272"/>
       <c r="I21" s="68"/>
       <c r="J21" s="69"/>
       <c r="K21" s="69"/>
       <c r="L21" s="76"/>
       <c r="M21" s="71"/>
-      <c r="N21" s="77" t="s">
-        <v>29</v>
-      </c>
+      <c r="N21" s="77"/>
     </row>
     <row r="22" spans="2:14" s="19" customFormat="1" ht="28" customHeight="1">
       <c r="B22" s="127"/>
@@ -20216,15 +20234,15 @@
       <c r="D22" s="121"/>
       <c r="E22" s="121"/>
       <c r="F22" s="128"/>
-      <c r="G22" s="199" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="200"/>
-      <c r="I22" s="201" t="s">
-        <v>138</v>
-      </c>
-      <c r="J22" s="202"/>
-      <c r="K22" s="203"/>
+      <c r="G22" s="275" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="276"/>
+      <c r="I22" s="277" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="278"/>
+      <c r="K22" s="279"/>
       <c r="L22" s="78"/>
       <c r="M22" s="79">
         <f>(SUM(M8,M17,M18,M19,M20,M21))</f>
@@ -20238,13 +20256,13 @@
       <c r="D23" s="121"/>
       <c r="E23" s="121"/>
       <c r="F23" s="128"/>
-      <c r="G23" s="204" t="s">
+      <c r="G23" s="280" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="205"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="202"/>
-      <c r="K23" s="203"/>
+      <c r="H23" s="281"/>
+      <c r="I23" s="277"/>
+      <c r="J23" s="278"/>
+      <c r="K23" s="279"/>
       <c r="L23" s="78"/>
       <c r="M23" s="79">
         <v>71075</v>
@@ -20257,13 +20275,13 @@
       <c r="D24" s="121"/>
       <c r="E24" s="121"/>
       <c r="F24" s="128"/>
-      <c r="G24" s="206" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" s="207"/>
-      <c r="I24" s="208"/>
-      <c r="J24" s="209"/>
-      <c r="K24" s="210"/>
+      <c r="G24" s="282" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="283"/>
+      <c r="I24" s="284"/>
+      <c r="J24" s="285"/>
+      <c r="K24" s="286"/>
       <c r="L24" s="82"/>
       <c r="M24" s="83">
         <f>M22-M23</f>
@@ -20277,13 +20295,13 @@
       <c r="D25" s="121"/>
       <c r="E25" s="121"/>
       <c r="F25" s="128"/>
-      <c r="G25" s="204" t="s">
-        <v>47</v>
-      </c>
-      <c r="H25" s="205"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="202"/>
-      <c r="K25" s="203"/>
+      <c r="G25" s="280" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="281"/>
+      <c r="I25" s="277"/>
+      <c r="J25" s="278"/>
+      <c r="K25" s="279"/>
       <c r="L25" s="78"/>
       <c r="M25" s="79" t="s">
         <v>27</v>
@@ -20296,13 +20314,13 @@
       <c r="D26" s="121"/>
       <c r="E26" s="121"/>
       <c r="F26" s="128"/>
-      <c r="G26" s="211" t="s">
+      <c r="G26" s="287" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="212"/>
-      <c r="I26" s="213"/>
-      <c r="J26" s="214"/>
-      <c r="K26" s="215"/>
+      <c r="H26" s="288"/>
+      <c r="I26" s="289"/>
+      <c r="J26" s="290"/>
+      <c r="K26" s="291"/>
       <c r="L26" s="85"/>
       <c r="M26" s="86">
         <f>M24</f>
@@ -20318,15 +20336,15 @@
       <c r="D27" s="130"/>
       <c r="E27" s="130"/>
       <c r="F27" s="131"/>
-      <c r="G27" s="216"/>
-      <c r="H27" s="217"/>
-      <c r="I27" s="222" t="s">
+      <c r="G27" s="292"/>
+      <c r="H27" s="293"/>
+      <c r="I27" s="298" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="222"/>
-      <c r="K27" s="222"/>
-      <c r="L27" s="222"/>
-      <c r="M27" s="222"/>
+      <c r="J27" s="298"/>
+      <c r="K27" s="298"/>
+      <c r="L27" s="298"/>
+      <c r="M27" s="298"/>
       <c r="N27" s="88"/>
     </row>
     <row r="28" spans="2:14" s="18" customFormat="1" ht="23" customHeight="1">
@@ -20335,15 +20353,15 @@
       <c r="D28" s="132"/>
       <c r="E28" s="132"/>
       <c r="F28" s="133"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="219"/>
-      <c r="I28" s="223" t="s">
+      <c r="G28" s="294"/>
+      <c r="H28" s="295"/>
+      <c r="I28" s="299" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="223"/>
-      <c r="K28" s="223"/>
-      <c r="L28" s="223"/>
-      <c r="M28" s="223"/>
+      <c r="J28" s="299"/>
+      <c r="K28" s="299"/>
+      <c r="L28" s="299"/>
+      <c r="M28" s="299"/>
       <c r="N28" s="89" t="s">
         <v>22</v>
       </c>
@@ -20354,15 +20372,15 @@
       <c r="D29" s="132"/>
       <c r="E29" s="132"/>
       <c r="F29" s="133"/>
-      <c r="G29" s="218"/>
-      <c r="H29" s="219"/>
-      <c r="I29" s="223" t="s">
+      <c r="G29" s="294"/>
+      <c r="H29" s="295"/>
+      <c r="I29" s="299" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="223"/>
-      <c r="K29" s="223"/>
-      <c r="L29" s="223"/>
-      <c r="M29" s="223"/>
+      <c r="J29" s="299"/>
+      <c r="K29" s="299"/>
+      <c r="L29" s="299"/>
+      <c r="M29" s="299"/>
       <c r="N29" s="89" t="s">
         <v>20</v>
       </c>
@@ -20373,15 +20391,15 @@
       <c r="D30" s="132"/>
       <c r="E30" s="132"/>
       <c r="F30" s="133"/>
-      <c r="G30" s="218"/>
-      <c r="H30" s="219"/>
-      <c r="I30" s="223" t="s">
+      <c r="G30" s="294"/>
+      <c r="H30" s="295"/>
+      <c r="I30" s="299" t="s">
         <v>19</v>
       </c>
-      <c r="J30" s="223"/>
-      <c r="K30" s="223"/>
-      <c r="L30" s="223"/>
-      <c r="M30" s="223"/>
+      <c r="J30" s="299"/>
+      <c r="K30" s="299"/>
+      <c r="L30" s="299"/>
+      <c r="M30" s="299"/>
       <c r="N30" s="89" t="s">
         <v>18</v>
       </c>
@@ -20392,15 +20410,15 @@
       <c r="D31" s="134"/>
       <c r="E31" s="134"/>
       <c r="F31" s="135"/>
-      <c r="G31" s="220"/>
-      <c r="H31" s="221"/>
-      <c r="I31" s="224" t="s">
+      <c r="G31" s="296"/>
+      <c r="H31" s="297"/>
+      <c r="I31" s="300" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="224"/>
-      <c r="K31" s="224"/>
-      <c r="L31" s="224"/>
-      <c r="M31" s="224"/>
+      <c r="J31" s="300"/>
+      <c r="K31" s="300"/>
+      <c r="L31" s="300"/>
+      <c r="M31" s="300"/>
       <c r="N31" s="90" t="s">
         <v>16</v>
       </c>
@@ -21050,99 +21068,99 @@
       <c r="C6" s="22"/>
     </row>
     <row r="7" spans="2:21" ht="4" customHeight="1">
-      <c r="B7" s="225" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="226"/>
-      <c r="P7" s="226"/>
-      <c r="Q7" s="226"/>
-      <c r="R7" s="226"/>
-      <c r="S7" s="226"/>
-      <c r="T7" s="226"/>
-      <c r="U7" s="226"/>
+      <c r="B7" s="154" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
+      <c r="I7" s="155"/>
+      <c r="J7" s="155"/>
+      <c r="K7" s="155"/>
+      <c r="L7" s="155"/>
+      <c r="M7" s="155"/>
+      <c r="N7" s="155"/>
+      <c r="O7" s="155"/>
+      <c r="P7" s="155"/>
+      <c r="Q7" s="155"/>
+      <c r="R7" s="155"/>
+      <c r="S7" s="155"/>
+      <c r="T7" s="155"/>
+      <c r="U7" s="155"/>
     </row>
     <row r="8" spans="2:21" ht="66" customHeight="1">
-      <c r="B8" s="227" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="227"/>
-      <c r="D8" s="227"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="227"/>
-      <c r="H8" s="227"/>
-      <c r="I8" s="227"/>
-      <c r="J8" s="227"/>
-      <c r="K8" s="227"/>
-      <c r="L8" s="227"/>
-      <c r="M8" s="227"/>
-      <c r="N8" s="227"/>
-      <c r="O8" s="227"/>
-      <c r="P8" s="227"/>
-      <c r="Q8" s="227"/>
-      <c r="R8" s="227"/>
-      <c r="S8" s="227"/>
-      <c r="T8" s="227"/>
-      <c r="U8" s="227"/>
+      <c r="B8" s="156" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="156"/>
+      <c r="J8" s="156"/>
+      <c r="K8" s="156"/>
+      <c r="L8" s="156"/>
+      <c r="M8" s="156"/>
+      <c r="N8" s="156"/>
+      <c r="O8" s="156"/>
+      <c r="P8" s="156"/>
+      <c r="Q8" s="156"/>
+      <c r="R8" s="156"/>
+      <c r="S8" s="156"/>
+      <c r="T8" s="156"/>
+      <c r="U8" s="156"/>
     </row>
     <row r="9" spans="2:21" ht="44" customHeight="1">
-      <c r="B9" s="228" t="str">
-        <f>갑지!K8</f>
+      <c r="B9" s="157" t="str">
+        <f>갑지!Q25</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="C9" s="228"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="228"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="228"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="228"/>
-      <c r="J9" s="228"/>
-      <c r="K9" s="228"/>
-      <c r="L9" s="228"/>
-      <c r="M9" s="228"/>
-      <c r="N9" s="228"/>
-      <c r="O9" s="228"/>
-      <c r="P9" s="228"/>
-      <c r="Q9" s="228"/>
-      <c r="R9" s="228"/>
-      <c r="S9" s="228"/>
-      <c r="T9" s="228"/>
-      <c r="U9" s="228"/>
+      <c r="C9" s="157"/>
+      <c r="D9" s="157"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="157"/>
+      <c r="G9" s="157"/>
+      <c r="H9" s="157"/>
+      <c r="I9" s="157"/>
+      <c r="J9" s="157"/>
+      <c r="K9" s="157"/>
+      <c r="L9" s="157"/>
+      <c r="M9" s="157"/>
+      <c r="N9" s="157"/>
+      <c r="O9" s="157"/>
+      <c r="P9" s="157"/>
+      <c r="Q9" s="157"/>
+      <c r="R9" s="157"/>
+      <c r="S9" s="157"/>
+      <c r="T9" s="157"/>
+      <c r="U9" s="157"/>
     </row>
     <row r="10" spans="2:21" ht="4" customHeight="1">
-      <c r="B10" s="229"/>
-      <c r="C10" s="230"/>
-      <c r="D10" s="230"/>
-      <c r="E10" s="230"/>
-      <c r="F10" s="230"/>
-      <c r="G10" s="230"/>
-      <c r="H10" s="230"/>
-      <c r="I10" s="230"/>
-      <c r="J10" s="230"/>
-      <c r="K10" s="230"/>
-      <c r="L10" s="230"/>
-      <c r="M10" s="230"/>
-      <c r="N10" s="230"/>
-      <c r="O10" s="230"/>
-      <c r="P10" s="230"/>
-      <c r="Q10" s="230"/>
-      <c r="R10" s="230"/>
-      <c r="S10" s="230"/>
-      <c r="T10" s="230"/>
-      <c r="U10" s="230"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="159"/>
+      <c r="H10" s="159"/>
+      <c r="I10" s="159"/>
+      <c r="J10" s="159"/>
+      <c r="K10" s="159"/>
+      <c r="L10" s="159"/>
+      <c r="M10" s="159"/>
+      <c r="N10" s="159"/>
+      <c r="O10" s="159"/>
+      <c r="P10" s="159"/>
+      <c r="Q10" s="159"/>
+      <c r="R10" s="159"/>
+      <c r="S10" s="159"/>
+      <c r="T10" s="159"/>
+      <c r="U10" s="159"/>
     </row>
     <row r="11" spans="2:21" ht="40" customHeight="1">
       <c r="B11" s="24"/>
@@ -21165,28 +21183,28 @@
       <c r="C15" s="24"/>
     </row>
     <row r="16" spans="2:21" ht="24">
-      <c r="B16" s="231" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="231"/>
-      <c r="D16" s="231"/>
-      <c r="E16" s="231"/>
-      <c r="F16" s="231"/>
-      <c r="G16" s="231"/>
-      <c r="H16" s="231"/>
-      <c r="I16" s="231"/>
-      <c r="J16" s="231"/>
-      <c r="K16" s="231"/>
-      <c r="L16" s="231"/>
-      <c r="M16" s="231"/>
-      <c r="N16" s="231"/>
-      <c r="O16" s="231"/>
-      <c r="P16" s="231"/>
-      <c r="Q16" s="231"/>
-      <c r="R16" s="231"/>
-      <c r="S16" s="231"/>
-      <c r="T16" s="231"/>
-      <c r="U16" s="231"/>
+      <c r="B16" s="160" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="160"/>
+      <c r="D16" s="160"/>
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="160"/>
+      <c r="K16" s="160"/>
+      <c r="L16" s="160"/>
+      <c r="M16" s="160"/>
+      <c r="N16" s="160"/>
+      <c r="O16" s="160"/>
+      <c r="P16" s="160"/>
+      <c r="Q16" s="160"/>
+      <c r="R16" s="160"/>
+      <c r="S16" s="160"/>
+      <c r="T16" s="160"/>
+      <c r="U16" s="160"/>
     </row>
     <row r="17" spans="2:21" ht="40" customHeight="1">
       <c r="B17" s="24"/>
@@ -21209,43 +21227,43 @@
       <c r="C21" s="24"/>
     </row>
     <row r="22" spans="2:21" ht="4" customHeight="1">
-      <c r="B22" s="232"/>
-      <c r="C22" s="232"/>
-      <c r="D22" s="232"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="232"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
-      <c r="K22" s="232"/>
-      <c r="L22" s="232"/>
-      <c r="M22" s="232"/>
-      <c r="N22" s="232"/>
-      <c r="O22" s="232"/>
-      <c r="P22" s="232"/>
-      <c r="Q22" s="232"/>
-      <c r="R22" s="232"/>
-      <c r="S22" s="232"/>
-      <c r="T22" s="232"/>
-      <c r="U22" s="232"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="161"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="161"/>
+      <c r="P22" s="161"/>
+      <c r="Q22" s="161"/>
+      <c r="R22" s="161"/>
+      <c r="S22" s="161"/>
+      <c r="T22" s="161"/>
+      <c r="U22" s="161"/>
     </row>
     <row r="23" spans="2:21" ht="53.25" customHeight="1">
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
-      <c r="I23" s="233" t="s">
-        <v>51</v>
-      </c>
-      <c r="J23" s="233"/>
-      <c r="K23" s="233"/>
-      <c r="L23" s="233"/>
-      <c r="M23" s="233"/>
-      <c r="N23" s="233"/>
-      <c r="O23" s="233"/>
-      <c r="P23" s="233"/>
-      <c r="Q23" s="233"/>
-      <c r="R23" s="233"/>
-      <c r="S23" s="233"/>
+      <c r="I23" s="162" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="162"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="162"/>
+      <c r="M23" s="162"/>
+      <c r="N23" s="162"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="162"/>
+      <c r="Q23" s="162"/>
+      <c r="R23" s="162"/>
+      <c r="S23" s="162"/>
       <c r="T23" s="26"/>
       <c r="U23" s="26"/>
     </row>
@@ -21253,40 +21271,40 @@
       <c r="D24" s="27"/>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
-      <c r="I24" s="234" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="234"/>
-      <c r="K24" s="234"/>
-      <c r="L24" s="234"/>
-      <c r="M24" s="234"/>
-      <c r="N24" s="234"/>
-      <c r="O24" s="234"/>
-      <c r="P24" s="234"/>
-      <c r="Q24" s="234"/>
-      <c r="R24" s="234"/>
-      <c r="S24" s="234"/>
-      <c r="T24" s="234"/>
+      <c r="I24" s="163" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" s="163"/>
+      <c r="K24" s="163"/>
+      <c r="L24" s="163"/>
+      <c r="M24" s="163"/>
+      <c r="N24" s="163"/>
+      <c r="O24" s="163"/>
+      <c r="P24" s="163"/>
+      <c r="Q24" s="163"/>
+      <c r="R24" s="163"/>
+      <c r="S24" s="163"/>
+      <c r="T24" s="163"/>
       <c r="U24" s="27"/>
     </row>
     <row r="25" spans="2:21" ht="24" customHeight="1">
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
-      <c r="I25" s="234" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="234"/>
-      <c r="K25" s="234"/>
-      <c r="L25" s="234"/>
-      <c r="M25" s="234"/>
-      <c r="N25" s="234"/>
-      <c r="O25" s="234"/>
-      <c r="P25" s="234"/>
-      <c r="Q25" s="234"/>
-      <c r="R25" s="234"/>
-      <c r="S25" s="234"/>
-      <c r="T25" s="234"/>
+      <c r="I25" s="163" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="163"/>
+      <c r="K25" s="163"/>
+      <c r="L25" s="163"/>
+      <c r="M25" s="163"/>
+      <c r="N25" s="163"/>
+      <c r="O25" s="163"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="163"/>
+      <c r="S25" s="163"/>
+      <c r="T25" s="163"/>
       <c r="U25" s="27"/>
     </row>
     <row r="26" spans="2:21" ht="24" customHeight="1">
@@ -21324,456 +21342,454 @@
       <c r="U27" s="28"/>
     </row>
     <row r="28" spans="2:21" ht="43.5" customHeight="1">
-      <c r="B28" s="235" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="236"/>
-      <c r="D28" s="236"/>
-      <c r="E28" s="236"/>
-      <c r="F28" s="236"/>
-      <c r="G28" s="236"/>
-      <c r="H28" s="236"/>
-      <c r="I28" s="236"/>
-      <c r="J28" s="236"/>
-      <c r="K28" s="236"/>
-      <c r="L28" s="236"/>
-      <c r="M28" s="236"/>
-      <c r="N28" s="236"/>
-      <c r="O28" s="236"/>
-      <c r="P28" s="236"/>
-      <c r="Q28" s="236"/>
-      <c r="R28" s="236"/>
-      <c r="S28" s="236"/>
-      <c r="T28" s="236"/>
-      <c r="U28" s="237"/>
+      <c r="B28" s="164" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="165"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="165"/>
+      <c r="F28" s="165"/>
+      <c r="G28" s="165"/>
+      <c r="H28" s="165"/>
+      <c r="I28" s="165"/>
+      <c r="J28" s="165"/>
+      <c r="K28" s="165"/>
+      <c r="L28" s="165"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="165"/>
+      <c r="O28" s="165"/>
+      <c r="P28" s="165"/>
+      <c r="Q28" s="165"/>
+      <c r="R28" s="165"/>
+      <c r="S28" s="165"/>
+      <c r="T28" s="165"/>
+      <c r="U28" s="166"/>
     </row>
     <row r="29" spans="2:21" ht="25" customHeight="1">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="167" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="168"/>
+      <c r="D29" s="171" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="239"/>
-      <c r="D29" s="242" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" s="242"/>
-      <c r="F29" s="242"/>
-      <c r="G29" s="243" t="str">
+      <c r="E29" s="171"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="172" t="str">
         <f>B9</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="H29" s="243"/>
-      <c r="I29" s="243"/>
-      <c r="J29" s="243"/>
-      <c r="K29" s="243"/>
-      <c r="L29" s="243"/>
-      <c r="M29" s="243"/>
-      <c r="N29" s="243"/>
-      <c r="O29" s="243"/>
-      <c r="P29" s="243"/>
-      <c r="Q29" s="243"/>
-      <c r="R29" s="243"/>
-      <c r="S29" s="243"/>
-      <c r="T29" s="243"/>
-      <c r="U29" s="244"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="172"/>
+      <c r="J29" s="172"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
+      <c r="O29" s="172"/>
+      <c r="P29" s="172"/>
+      <c r="Q29" s="172"/>
+      <c r="R29" s="172"/>
+      <c r="S29" s="172"/>
+      <c r="T29" s="172"/>
+      <c r="U29" s="173"/>
     </row>
     <row r="30" spans="2:21" ht="25" customHeight="1">
-      <c r="B30" s="240"/>
-      <c r="C30" s="241"/>
-      <c r="D30" s="245" t="s">
+      <c r="B30" s="169"/>
+      <c r="C30" s="170"/>
+      <c r="D30" s="174" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="174"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="175" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="175"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="175"/>
+      <c r="L30" s="175"/>
+      <c r="M30" s="175"/>
+      <c r="N30" s="175"/>
+      <c r="O30" s="175"/>
+      <c r="P30" s="175"/>
+      <c r="Q30" s="175"/>
+      <c r="R30" s="175"/>
+      <c r="S30" s="175"/>
+      <c r="T30" s="175"/>
+      <c r="U30" s="176"/>
+    </row>
+    <row r="31" spans="2:21" ht="25" customHeight="1">
+      <c r="B31" s="169"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="174"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="175" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="175"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="175"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="175"/>
+      <c r="Q31" s="175"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="175"/>
+      <c r="T31" s="175"/>
+      <c r="U31" s="176"/>
+    </row>
+    <row r="32" spans="2:21" ht="25" customHeight="1">
+      <c r="B32" s="169"/>
+      <c r="C32" s="170"/>
+      <c r="D32" s="174"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="175" t="s">
+        <v>165</v>
+      </c>
+      <c r="H32" s="175"/>
+      <c r="I32" s="175"/>
+      <c r="J32" s="175"/>
+      <c r="K32" s="175"/>
+      <c r="L32" s="175"/>
+      <c r="M32" s="175"/>
+      <c r="N32" s="175"/>
+      <c r="O32" s="175"/>
+      <c r="P32" s="175"/>
+      <c r="Q32" s="175"/>
+      <c r="R32" s="175"/>
+      <c r="S32" s="175"/>
+      <c r="T32" s="175"/>
+      <c r="U32" s="176"/>
+    </row>
+    <row r="33" spans="2:21" ht="25" customHeight="1">
+      <c r="B33" s="169"/>
+      <c r="C33" s="170"/>
+      <c r="D33" s="174"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="174"/>
+      <c r="G33" s="175" t="s">
+        <v>146</v>
+      </c>
+      <c r="H33" s="175"/>
+      <c r="I33" s="175"/>
+      <c r="J33" s="175"/>
+      <c r="K33" s="175"/>
+      <c r="L33" s="175"/>
+      <c r="M33" s="175"/>
+      <c r="N33" s="175"/>
+      <c r="O33" s="175"/>
+      <c r="P33" s="175"/>
+      <c r="Q33" s="175"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="175"/>
+      <c r="T33" s="175"/>
+      <c r="U33" s="176"/>
+    </row>
+    <row r="34" spans="2:21" ht="25" customHeight="1">
+      <c r="B34" s="169"/>
+      <c r="C34" s="170"/>
+      <c r="D34" s="174"/>
+      <c r="E34" s="174"/>
+      <c r="F34" s="174"/>
+      <c r="G34" s="177" t="s">
+        <v>147</v>
+      </c>
+      <c r="H34" s="177"/>
+      <c r="I34" s="177"/>
+      <c r="J34" s="177"/>
+      <c r="K34" s="177"/>
+      <c r="L34" s="177"/>
+      <c r="M34" s="177"/>
+      <c r="N34" s="177"/>
+      <c r="O34" s="177"/>
+      <c r="P34" s="177"/>
+      <c r="Q34" s="177"/>
+      <c r="R34" s="177"/>
+      <c r="S34" s="177"/>
+      <c r="T34" s="177"/>
+      <c r="U34" s="178"/>
+    </row>
+    <row r="35" spans="2:21" ht="25" customHeight="1">
+      <c r="B35" s="169" t="s">
         <v>56</v>
       </c>
-      <c r="E30" s="245"/>
-      <c r="F30" s="245"/>
-      <c r="G30" s="246" t="s">
-        <v>150</v>
-      </c>
-      <c r="H30" s="246"/>
-      <c r="I30" s="246"/>
-      <c r="J30" s="246"/>
-      <c r="K30" s="246"/>
-      <c r="L30" s="246"/>
-      <c r="M30" s="246"/>
-      <c r="N30" s="246"/>
-      <c r="O30" s="246"/>
-      <c r="P30" s="246"/>
-      <c r="Q30" s="246"/>
-      <c r="R30" s="246"/>
-      <c r="S30" s="246"/>
-      <c r="T30" s="246"/>
-      <c r="U30" s="247"/>
-    </row>
-    <row r="31" spans="2:21" ht="25" customHeight="1">
-      <c r="B31" s="240"/>
-      <c r="C31" s="241"/>
-      <c r="D31" s="245"/>
-      <c r="E31" s="245"/>
-      <c r="F31" s="245"/>
-      <c r="G31" s="246" t="s">
-        <v>151</v>
-      </c>
-      <c r="H31" s="246"/>
-      <c r="I31" s="246"/>
-      <c r="J31" s="246"/>
-      <c r="K31" s="246"/>
-      <c r="L31" s="246"/>
-      <c r="M31" s="246"/>
-      <c r="N31" s="246"/>
-      <c r="O31" s="246"/>
-      <c r="P31" s="246"/>
-      <c r="Q31" s="246"/>
-      <c r="R31" s="246"/>
-      <c r="S31" s="246"/>
-      <c r="T31" s="246"/>
-      <c r="U31" s="247"/>
-    </row>
-    <row r="32" spans="2:21" ht="25" customHeight="1">
-      <c r="B32" s="240"/>
-      <c r="C32" s="241"/>
-      <c r="D32" s="245"/>
-      <c r="E32" s="245"/>
-      <c r="F32" s="245"/>
-      <c r="G32" s="246" t="s">
-        <v>152</v>
-      </c>
-      <c r="H32" s="246"/>
-      <c r="I32" s="246"/>
-      <c r="J32" s="246"/>
-      <c r="K32" s="246"/>
-      <c r="L32" s="246"/>
-      <c r="M32" s="246"/>
-      <c r="N32" s="246"/>
-      <c r="O32" s="246"/>
-      <c r="P32" s="246"/>
-      <c r="Q32" s="246"/>
-      <c r="R32" s="246"/>
-      <c r="S32" s="246"/>
-      <c r="T32" s="246"/>
-      <c r="U32" s="247"/>
-    </row>
-    <row r="33" spans="2:21" ht="25" customHeight="1">
-      <c r="B33" s="240"/>
-      <c r="C33" s="241"/>
-      <c r="D33" s="245"/>
-      <c r="E33" s="245"/>
-      <c r="F33" s="245"/>
-      <c r="G33" s="246" t="s">
-        <v>153</v>
-      </c>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="246"/>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
-      <c r="M33" s="246"/>
-      <c r="N33" s="246"/>
-      <c r="O33" s="246"/>
-      <c r="P33" s="246"/>
-      <c r="Q33" s="246"/>
-      <c r="R33" s="246"/>
-      <c r="S33" s="246"/>
-      <c r="T33" s="246"/>
-      <c r="U33" s="247"/>
-    </row>
-    <row r="34" spans="2:21" ht="25" customHeight="1">
-      <c r="B34" s="240"/>
-      <c r="C34" s="241"/>
-      <c r="D34" s="245"/>
-      <c r="E34" s="245"/>
-      <c r="F34" s="245"/>
-      <c r="G34" s="248" t="s">
-        <v>154</v>
-      </c>
-      <c r="H34" s="248"/>
-      <c r="I34" s="248"/>
-      <c r="J34" s="248"/>
-      <c r="K34" s="248"/>
-      <c r="L34" s="248"/>
-      <c r="M34" s="248"/>
-      <c r="N34" s="248"/>
-      <c r="O34" s="248"/>
-      <c r="P34" s="248"/>
-      <c r="Q34" s="248"/>
-      <c r="R34" s="248"/>
-      <c r="S34" s="248"/>
-      <c r="T34" s="248"/>
-      <c r="U34" s="249"/>
-    </row>
-    <row r="35" spans="2:21" ht="25" customHeight="1">
-      <c r="B35" s="240" t="s">
+      <c r="C35" s="170"/>
+      <c r="D35" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="241"/>
-      <c r="D35" s="245" t="s">
+      <c r="E35" s="174"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="183" t="str">
+        <f>G29&amp;" 장기수선계획 조정"</f>
+        <v>마곡엠밸리4단지아파트 장기수선계획 조정</v>
+      </c>
+      <c r="H35" s="184"/>
+      <c r="I35" s="184"/>
+      <c r="J35" s="184"/>
+      <c r="K35" s="184"/>
+      <c r="L35" s="184"/>
+      <c r="M35" s="184"/>
+      <c r="N35" s="184"/>
+      <c r="O35" s="184"/>
+      <c r="P35" s="184"/>
+      <c r="Q35" s="184"/>
+      <c r="R35" s="184"/>
+      <c r="S35" s="184"/>
+      <c r="T35" s="184"/>
+      <c r="U35" s="185"/>
+    </row>
+    <row r="36" spans="2:21" ht="25" customHeight="1">
+      <c r="B36" s="169"/>
+      <c r="C36" s="170"/>
+      <c r="D36" s="174" t="s">
         <v>58</v>
       </c>
-      <c r="E35" s="245"/>
-      <c r="F35" s="245"/>
-      <c r="G35" s="254" t="str">
-        <f>G29</f>
-        <v>마곡엠밸리4단지아파트</v>
-      </c>
-      <c r="H35" s="255"/>
-      <c r="I35" s="255"/>
-      <c r="J35" s="255"/>
-      <c r="K35" s="255"/>
-      <c r="L35" s="255"/>
-      <c r="M35" s="255" t="s">
-        <v>104</v>
-      </c>
-      <c r="N35" s="255"/>
-      <c r="O35" s="255"/>
-      <c r="P35" s="255"/>
-      <c r="Q35" s="255"/>
-      <c r="R35" s="255"/>
-      <c r="S35" s="255"/>
-      <c r="T35" s="255"/>
-      <c r="U35" s="256"/>
-    </row>
-    <row r="36" spans="2:21" ht="25" customHeight="1">
-      <c r="B36" s="240"/>
-      <c r="C36" s="241"/>
-      <c r="D36" s="245" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
-      <c r="G36" s="257" t="str">
+      <c r="E36" s="174"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="304" t="str">
         <f>대가산출!I3</f>
         <v>일금육십만원정 (₩600,000) - VAT별도</v>
       </c>
-      <c r="H36" s="257"/>
-      <c r="I36" s="257"/>
-      <c r="J36" s="257"/>
-      <c r="K36" s="257"/>
-      <c r="L36" s="257"/>
-      <c r="M36" s="257"/>
-      <c r="N36" s="257"/>
-      <c r="O36" s="257"/>
-      <c r="P36" s="257"/>
-      <c r="Q36" s="257"/>
-      <c r="R36" s="257"/>
-      <c r="S36" s="257"/>
-      <c r="T36" s="257"/>
-      <c r="U36" s="258"/>
+      <c r="H36" s="304"/>
+      <c r="I36" s="304"/>
+      <c r="J36" s="304"/>
+      <c r="K36" s="304"/>
+      <c r="L36" s="304"/>
+      <c r="M36" s="304"/>
+      <c r="N36" s="304"/>
+      <c r="O36" s="304"/>
+      <c r="P36" s="304"/>
+      <c r="Q36" s="304"/>
+      <c r="R36" s="304"/>
+      <c r="S36" s="304"/>
+      <c r="T36" s="304"/>
+      <c r="U36" s="305"/>
     </row>
     <row r="37" spans="2:21" ht="25" customHeight="1">
-      <c r="B37" s="240"/>
-      <c r="C37" s="241"/>
-      <c r="D37" s="245" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" s="245"/>
-      <c r="F37" s="245"/>
-      <c r="G37" s="259" t="str">
+      <c r="B37" s="169"/>
+      <c r="C37" s="170"/>
+      <c r="D37" s="174" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="174"/>
+      <c r="F37" s="174"/>
+      <c r="G37" s="306" t="str">
         <f>대가산출!I3</f>
         <v>일금육십만원정 (₩600,000) - VAT별도</v>
       </c>
-      <c r="H37" s="259"/>
-      <c r="I37" s="259"/>
-      <c r="J37" s="259"/>
-      <c r="K37" s="259"/>
-      <c r="L37" s="259"/>
-      <c r="M37" s="259"/>
-      <c r="N37" s="259"/>
-      <c r="O37" s="259"/>
-      <c r="P37" s="259"/>
-      <c r="Q37" s="259"/>
-      <c r="R37" s="259"/>
-      <c r="S37" s="259"/>
-      <c r="T37" s="259"/>
-      <c r="U37" s="260"/>
+      <c r="H37" s="306"/>
+      <c r="I37" s="306"/>
+      <c r="J37" s="306"/>
+      <c r="K37" s="306"/>
+      <c r="L37" s="306"/>
+      <c r="M37" s="306"/>
+      <c r="N37" s="306"/>
+      <c r="O37" s="306"/>
+      <c r="P37" s="306"/>
+      <c r="Q37" s="306"/>
+      <c r="R37" s="306"/>
+      <c r="S37" s="306"/>
+      <c r="T37" s="306"/>
+      <c r="U37" s="307"/>
     </row>
     <row r="38" spans="2:21" ht="25" customHeight="1">
-      <c r="B38" s="240"/>
-      <c r="C38" s="241"/>
-      <c r="D38" s="245" t="s">
+      <c r="B38" s="169"/>
+      <c r="C38" s="170"/>
+      <c r="D38" s="174" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="174"/>
+      <c r="F38" s="174"/>
+      <c r="G38" s="186" t="s">
+        <v>166</v>
+      </c>
+      <c r="H38" s="186"/>
+      <c r="I38" s="186"/>
+      <c r="J38" s="186"/>
+      <c r="K38" s="186"/>
+      <c r="L38" s="186"/>
+      <c r="M38" s="186"/>
+      <c r="N38" s="186"/>
+      <c r="O38" s="186"/>
+      <c r="P38" s="186"/>
+      <c r="Q38" s="186"/>
+      <c r="R38" s="186"/>
+      <c r="S38" s="186"/>
+      <c r="T38" s="186"/>
+      <c r="U38" s="187"/>
+    </row>
+    <row r="39" spans="2:21" ht="25" customHeight="1">
+      <c r="B39" s="169"/>
+      <c r="C39" s="170"/>
+      <c r="D39" s="174" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="174"/>
+      <c r="F39" s="174"/>
+      <c r="G39" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="245"/>
-      <c r="F38" s="245"/>
-      <c r="G38" s="257" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38" s="257"/>
-      <c r="I38" s="257"/>
-      <c r="J38" s="257"/>
-      <c r="K38" s="257"/>
-      <c r="L38" s="257"/>
-      <c r="M38" s="257"/>
-      <c r="N38" s="257"/>
-      <c r="O38" s="257"/>
-      <c r="P38" s="257"/>
-      <c r="Q38" s="257"/>
-      <c r="R38" s="257"/>
-      <c r="S38" s="257"/>
-      <c r="T38" s="257"/>
-      <c r="U38" s="258"/>
-    </row>
-    <row r="39" spans="2:21" ht="25" customHeight="1">
-      <c r="B39" s="240"/>
-      <c r="C39" s="241"/>
-      <c r="D39" s="245" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="245"/>
-      <c r="F39" s="245"/>
-      <c r="G39" s="257" t="s">
-        <v>63</v>
-      </c>
-      <c r="H39" s="257"/>
-      <c r="I39" s="257"/>
-      <c r="J39" s="257"/>
-      <c r="K39" s="257"/>
-      <c r="L39" s="257"/>
-      <c r="M39" s="257"/>
-      <c r="N39" s="257"/>
-      <c r="O39" s="257"/>
-      <c r="P39" s="257"/>
-      <c r="Q39" s="257"/>
-      <c r="R39" s="257"/>
-      <c r="S39" s="257"/>
-      <c r="T39" s="257"/>
-      <c r="U39" s="258"/>
+      <c r="H39" s="186"/>
+      <c r="I39" s="186"/>
+      <c r="J39" s="186"/>
+      <c r="K39" s="186"/>
+      <c r="L39" s="186"/>
+      <c r="M39" s="186"/>
+      <c r="N39" s="186"/>
+      <c r="O39" s="186"/>
+      <c r="P39" s="186"/>
+      <c r="Q39" s="186"/>
+      <c r="R39" s="186"/>
+      <c r="S39" s="186"/>
+      <c r="T39" s="186"/>
+      <c r="U39" s="187"/>
     </row>
     <row r="40" spans="2:21" ht="25" customHeight="1">
-      <c r="B40" s="240"/>
-      <c r="C40" s="241"/>
-      <c r="D40" s="245" t="s">
-        <v>106</v>
-      </c>
-      <c r="E40" s="245"/>
-      <c r="F40" s="245"/>
-      <c r="G40" s="257" t="str">
+      <c r="B40" s="169"/>
+      <c r="C40" s="170"/>
+      <c r="D40" s="174" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="174"/>
+      <c r="F40" s="174"/>
+      <c r="G40" s="186" t="str">
         <f>갑지!Q26</f>
         <v>서울 성북구 길음로9길 50 (길음동)</v>
       </c>
-      <c r="H40" s="257"/>
-      <c r="I40" s="257"/>
-      <c r="J40" s="257"/>
-      <c r="K40" s="257"/>
-      <c r="L40" s="257"/>
-      <c r="M40" s="257"/>
-      <c r="N40" s="257"/>
-      <c r="O40" s="257"/>
-      <c r="P40" s="257"/>
-      <c r="Q40" s="257"/>
-      <c r="R40" s="257"/>
-      <c r="S40" s="257"/>
-      <c r="T40" s="257"/>
-      <c r="U40" s="258"/>
+      <c r="H40" s="186"/>
+      <c r="I40" s="186"/>
+      <c r="J40" s="186"/>
+      <c r="K40" s="186"/>
+      <c r="L40" s="186"/>
+      <c r="M40" s="186"/>
+      <c r="N40" s="186"/>
+      <c r="O40" s="186"/>
+      <c r="P40" s="186"/>
+      <c r="Q40" s="186"/>
+      <c r="R40" s="186"/>
+      <c r="S40" s="186"/>
+      <c r="T40" s="186"/>
+      <c r="U40" s="187"/>
     </row>
     <row r="41" spans="2:21" ht="25" customHeight="1">
-      <c r="B41" s="240"/>
-      <c r="C41" s="241"/>
-      <c r="D41" s="245"/>
-      <c r="E41" s="245"/>
-      <c r="F41" s="245"/>
-      <c r="G41" s="261" t="s">
-        <v>144</v>
-      </c>
-      <c r="H41" s="262"/>
-      <c r="I41" s="262" t="s">
-        <v>141</v>
-      </c>
-      <c r="J41" s="262"/>
-      <c r="K41" s="262"/>
-      <c r="L41" s="262"/>
-      <c r="M41" s="262"/>
+      <c r="B41" s="169"/>
+      <c r="C41" s="170"/>
+      <c r="D41" s="174"/>
+      <c r="E41" s="174"/>
+      <c r="F41" s="174"/>
+      <c r="G41" s="188" t="s">
+        <v>140</v>
+      </c>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
+      <c r="L41" s="189"/>
+      <c r="M41" s="189"/>
       <c r="N41" s="153" t="s">
         <v>13</v>
       </c>
-      <c r="O41" s="262" t="s">
-        <v>142</v>
-      </c>
-      <c r="P41" s="262"/>
-      <c r="Q41" s="262" t="s">
-        <v>143</v>
-      </c>
-      <c r="R41" s="262"/>
-      <c r="S41" s="262"/>
-      <c r="T41" s="262"/>
-      <c r="U41" s="263"/>
+      <c r="O41" s="189" t="s">
+        <v>138</v>
+      </c>
+      <c r="P41" s="189"/>
+      <c r="Q41" s="189" t="s">
+        <v>139</v>
+      </c>
+      <c r="R41" s="189"/>
+      <c r="S41" s="189"/>
+      <c r="T41" s="189"/>
+      <c r="U41" s="190"/>
     </row>
     <row r="42" spans="2:21" ht="25" customHeight="1">
-      <c r="B42" s="250"/>
-      <c r="C42" s="251"/>
-      <c r="D42" s="264" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="265"/>
-      <c r="F42" s="266"/>
-      <c r="G42" s="254" t="s">
-        <v>70</v>
-      </c>
-      <c r="H42" s="255"/>
-      <c r="I42" s="255"/>
-      <c r="J42" s="255"/>
-      <c r="K42" s="255"/>
-      <c r="L42" s="255"/>
-      <c r="M42" s="255"/>
-      <c r="N42" s="255"/>
-      <c r="O42" s="255"/>
-      <c r="P42" s="255"/>
-      <c r="Q42" s="255"/>
-      <c r="R42" s="255"/>
-      <c r="S42" s="255"/>
-      <c r="T42" s="255"/>
-      <c r="U42" s="256"/>
+      <c r="B42" s="179"/>
+      <c r="C42" s="180"/>
+      <c r="D42" s="191" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="192"/>
+      <c r="F42" s="193"/>
+      <c r="G42" s="183" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="184"/>
+      <c r="I42" s="184"/>
+      <c r="J42" s="184"/>
+      <c r="K42" s="184"/>
+      <c r="L42" s="184"/>
+      <c r="M42" s="184"/>
+      <c r="N42" s="184"/>
+      <c r="O42" s="184"/>
+      <c r="P42" s="184"/>
+      <c r="Q42" s="184"/>
+      <c r="R42" s="184"/>
+      <c r="S42" s="184"/>
+      <c r="T42" s="184"/>
+      <c r="U42" s="185"/>
     </row>
     <row r="43" spans="2:21" ht="25" customHeight="1">
-      <c r="B43" s="252"/>
-      <c r="C43" s="253"/>
-      <c r="D43" s="267" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="267"/>
-      <c r="F43" s="267"/>
-      <c r="G43" s="268"/>
-      <c r="H43" s="268"/>
-      <c r="I43" s="268"/>
-      <c r="J43" s="268"/>
-      <c r="K43" s="268"/>
-      <c r="L43" s="268"/>
-      <c r="M43" s="268"/>
-      <c r="N43" s="268"/>
-      <c r="O43" s="268"/>
-      <c r="P43" s="268"/>
-      <c r="Q43" s="268"/>
-      <c r="R43" s="268"/>
-      <c r="S43" s="268"/>
-      <c r="T43" s="268"/>
-      <c r="U43" s="269"/>
+      <c r="B43" s="181"/>
+      <c r="C43" s="182"/>
+      <c r="D43" s="194" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="194"/>
+      <c r="F43" s="194"/>
+      <c r="G43" s="195"/>
+      <c r="H43" s="195"/>
+      <c r="I43" s="195"/>
+      <c r="J43" s="195"/>
+      <c r="K43" s="195"/>
+      <c r="L43" s="195"/>
+      <c r="M43" s="195"/>
+      <c r="N43" s="195"/>
+      <c r="O43" s="195"/>
+      <c r="P43" s="195"/>
+      <c r="Q43" s="195"/>
+      <c r="R43" s="195"/>
+      <c r="S43" s="195"/>
+      <c r="T43" s="195"/>
+      <c r="U43" s="196"/>
     </row>
     <row r="44" spans="2:21">
-      <c r="B44" s="270"/>
-      <c r="C44" s="271"/>
-      <c r="D44" s="271"/>
-      <c r="E44" s="271"/>
+      <c r="B44" s="197"/>
+      <c r="C44" s="198"/>
+      <c r="D44" s="198"/>
+      <c r="E44" s="198"/>
       <c r="U44" s="29"/>
     </row>
     <row r="45" spans="2:21" ht="67.5" customHeight="1">
-      <c r="B45" s="272" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="273"/>
-      <c r="D45" s="273"/>
-      <c r="E45" s="273"/>
-      <c r="F45" s="273"/>
-      <c r="G45" s="273"/>
-      <c r="H45" s="273"/>
-      <c r="I45" s="273"/>
-      <c r="J45" s="273"/>
-      <c r="K45" s="273"/>
-      <c r="L45" s="273"/>
-      <c r="M45" s="273"/>
-      <c r="N45" s="273"/>
-      <c r="O45" s="273"/>
-      <c r="P45" s="273"/>
-      <c r="Q45" s="273"/>
-      <c r="R45" s="273"/>
-      <c r="S45" s="273"/>
-      <c r="T45" s="273"/>
-      <c r="U45" s="274"/>
+      <c r="B45" s="199" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="200"/>
+      <c r="D45" s="200"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="200"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="200"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="200"/>
+      <c r="L45" s="200"/>
+      <c r="M45" s="200"/>
+      <c r="N45" s="200"/>
+      <c r="O45" s="200"/>
+      <c r="P45" s="200"/>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="200"/>
+      <c r="S45" s="200"/>
+      <c r="T45" s="200"/>
+      <c r="U45" s="201"/>
     </row>
     <row r="46" spans="2:21">
       <c r="B46" s="30"/>
@@ -21783,275 +21799,275 @@
       <c r="U46" s="29"/>
     </row>
     <row r="47" spans="2:21" ht="25" customHeight="1">
-      <c r="B47" s="275" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="276"/>
-      <c r="D47" s="276"/>
-      <c r="E47" s="276"/>
-      <c r="F47" s="276"/>
-      <c r="G47" s="273" t="s">
-        <v>96</v>
-      </c>
-      <c r="H47" s="273"/>
-      <c r="I47" s="273"/>
-      <c r="J47" s="273"/>
-      <c r="K47" s="273"/>
-      <c r="L47" s="273"/>
-      <c r="M47" s="273"/>
-      <c r="N47" s="273"/>
-      <c r="O47" s="273"/>
-      <c r="P47" s="273"/>
-      <c r="Q47" s="273"/>
-      <c r="R47" s="273"/>
-      <c r="S47" s="273"/>
-      <c r="T47" s="273"/>
-      <c r="U47" s="274"/>
+      <c r="B47" s="202" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="203"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="203"/>
+      <c r="F47" s="203"/>
+      <c r="G47" s="200" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47" s="200"/>
+      <c r="I47" s="200"/>
+      <c r="J47" s="200"/>
+      <c r="K47" s="200"/>
+      <c r="L47" s="200"/>
+      <c r="M47" s="200"/>
+      <c r="N47" s="200"/>
+      <c r="O47" s="200"/>
+      <c r="P47" s="200"/>
+      <c r="Q47" s="200"/>
+      <c r="R47" s="200"/>
+      <c r="S47" s="200"/>
+      <c r="T47" s="200"/>
+      <c r="U47" s="201"/>
     </row>
     <row r="48" spans="2:21" ht="25" customHeight="1">
       <c r="B48" s="32"/>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="273"/>
-      <c r="S48" s="273"/>
-      <c r="T48" s="273"/>
-      <c r="U48" s="274"/>
+      <c r="E48" s="200"/>
+      <c r="F48" s="200"/>
+      <c r="G48" s="200"/>
+      <c r="H48" s="200"/>
+      <c r="I48" s="200"/>
+      <c r="J48" s="200"/>
+      <c r="K48" s="200"/>
+      <c r="L48" s="200"/>
+      <c r="M48" s="200"/>
+      <c r="N48" s="200"/>
+      <c r="O48" s="200"/>
+      <c r="P48" s="200"/>
+      <c r="Q48" s="200"/>
+      <c r="R48" s="200"/>
+      <c r="S48" s="200"/>
+      <c r="T48" s="200"/>
+      <c r="U48" s="201"/>
     </row>
     <row r="49" spans="2:21" ht="25" customHeight="1">
       <c r="B49" s="32"/>
       <c r="C49" s="27"/>
       <c r="D49" s="27"/>
-      <c r="E49" s="273"/>
-      <c r="F49" s="273"/>
-      <c r="G49" s="273"/>
-      <c r="H49" s="273"/>
-      <c r="I49" s="273"/>
-      <c r="J49" s="273"/>
-      <c r="K49" s="273"/>
-      <c r="L49" s="273"/>
-      <c r="M49" s="273"/>
-      <c r="N49" s="273"/>
-      <c r="O49" s="273"/>
-      <c r="P49" s="273"/>
-      <c r="Q49" s="273"/>
-      <c r="R49" s="273"/>
-      <c r="S49" s="273"/>
-      <c r="T49" s="273"/>
-      <c r="U49" s="274"/>
+      <c r="E49" s="200"/>
+      <c r="F49" s="200"/>
+      <c r="G49" s="200"/>
+      <c r="H49" s="200"/>
+      <c r="I49" s="200"/>
+      <c r="J49" s="200"/>
+      <c r="K49" s="200"/>
+      <c r="L49" s="200"/>
+      <c r="M49" s="200"/>
+      <c r="N49" s="200"/>
+      <c r="O49" s="200"/>
+      <c r="P49" s="200"/>
+      <c r="Q49" s="200"/>
+      <c r="R49" s="200"/>
+      <c r="S49" s="200"/>
+      <c r="T49" s="200"/>
+      <c r="U49" s="201"/>
     </row>
     <row r="50" spans="2:21">
-      <c r="B50" s="270"/>
-      <c r="C50" s="271"/>
-      <c r="D50" s="271"/>
-      <c r="E50" s="271"/>
+      <c r="B50" s="197"/>
+      <c r="C50" s="198"/>
+      <c r="D50" s="198"/>
+      <c r="E50" s="198"/>
       <c r="U50" s="29"/>
     </row>
     <row r="51" spans="2:21" ht="25" customHeight="1">
-      <c r="B51" s="277" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" s="278"/>
-      <c r="D51" s="278"/>
-      <c r="E51" s="278"/>
-      <c r="F51" s="278"/>
-      <c r="G51" s="279" t="s">
+      <c r="B51" s="204" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="205"/>
+      <c r="D51" s="205"/>
+      <c r="E51" s="205"/>
+      <c r="F51" s="205"/>
+      <c r="G51" s="206" t="s">
+        <v>104</v>
+      </c>
+      <c r="H51" s="206"/>
+      <c r="I51" s="206"/>
+      <c r="J51" s="206"/>
+      <c r="K51" s="206"/>
+      <c r="L51" s="206"/>
+      <c r="M51" s="206"/>
+      <c r="N51" s="206"/>
+      <c r="O51" s="206"/>
+      <c r="P51" s="206"/>
+      <c r="Q51" s="206"/>
+      <c r="R51" s="206"/>
+      <c r="S51" s="206"/>
+      <c r="T51" s="206"/>
+      <c r="U51" s="207"/>
+    </row>
+    <row r="52" spans="2:21" ht="40.5" customHeight="1">
+      <c r="B52" s="208" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="209"/>
+      <c r="D52" s="209"/>
+      <c r="E52" s="209"/>
+      <c r="F52" s="209"/>
+      <c r="G52" s="209"/>
+      <c r="H52" s="209"/>
+      <c r="I52" s="209"/>
+      <c r="J52" s="209"/>
+      <c r="K52" s="209"/>
+      <c r="L52" s="209" t="s">
+        <v>106</v>
+      </c>
+      <c r="M52" s="209"/>
+      <c r="N52" s="209"/>
+      <c r="O52" s="209"/>
+      <c r="P52" s="209"/>
+      <c r="Q52" s="209"/>
+      <c r="R52" s="209"/>
+      <c r="S52" s="209"/>
+      <c r="T52" s="209"/>
+      <c r="U52" s="210"/>
+    </row>
+    <row r="53" spans="2:21" ht="40.5" customHeight="1">
+      <c r="B53" s="211" t="s">
         <v>107</v>
       </c>
-      <c r="H51" s="279"/>
-      <c r="I51" s="279"/>
-      <c r="J51" s="279"/>
-      <c r="K51" s="279"/>
-      <c r="L51" s="279"/>
-      <c r="M51" s="279"/>
-      <c r="N51" s="279"/>
-      <c r="O51" s="279"/>
-      <c r="P51" s="279"/>
-      <c r="Q51" s="279"/>
-      <c r="R51" s="279"/>
-      <c r="S51" s="279"/>
-      <c r="T51" s="279"/>
-      <c r="U51" s="280"/>
-    </row>
-    <row r="52" spans="2:21" ht="40.5" customHeight="1">
-      <c r="B52" s="281" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="282"/>
-      <c r="D52" s="282"/>
-      <c r="E52" s="282"/>
-      <c r="F52" s="282"/>
-      <c r="G52" s="282"/>
-      <c r="H52" s="282"/>
-      <c r="I52" s="282"/>
-      <c r="J52" s="282"/>
-      <c r="K52" s="282"/>
-      <c r="L52" s="282" t="s">
-        <v>109</v>
-      </c>
-      <c r="M52" s="282"/>
-      <c r="N52" s="282"/>
-      <c r="O52" s="282"/>
-      <c r="P52" s="282"/>
-      <c r="Q52" s="282"/>
-      <c r="R52" s="282"/>
-      <c r="S52" s="282"/>
-      <c r="T52" s="282"/>
-      <c r="U52" s="283"/>
-    </row>
-    <row r="53" spans="2:21" ht="40.5" customHeight="1">
-      <c r="B53" s="284" t="s">
-        <v>110</v>
-      </c>
-      <c r="C53" s="285"/>
-      <c r="D53" s="285"/>
-      <c r="E53" s="286"/>
-      <c r="F53" s="287" t="str">
+      <c r="C53" s="212"/>
+      <c r="D53" s="212"/>
+      <c r="E53" s="213"/>
+      <c r="F53" s="310" t="str">
         <f>G29</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="G53" s="288"/>
-      <c r="H53" s="288"/>
-      <c r="I53" s="288"/>
-      <c r="J53" s="288"/>
-      <c r="K53" s="289"/>
-      <c r="L53" s="290" t="s">
-        <v>111</v>
-      </c>
-      <c r="M53" s="291"/>
-      <c r="N53" s="291"/>
-      <c r="O53" s="292"/>
-      <c r="P53" s="293" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q53" s="294"/>
-      <c r="R53" s="294"/>
-      <c r="S53" s="294"/>
-      <c r="T53" s="294"/>
-      <c r="U53" s="295"/>
+      <c r="G53" s="311"/>
+      <c r="H53" s="311"/>
+      <c r="I53" s="311"/>
+      <c r="J53" s="311"/>
+      <c r="K53" s="312"/>
+      <c r="L53" s="214" t="s">
+        <v>108</v>
+      </c>
+      <c r="M53" s="215"/>
+      <c r="N53" s="215"/>
+      <c r="O53" s="216"/>
+      <c r="P53" s="217" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q53" s="218"/>
+      <c r="R53" s="218"/>
+      <c r="S53" s="218"/>
+      <c r="T53" s="218"/>
+      <c r="U53" s="219"/>
     </row>
     <row r="54" spans="2:21" ht="40.5" customHeight="1">
-      <c r="B54" s="296" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="291"/>
-      <c r="D54" s="291"/>
-      <c r="E54" s="292"/>
-      <c r="F54" s="297" t="str">
+      <c r="B54" s="220" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="215"/>
+      <c r="D54" s="215"/>
+      <c r="E54" s="216"/>
+      <c r="F54" s="221" t="str">
         <f>G40</f>
         <v>서울 성북구 길음로9길 50 (길음동)</v>
       </c>
-      <c r="G54" s="298"/>
-      <c r="H54" s="298"/>
-      <c r="I54" s="298"/>
-      <c r="J54" s="298"/>
-      <c r="K54" s="299"/>
-      <c r="L54" s="290" t="s">
-        <v>114</v>
-      </c>
-      <c r="M54" s="291"/>
-      <c r="N54" s="291"/>
-      <c r="O54" s="292"/>
-      <c r="P54" s="300" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q54" s="294"/>
-      <c r="R54" s="294"/>
-      <c r="S54" s="294"/>
-      <c r="T54" s="294"/>
-      <c r="U54" s="295"/>
+      <c r="G54" s="222"/>
+      <c r="H54" s="222"/>
+      <c r="I54" s="222"/>
+      <c r="J54" s="222"/>
+      <c r="K54" s="223"/>
+      <c r="L54" s="214" t="s">
+        <v>111</v>
+      </c>
+      <c r="M54" s="215"/>
+      <c r="N54" s="215"/>
+      <c r="O54" s="216"/>
+      <c r="P54" s="224" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q54" s="218"/>
+      <c r="R54" s="218"/>
+      <c r="S54" s="218"/>
+      <c r="T54" s="218"/>
+      <c r="U54" s="219"/>
     </row>
     <row r="55" spans="2:21" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B55" s="301" t="s">
+      <c r="B55" s="225" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="226"/>
+      <c r="D55" s="226"/>
+      <c r="E55" s="226"/>
+      <c r="F55" s="227"/>
+      <c r="G55" s="226"/>
+      <c r="H55" s="226"/>
+      <c r="I55" s="226"/>
+      <c r="J55" s="226"/>
+      <c r="K55" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="L55" s="227" t="s">
+        <v>112</v>
+      </c>
+      <c r="M55" s="226"/>
+      <c r="N55" s="226"/>
+      <c r="O55" s="228"/>
+      <c r="P55" s="227" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="302"/>
-      <c r="D55" s="302"/>
-      <c r="E55" s="302"/>
-      <c r="F55" s="302"/>
-      <c r="G55" s="302"/>
-      <c r="H55" s="302"/>
-      <c r="I55" s="302"/>
-      <c r="J55" s="302"/>
-      <c r="K55" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="L55" s="303" t="s">
-        <v>115</v>
-      </c>
-      <c r="M55" s="302"/>
-      <c r="N55" s="302"/>
-      <c r="O55" s="304"/>
-      <c r="P55" s="303" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q55" s="302"/>
-      <c r="R55" s="302"/>
-      <c r="S55" s="302"/>
-      <c r="T55" s="302"/>
+      <c r="Q55" s="226"/>
+      <c r="R55" s="226"/>
+      <c r="S55" s="226"/>
+      <c r="T55" s="226"/>
       <c r="U55" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="2:21" ht="16">
-      <c r="B56" s="305" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" s="305"/>
-      <c r="D56" s="305"/>
-      <c r="E56" s="305"/>
-      <c r="F56" s="305"/>
-      <c r="G56" s="305"/>
-      <c r="H56" s="305"/>
-      <c r="I56" s="305"/>
-      <c r="J56" s="305"/>
-      <c r="K56" s="305"/>
-      <c r="L56" s="305"/>
-      <c r="M56" s="305"/>
-      <c r="N56" s="305"/>
-      <c r="O56" s="305"/>
-      <c r="P56" s="305"/>
-      <c r="Q56" s="305"/>
-      <c r="R56" s="305"/>
-      <c r="S56" s="305"/>
-      <c r="T56" s="305"/>
-      <c r="U56" s="305"/>
+      <c r="B56" s="229" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="229"/>
+      <c r="D56" s="229"/>
+      <c r="E56" s="229"/>
+      <c r="F56" s="229"/>
+      <c r="G56" s="229"/>
+      <c r="H56" s="229"/>
+      <c r="I56" s="229"/>
+      <c r="J56" s="229"/>
+      <c r="K56" s="229"/>
+      <c r="L56" s="229"/>
+      <c r="M56" s="229"/>
+      <c r="N56" s="229"/>
+      <c r="O56" s="229"/>
+      <c r="P56" s="229"/>
+      <c r="Q56" s="229"/>
+      <c r="R56" s="229"/>
+      <c r="S56" s="229"/>
+      <c r="T56" s="229"/>
+      <c r="U56" s="229"/>
     </row>
     <row r="57" spans="2:21" ht="26">
-      <c r="B57" s="306" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" s="306"/>
-      <c r="D57" s="306"/>
-      <c r="E57" s="306"/>
-      <c r="F57" s="306"/>
-      <c r="G57" s="306"/>
-      <c r="H57" s="306"/>
-      <c r="I57" s="306"/>
-      <c r="J57" s="306"/>
-      <c r="K57" s="306"/>
-      <c r="L57" s="306"/>
-      <c r="M57" s="306"/>
-      <c r="N57" s="306"/>
-      <c r="O57" s="306"/>
-      <c r="P57" s="306"/>
-      <c r="Q57" s="306"/>
-      <c r="R57" s="306"/>
-      <c r="S57" s="306"/>
-      <c r="T57" s="306"/>
-      <c r="U57" s="306"/>
+      <c r="B57" s="230" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="230"/>
+      <c r="D57" s="230"/>
+      <c r="E57" s="230"/>
+      <c r="F57" s="230"/>
+      <c r="G57" s="230"/>
+      <c r="H57" s="230"/>
+      <c r="I57" s="230"/>
+      <c r="J57" s="230"/>
+      <c r="K57" s="230"/>
+      <c r="L57" s="230"/>
+      <c r="M57" s="230"/>
+      <c r="N57" s="230"/>
+      <c r="O57" s="230"/>
+      <c r="P57" s="230"/>
+      <c r="Q57" s="230"/>
+      <c r="R57" s="230"/>
+      <c r="S57" s="230"/>
+      <c r="T57" s="230"/>
+      <c r="U57" s="230"/>
     </row>
     <row r="58" spans="2:21" ht="15">
       <c r="B58" s="33"/>
@@ -22060,103 +22076,97 @@
       <c r="I58" s="16"/>
     </row>
     <row r="59" spans="2:21" ht="16.5" customHeight="1">
-      <c r="B59" s="307" t="s">
-        <v>156</v>
-      </c>
-      <c r="C59" s="307"/>
-      <c r="D59" s="307"/>
-      <c r="E59" s="307"/>
-      <c r="F59" s="307"/>
-      <c r="G59" s="307"/>
-      <c r="H59" s="307"/>
-      <c r="I59" s="307"/>
-      <c r="J59" s="307"/>
-      <c r="K59" s="307"/>
-      <c r="L59" s="307"/>
-      <c r="M59" s="307"/>
-      <c r="N59" s="307"/>
-      <c r="O59" s="307"/>
-      <c r="P59" s="307"/>
-      <c r="Q59" s="307"/>
-      <c r="R59" s="307"/>
-      <c r="S59" s="307"/>
-      <c r="T59" s="307"/>
-      <c r="U59" s="307"/>
+      <c r="C59" s="308" t="s">
+        <v>174</v>
+      </c>
+      <c r="D59" s="308"/>
+      <c r="E59" s="308"/>
+      <c r="F59" s="308"/>
+      <c r="G59" s="308"/>
+      <c r="H59" s="308"/>
+      <c r="I59" s="308"/>
+      <c r="J59" s="308"/>
+      <c r="K59" s="308"/>
+      <c r="L59" s="308"/>
+      <c r="M59" s="308"/>
+      <c r="N59" s="308"/>
+      <c r="O59" s="308"/>
+      <c r="P59" s="308"/>
+      <c r="Q59" s="308"/>
+      <c r="R59" s="308"/>
+      <c r="S59" s="308"/>
+      <c r="T59" s="308"/>
+      <c r="U59" s="308"/>
     </row>
     <row r="60" spans="2:21" ht="16.5" customHeight="1">
-      <c r="B60" s="308" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="308"/>
-      <c r="D60" s="308"/>
-      <c r="E60" s="308"/>
-      <c r="F60" s="308"/>
-      <c r="G60" s="308"/>
-      <c r="H60" s="308"/>
-      <c r="I60" s="308"/>
-      <c r="J60" s="308"/>
-      <c r="K60" s="308"/>
-      <c r="L60" s="308"/>
-      <c r="M60" s="308"/>
-      <c r="N60" s="308"/>
-      <c r="O60" s="308"/>
-      <c r="P60" s="308"/>
-      <c r="Q60" s="308"/>
-      <c r="R60" s="308"/>
-      <c r="S60" s="308"/>
-      <c r="T60" s="308"/>
-      <c r="U60" s="308"/>
+      <c r="C60" s="200" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="200"/>
+      <c r="E60" s="200"/>
+      <c r="F60" s="200"/>
+      <c r="G60" s="200"/>
+      <c r="H60" s="200"/>
+      <c r="I60" s="200"/>
+      <c r="J60" s="200"/>
+      <c r="K60" s="200"/>
+      <c r="L60" s="200"/>
+      <c r="M60" s="200"/>
+      <c r="N60" s="200"/>
+      <c r="O60" s="200"/>
+      <c r="P60" s="200"/>
+      <c r="Q60" s="200"/>
+      <c r="R60" s="200"/>
+      <c r="S60" s="200"/>
+      <c r="T60" s="200"/>
+      <c r="U60" s="200"/>
     </row>
     <row r="61" spans="2:21" ht="16.5" customHeight="1">
-      <c r="B61" s="309" t="str">
-        <f>F53</f>
-        <v>마곡엠밸리4단지아파트</v>
-      </c>
-      <c r="C61" s="309"/>
-      <c r="D61" s="309"/>
-      <c r="E61" s="309"/>
-      <c r="F61" s="309"/>
-      <c r="G61" s="309"/>
-      <c r="H61" s="309"/>
-      <c r="I61" s="308" t="s">
-        <v>145</v>
-      </c>
-      <c r="J61" s="308"/>
-      <c r="K61" s="308"/>
-      <c r="L61" s="308"/>
-      <c r="M61" s="308"/>
-      <c r="N61" s="308"/>
-      <c r="O61" s="308"/>
-      <c r="P61" s="308"/>
-      <c r="Q61" s="308"/>
-      <c r="R61" s="308"/>
-      <c r="S61" s="308"/>
-      <c r="T61" s="308"/>
-      <c r="U61" s="308"/>
+      <c r="C61" s="200" t="str">
+        <f>F53&amp;" (이하 ""발주자""라 한다)와 장기수선계획 조정 대행자인"</f>
+        <v>마곡엠밸리4단지아파트 (이하 "발주자"라 한다)와 장기수선계획 조정 대행자인</v>
+      </c>
+      <c r="D61" s="200"/>
+      <c r="E61" s="200"/>
+      <c r="F61" s="200"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="200"/>
+      <c r="I61" s="200"/>
+      <c r="J61" s="200"/>
+      <c r="K61" s="200"/>
+      <c r="L61" s="200"/>
+      <c r="M61" s="200"/>
+      <c r="N61" s="200"/>
+      <c r="O61" s="200"/>
+      <c r="P61" s="200"/>
+      <c r="Q61" s="200"/>
+      <c r="R61" s="200"/>
+      <c r="S61" s="200"/>
+      <c r="T61" s="200"/>
+      <c r="U61" s="200"/>
     </row>
     <row r="62" spans="2:21" ht="16.5" customHeight="1">
-      <c r="B62" s="310" t="s">
-        <v>146</v>
-      </c>
-      <c r="C62" s="310"/>
-      <c r="D62" s="310"/>
-      <c r="E62" s="310"/>
-      <c r="F62" s="310"/>
-      <c r="G62" s="310"/>
-      <c r="H62" s="310"/>
-      <c r="I62" s="310"/>
-      <c r="J62" s="310"/>
-      <c r="K62" s="310"/>
-      <c r="L62" s="310"/>
-      <c r="M62" s="310"/>
-      <c r="N62" s="310"/>
-      <c r="O62" s="310"/>
-      <c r="P62" s="310"/>
-      <c r="Q62" s="310"/>
-      <c r="R62" s="310"/>
-      <c r="S62" s="310"/>
-      <c r="T62" s="310"/>
-      <c r="U62" s="310"/>
+      <c r="C62" s="309" t="s">
+        <v>176</v>
+      </c>
+      <c r="D62" s="309"/>
+      <c r="E62" s="309"/>
+      <c r="F62" s="309"/>
+      <c r="G62" s="309"/>
+      <c r="H62" s="309"/>
+      <c r="I62" s="309"/>
+      <c r="J62" s="309"/>
+      <c r="K62" s="309"/>
+      <c r="L62" s="309"/>
+      <c r="M62" s="309"/>
+      <c r="N62" s="309"/>
+      <c r="O62" s="309"/>
+      <c r="P62" s="309"/>
+      <c r="Q62" s="309"/>
+      <c r="R62" s="309"/>
+      <c r="S62" s="309"/>
+      <c r="T62" s="309"/>
+      <c r="U62" s="309"/>
     </row>
     <row r="63" spans="2:21" ht="20" customHeight="1">
       <c r="B63" s="34"/>
@@ -22170,40 +22180,40 @@
       <c r="J63" s="34"/>
     </row>
     <row r="64" spans="2:21" ht="20" customHeight="1">
-      <c r="B64" s="311" t="s">
-        <v>155</v>
-      </c>
-      <c r="C64" s="311"/>
-      <c r="D64" s="311"/>
-      <c r="E64" s="311"/>
-      <c r="F64" s="311"/>
-      <c r="G64" s="311"/>
-      <c r="H64" s="311"/>
-      <c r="I64" s="311"/>
-      <c r="J64" s="311"/>
+      <c r="B64" s="231" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="231"/>
+      <c r="D64" s="231"/>
+      <c r="E64" s="231"/>
+      <c r="F64" s="231"/>
+      <c r="G64" s="231"/>
+      <c r="H64" s="231"/>
+      <c r="I64" s="231"/>
+      <c r="J64" s="231"/>
     </row>
     <row r="65" spans="2:21" ht="75.75" customHeight="1">
-      <c r="C65" s="273" t="s">
-        <v>131</v>
-      </c>
-      <c r="D65" s="273"/>
-      <c r="E65" s="273"/>
-      <c r="F65" s="273"/>
-      <c r="G65" s="273"/>
-      <c r="H65" s="273"/>
-      <c r="I65" s="273"/>
-      <c r="J65" s="273"/>
-      <c r="K65" s="273"/>
-      <c r="L65" s="273"/>
-      <c r="M65" s="273"/>
-      <c r="N65" s="273"/>
-      <c r="O65" s="273"/>
-      <c r="P65" s="273"/>
-      <c r="Q65" s="273"/>
-      <c r="R65" s="273"/>
-      <c r="S65" s="273"/>
-      <c r="T65" s="273"/>
-      <c r="U65" s="273"/>
+      <c r="C65" s="200" t="s">
+        <v>127</v>
+      </c>
+      <c r="D65" s="200"/>
+      <c r="E65" s="200"/>
+      <c r="F65" s="200"/>
+      <c r="G65" s="200"/>
+      <c r="H65" s="200"/>
+      <c r="I65" s="200"/>
+      <c r="J65" s="200"/>
+      <c r="K65" s="200"/>
+      <c r="L65" s="200"/>
+      <c r="M65" s="200"/>
+      <c r="N65" s="200"/>
+      <c r="O65" s="200"/>
+      <c r="P65" s="200"/>
+      <c r="Q65" s="200"/>
+      <c r="R65" s="200"/>
+      <c r="S65" s="200"/>
+      <c r="T65" s="200"/>
+      <c r="U65" s="200"/>
     </row>
     <row r="66" spans="2:21" ht="20" customHeight="1">
       <c r="B66" s="35"/>
@@ -22212,120 +22222,120 @@
       <c r="I66" s="16"/>
     </row>
     <row r="67" spans="2:21" ht="20" customHeight="1">
-      <c r="B67" s="311" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="311"/>
-      <c r="D67" s="311"/>
-      <c r="E67" s="311"/>
-      <c r="F67" s="311"/>
-      <c r="G67" s="311"/>
-      <c r="H67" s="311"/>
-      <c r="I67" s="311"/>
-      <c r="J67" s="311"/>
-      <c r="K67" s="311"/>
-      <c r="L67" s="311"/>
-      <c r="M67" s="311"/>
-      <c r="N67" s="311"/>
-      <c r="O67" s="311"/>
-      <c r="P67" s="311"/>
-      <c r="Q67" s="311"/>
-      <c r="R67" s="311"/>
-      <c r="S67" s="311"/>
-      <c r="T67" s="311"/>
-      <c r="U67" s="311"/>
+      <c r="B67" s="231" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="231"/>
+      <c r="D67" s="231"/>
+      <c r="E67" s="231"/>
+      <c r="F67" s="231"/>
+      <c r="G67" s="231"/>
+      <c r="H67" s="231"/>
+      <c r="I67" s="231"/>
+      <c r="J67" s="231"/>
+      <c r="K67" s="231"/>
+      <c r="L67" s="231"/>
+      <c r="M67" s="231"/>
+      <c r="N67" s="231"/>
+      <c r="O67" s="231"/>
+      <c r="P67" s="231"/>
+      <c r="Q67" s="231"/>
+      <c r="R67" s="231"/>
+      <c r="S67" s="231"/>
+      <c r="T67" s="231"/>
+      <c r="U67" s="231"/>
     </row>
     <row r="68" spans="2:21" ht="20" customHeight="1">
-      <c r="C68" s="312" t="s">
-        <v>116</v>
-      </c>
-      <c r="D68" s="312"/>
-      <c r="E68" s="312"/>
-      <c r="F68" s="312"/>
-      <c r="G68" s="312"/>
-      <c r="H68" s="312"/>
-      <c r="I68" s="312"/>
-      <c r="J68" s="312"/>
-      <c r="K68" s="312"/>
-      <c r="L68" s="312"/>
-      <c r="M68" s="312"/>
-      <c r="N68" s="312"/>
-      <c r="O68" s="312"/>
-      <c r="P68" s="312"/>
-      <c r="Q68" s="312"/>
-      <c r="R68" s="312"/>
-      <c r="S68" s="312"/>
-      <c r="T68" s="312"/>
-      <c r="U68" s="312"/>
+      <c r="C68" s="232" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" s="232"/>
+      <c r="E68" s="232"/>
+      <c r="F68" s="232"/>
+      <c r="G68" s="232"/>
+      <c r="H68" s="232"/>
+      <c r="I68" s="232"/>
+      <c r="J68" s="232"/>
+      <c r="K68" s="232"/>
+      <c r="L68" s="232"/>
+      <c r="M68" s="232"/>
+      <c r="N68" s="232"/>
+      <c r="O68" s="232"/>
+      <c r="P68" s="232"/>
+      <c r="Q68" s="232"/>
+      <c r="R68" s="232"/>
+      <c r="S68" s="232"/>
+      <c r="T68" s="232"/>
+      <c r="U68" s="232"/>
     </row>
     <row r="69" spans="2:21" ht="23.25" customHeight="1">
       <c r="C69" s="36"/>
-      <c r="D69" s="312" t="s">
-        <v>125</v>
-      </c>
-      <c r="E69" s="312"/>
-      <c r="F69" s="312"/>
-      <c r="G69" s="312"/>
-      <c r="H69" s="312"/>
-      <c r="I69" s="312"/>
-      <c r="J69" s="312"/>
-      <c r="K69" s="312"/>
-      <c r="L69" s="312"/>
-      <c r="M69" s="312"/>
-      <c r="N69" s="312"/>
-      <c r="O69" s="312"/>
-      <c r="P69" s="312"/>
-      <c r="Q69" s="312"/>
-      <c r="R69" s="312"/>
-      <c r="S69" s="312"/>
-      <c r="T69" s="312"/>
-      <c r="U69" s="312"/>
+      <c r="D69" s="232" t="s">
+        <v>121</v>
+      </c>
+      <c r="E69" s="232"/>
+      <c r="F69" s="232"/>
+      <c r="G69" s="232"/>
+      <c r="H69" s="232"/>
+      <c r="I69" s="232"/>
+      <c r="J69" s="232"/>
+      <c r="K69" s="232"/>
+      <c r="L69" s="232"/>
+      <c r="M69" s="232"/>
+      <c r="N69" s="232"/>
+      <c r="O69" s="232"/>
+      <c r="P69" s="232"/>
+      <c r="Q69" s="232"/>
+      <c r="R69" s="232"/>
+      <c r="S69" s="232"/>
+      <c r="T69" s="232"/>
+      <c r="U69" s="232"/>
     </row>
     <row r="70" spans="2:21" ht="30.75" customHeight="1">
       <c r="C70" s="36"/>
-      <c r="D70" s="273" t="s">
-        <v>121</v>
-      </c>
-      <c r="E70" s="273"/>
-      <c r="F70" s="273"/>
-      <c r="G70" s="273"/>
-      <c r="H70" s="273"/>
-      <c r="I70" s="273"/>
-      <c r="J70" s="273"/>
-      <c r="K70" s="273"/>
-      <c r="L70" s="273"/>
-      <c r="M70" s="273"/>
-      <c r="N70" s="273"/>
-      <c r="O70" s="273"/>
-      <c r="P70" s="273"/>
-      <c r="Q70" s="273"/>
-      <c r="R70" s="273"/>
-      <c r="S70" s="273"/>
-      <c r="T70" s="273"/>
-      <c r="U70" s="273"/>
+      <c r="D70" s="200" t="s">
+        <v>117</v>
+      </c>
+      <c r="E70" s="200"/>
+      <c r="F70" s="200"/>
+      <c r="G70" s="200"/>
+      <c r="H70" s="200"/>
+      <c r="I70" s="200"/>
+      <c r="J70" s="200"/>
+      <c r="K70" s="200"/>
+      <c r="L70" s="200"/>
+      <c r="M70" s="200"/>
+      <c r="N70" s="200"/>
+      <c r="O70" s="200"/>
+      <c r="P70" s="200"/>
+      <c r="Q70" s="200"/>
+      <c r="R70" s="200"/>
+      <c r="S70" s="200"/>
+      <c r="T70" s="200"/>
+      <c r="U70" s="200"/>
     </row>
     <row r="71" spans="2:21" ht="27" customHeight="1">
       <c r="C71" s="39"/>
-      <c r="D71" s="273" t="s">
-        <v>120</v>
-      </c>
-      <c r="E71" s="273"/>
-      <c r="F71" s="273"/>
-      <c r="G71" s="273"/>
-      <c r="H71" s="273"/>
-      <c r="I71" s="273"/>
-      <c r="J71" s="273"/>
-      <c r="K71" s="273"/>
-      <c r="L71" s="273"/>
-      <c r="M71" s="273"/>
-      <c r="N71" s="273"/>
-      <c r="O71" s="273"/>
-      <c r="P71" s="273"/>
-      <c r="Q71" s="273"/>
-      <c r="R71" s="273"/>
-      <c r="S71" s="273"/>
-      <c r="T71" s="273"/>
-      <c r="U71" s="273"/>
+      <c r="D71" s="200" t="s">
+        <v>116</v>
+      </c>
+      <c r="E71" s="200"/>
+      <c r="F71" s="200"/>
+      <c r="G71" s="200"/>
+      <c r="H71" s="200"/>
+      <c r="I71" s="200"/>
+      <c r="J71" s="200"/>
+      <c r="K71" s="200"/>
+      <c r="L71" s="200"/>
+      <c r="M71" s="200"/>
+      <c r="N71" s="200"/>
+      <c r="O71" s="200"/>
+      <c r="P71" s="200"/>
+      <c r="Q71" s="200"/>
+      <c r="R71" s="200"/>
+      <c r="S71" s="200"/>
+      <c r="T71" s="200"/>
+      <c r="U71" s="200"/>
     </row>
     <row r="72" spans="2:21" ht="20" customHeight="1">
       <c r="B72" s="35"/>
@@ -22334,51 +22344,51 @@
       <c r="I72" s="16"/>
     </row>
     <row r="73" spans="2:21" ht="20" customHeight="1">
-      <c r="B73" s="311" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" s="311"/>
-      <c r="D73" s="311"/>
-      <c r="E73" s="311"/>
-      <c r="F73" s="311"/>
-      <c r="G73" s="311"/>
-      <c r="H73" s="311"/>
-      <c r="I73" s="311"/>
-      <c r="J73" s="311"/>
-      <c r="K73" s="311"/>
-      <c r="L73" s="311"/>
-      <c r="M73" s="311"/>
-      <c r="N73" s="311"/>
-      <c r="O73" s="311"/>
-      <c r="P73" s="311"/>
-      <c r="Q73" s="311"/>
-      <c r="R73" s="311"/>
-      <c r="S73" s="311"/>
-      <c r="T73" s="311"/>
-      <c r="U73" s="311"/>
+      <c r="B73" s="231" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="231"/>
+      <c r="D73" s="231"/>
+      <c r="E73" s="231"/>
+      <c r="F73" s="231"/>
+      <c r="G73" s="231"/>
+      <c r="H73" s="231"/>
+      <c r="I73" s="231"/>
+      <c r="J73" s="231"/>
+      <c r="K73" s="231"/>
+      <c r="L73" s="231"/>
+      <c r="M73" s="231"/>
+      <c r="N73" s="231"/>
+      <c r="O73" s="231"/>
+      <c r="P73" s="231"/>
+      <c r="Q73" s="231"/>
+      <c r="R73" s="231"/>
+      <c r="S73" s="231"/>
+      <c r="T73" s="231"/>
+      <c r="U73" s="231"/>
     </row>
     <row r="74" spans="2:21" ht="20" customHeight="1">
-      <c r="C74" s="312" t="s">
-        <v>76</v>
-      </c>
-      <c r="D74" s="312"/>
-      <c r="E74" s="312"/>
-      <c r="F74" s="312"/>
-      <c r="G74" s="312"/>
-      <c r="H74" s="312"/>
-      <c r="I74" s="312"/>
-      <c r="J74" s="312"/>
-      <c r="K74" s="312"/>
-      <c r="L74" s="312"/>
-      <c r="M74" s="312"/>
-      <c r="N74" s="312"/>
-      <c r="O74" s="312"/>
-      <c r="P74" s="312"/>
-      <c r="Q74" s="312"/>
-      <c r="R74" s="312"/>
-      <c r="S74" s="312"/>
-      <c r="T74" s="312"/>
-      <c r="U74" s="312"/>
+      <c r="C74" s="232" t="s">
+        <v>74</v>
+      </c>
+      <c r="D74" s="232"/>
+      <c r="E74" s="232"/>
+      <c r="F74" s="232"/>
+      <c r="G74" s="232"/>
+      <c r="H74" s="232"/>
+      <c r="I74" s="232"/>
+      <c r="J74" s="232"/>
+      <c r="K74" s="232"/>
+      <c r="L74" s="232"/>
+      <c r="M74" s="232"/>
+      <c r="N74" s="232"/>
+      <c r="O74" s="232"/>
+      <c r="P74" s="232"/>
+      <c r="Q74" s="232"/>
+      <c r="R74" s="232"/>
+      <c r="S74" s="232"/>
+      <c r="T74" s="232"/>
+      <c r="U74" s="232"/>
     </row>
     <row r="75" spans="2:21" ht="20" customHeight="1">
       <c r="B75" s="35"/>
@@ -22387,112 +22397,112 @@
       <c r="I75" s="16"/>
     </row>
     <row r="76" spans="2:21" ht="20" customHeight="1">
-      <c r="B76" s="311" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="311"/>
-      <c r="D76" s="311"/>
-      <c r="E76" s="311"/>
-      <c r="F76" s="311"/>
-      <c r="G76" s="311"/>
-      <c r="H76" s="311"/>
-      <c r="I76" s="311"/>
-      <c r="J76" s="311"/>
+      <c r="B76" s="231" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="231"/>
+      <c r="D76" s="231"/>
+      <c r="E76" s="231"/>
+      <c r="F76" s="231"/>
+      <c r="G76" s="231"/>
+      <c r="H76" s="231"/>
+      <c r="I76" s="231"/>
+      <c r="J76" s="231"/>
     </row>
     <row r="77" spans="2:21" ht="20" customHeight="1">
-      <c r="C77" s="273" t="s">
-        <v>126</v>
-      </c>
-      <c r="D77" s="273"/>
-      <c r="E77" s="273"/>
-      <c r="F77" s="273"/>
-      <c r="G77" s="273"/>
-      <c r="H77" s="273"/>
-      <c r="I77" s="273"/>
-      <c r="J77" s="273"/>
-      <c r="K77" s="273"/>
-      <c r="L77" s="273"/>
-      <c r="M77" s="273"/>
-      <c r="N77" s="273"/>
-      <c r="O77" s="273"/>
-      <c r="P77" s="273"/>
-      <c r="Q77" s="273"/>
-      <c r="R77" s="273"/>
-      <c r="S77" s="273"/>
-      <c r="T77" s="273"/>
-      <c r="U77" s="273"/>
+      <c r="C77" s="200" t="s">
+        <v>122</v>
+      </c>
+      <c r="D77" s="200"/>
+      <c r="E77" s="200"/>
+      <c r="F77" s="200"/>
+      <c r="G77" s="200"/>
+      <c r="H77" s="200"/>
+      <c r="I77" s="200"/>
+      <c r="J77" s="200"/>
+      <c r="K77" s="200"/>
+      <c r="L77" s="200"/>
+      <c r="M77" s="200"/>
+      <c r="N77" s="200"/>
+      <c r="O77" s="200"/>
+      <c r="P77" s="200"/>
+      <c r="Q77" s="200"/>
+      <c r="R77" s="200"/>
+      <c r="S77" s="200"/>
+      <c r="T77" s="200"/>
+      <c r="U77" s="200"/>
     </row>
     <row r="78" spans="2:21" ht="20" customHeight="1">
       <c r="B78" s="37"/>
-      <c r="C78" s="273" t="s">
-        <v>78</v>
-      </c>
-      <c r="D78" s="273"/>
-      <c r="E78" s="273"/>
-      <c r="F78" s="273"/>
-      <c r="G78" s="273"/>
-      <c r="H78" s="273"/>
-      <c r="I78" s="273"/>
-      <c r="J78" s="273"/>
-      <c r="K78" s="273"/>
-      <c r="L78" s="273"/>
-      <c r="M78" s="273"/>
-      <c r="N78" s="273"/>
-      <c r="O78" s="273"/>
-      <c r="P78" s="273"/>
-      <c r="Q78" s="273"/>
-      <c r="R78" s="273"/>
-      <c r="S78" s="273"/>
-      <c r="T78" s="273"/>
-      <c r="U78" s="273"/>
+      <c r="C78" s="200" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78" s="200"/>
+      <c r="E78" s="200"/>
+      <c r="F78" s="200"/>
+      <c r="G78" s="200"/>
+      <c r="H78" s="200"/>
+      <c r="I78" s="200"/>
+      <c r="J78" s="200"/>
+      <c r="K78" s="200"/>
+      <c r="L78" s="200"/>
+      <c r="M78" s="200"/>
+      <c r="N78" s="200"/>
+      <c r="O78" s="200"/>
+      <c r="P78" s="200"/>
+      <c r="Q78" s="200"/>
+      <c r="R78" s="200"/>
+      <c r="S78" s="200"/>
+      <c r="T78" s="200"/>
+      <c r="U78" s="200"/>
     </row>
     <row r="79" spans="2:21" ht="33" customHeight="1">
       <c r="B79" s="38"/>
-      <c r="C79" s="273" t="s">
-        <v>79</v>
-      </c>
-      <c r="D79" s="273"/>
-      <c r="E79" s="273"/>
-      <c r="F79" s="273"/>
-      <c r="G79" s="273"/>
-      <c r="H79" s="273"/>
-      <c r="I79" s="273"/>
-      <c r="J79" s="273"/>
-      <c r="K79" s="273"/>
-      <c r="L79" s="273"/>
-      <c r="M79" s="273"/>
-      <c r="N79" s="273"/>
-      <c r="O79" s="273"/>
-      <c r="P79" s="273"/>
-      <c r="Q79" s="273"/>
-      <c r="R79" s="273"/>
-      <c r="S79" s="273"/>
-      <c r="T79" s="273"/>
-      <c r="U79" s="273"/>
+      <c r="C79" s="200" t="s">
+        <v>77</v>
+      </c>
+      <c r="D79" s="200"/>
+      <c r="E79" s="200"/>
+      <c r="F79" s="200"/>
+      <c r="G79" s="200"/>
+      <c r="H79" s="200"/>
+      <c r="I79" s="200"/>
+      <c r="J79" s="200"/>
+      <c r="K79" s="200"/>
+      <c r="L79" s="200"/>
+      <c r="M79" s="200"/>
+      <c r="N79" s="200"/>
+      <c r="O79" s="200"/>
+      <c r="P79" s="200"/>
+      <c r="Q79" s="200"/>
+      <c r="R79" s="200"/>
+      <c r="S79" s="200"/>
+      <c r="T79" s="200"/>
+      <c r="U79" s="200"/>
     </row>
     <row r="80" spans="2:21" ht="34" customHeight="1">
       <c r="B80" s="38"/>
-      <c r="C80" s="273" t="s">
-        <v>80</v>
-      </c>
-      <c r="D80" s="273"/>
-      <c r="E80" s="273"/>
-      <c r="F80" s="273"/>
-      <c r="G80" s="273"/>
-      <c r="H80" s="273"/>
-      <c r="I80" s="273"/>
-      <c r="J80" s="273"/>
-      <c r="K80" s="273"/>
-      <c r="L80" s="273"/>
-      <c r="M80" s="273"/>
-      <c r="N80" s="273"/>
-      <c r="O80" s="273"/>
-      <c r="P80" s="273"/>
-      <c r="Q80" s="273"/>
-      <c r="R80" s="273"/>
-      <c r="S80" s="273"/>
-      <c r="T80" s="273"/>
-      <c r="U80" s="273"/>
+      <c r="C80" s="200" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" s="200"/>
+      <c r="E80" s="200"/>
+      <c r="F80" s="200"/>
+      <c r="G80" s="200"/>
+      <c r="H80" s="200"/>
+      <c r="I80" s="200"/>
+      <c r="J80" s="200"/>
+      <c r="K80" s="200"/>
+      <c r="L80" s="200"/>
+      <c r="M80" s="200"/>
+      <c r="N80" s="200"/>
+      <c r="O80" s="200"/>
+      <c r="P80" s="200"/>
+      <c r="Q80" s="200"/>
+      <c r="R80" s="200"/>
+      <c r="S80" s="200"/>
+      <c r="T80" s="200"/>
+      <c r="U80" s="200"/>
     </row>
     <row r="81" spans="2:21" ht="20" customHeight="1">
       <c r="C81" s="36"/>
@@ -22505,40 +22515,40 @@
       <c r="J81" s="36"/>
     </row>
     <row r="82" spans="2:21" ht="20" customHeight="1">
-      <c r="B82" s="311" t="s">
-        <v>81</v>
-      </c>
-      <c r="C82" s="311"/>
-      <c r="D82" s="311"/>
-      <c r="E82" s="311"/>
-      <c r="F82" s="311"/>
-      <c r="G82" s="311"/>
-      <c r="H82" s="311"/>
-      <c r="I82" s="311"/>
-      <c r="J82" s="311"/>
+      <c r="B82" s="231" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" s="231"/>
+      <c r="D82" s="231"/>
+      <c r="E82" s="231"/>
+      <c r="F82" s="231"/>
+      <c r="G82" s="231"/>
+      <c r="H82" s="231"/>
+      <c r="I82" s="231"/>
+      <c r="J82" s="231"/>
     </row>
     <row r="83" spans="2:21" ht="52.5" customHeight="1">
-      <c r="C83" s="273" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="273"/>
-      <c r="E83" s="273"/>
-      <c r="F83" s="273"/>
-      <c r="G83" s="273"/>
-      <c r="H83" s="273"/>
-      <c r="I83" s="273"/>
-      <c r="J83" s="273"/>
-      <c r="K83" s="273"/>
-      <c r="L83" s="273"/>
-      <c r="M83" s="273"/>
-      <c r="N83" s="273"/>
-      <c r="O83" s="273"/>
-      <c r="P83" s="273"/>
-      <c r="Q83" s="273"/>
-      <c r="R83" s="273"/>
-      <c r="S83" s="273"/>
-      <c r="T83" s="273"/>
-      <c r="U83" s="273"/>
+      <c r="C83" s="200" t="s">
+        <v>80</v>
+      </c>
+      <c r="D83" s="200"/>
+      <c r="E83" s="200"/>
+      <c r="F83" s="200"/>
+      <c r="G83" s="200"/>
+      <c r="H83" s="200"/>
+      <c r="I83" s="200"/>
+      <c r="J83" s="200"/>
+      <c r="K83" s="200"/>
+      <c r="L83" s="200"/>
+      <c r="M83" s="200"/>
+      <c r="N83" s="200"/>
+      <c r="O83" s="200"/>
+      <c r="P83" s="200"/>
+      <c r="Q83" s="200"/>
+      <c r="R83" s="200"/>
+      <c r="S83" s="200"/>
+      <c r="T83" s="200"/>
+      <c r="U83" s="200"/>
     </row>
     <row r="84" spans="2:21" ht="19.5" customHeight="1">
       <c r="C84" s="34"/>
@@ -22562,212 +22572,212 @@
       <c r="U84" s="34"/>
     </row>
     <row r="85" spans="2:21" ht="20" customHeight="1">
-      <c r="B85" s="311" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" s="311"/>
-      <c r="D85" s="311"/>
-      <c r="E85" s="311"/>
-      <c r="F85" s="311"/>
-      <c r="G85" s="311"/>
-      <c r="H85" s="311"/>
-      <c r="I85" s="311"/>
-      <c r="J85" s="311"/>
-      <c r="K85" s="311"/>
-      <c r="L85" s="311"/>
-      <c r="M85" s="311"/>
-      <c r="N85" s="311"/>
-      <c r="O85" s="311"/>
-      <c r="P85" s="311"/>
-      <c r="Q85" s="311"/>
-      <c r="R85" s="311"/>
-      <c r="S85" s="311"/>
-      <c r="T85" s="311"/>
-      <c r="U85" s="311"/>
+      <c r="B85" s="231" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" s="231"/>
+      <c r="D85" s="231"/>
+      <c r="E85" s="231"/>
+      <c r="F85" s="231"/>
+      <c r="G85" s="231"/>
+      <c r="H85" s="231"/>
+      <c r="I85" s="231"/>
+      <c r="J85" s="231"/>
+      <c r="K85" s="231"/>
+      <c r="L85" s="231"/>
+      <c r="M85" s="231"/>
+      <c r="N85" s="231"/>
+      <c r="O85" s="231"/>
+      <c r="P85" s="231"/>
+      <c r="Q85" s="231"/>
+      <c r="R85" s="231"/>
+      <c r="S85" s="231"/>
+      <c r="T85" s="231"/>
+      <c r="U85" s="231"/>
     </row>
     <row r="86" spans="2:21" ht="69" customHeight="1">
-      <c r="C86" s="273" t="s">
-        <v>127</v>
-      </c>
-      <c r="D86" s="273"/>
-      <c r="E86" s="273"/>
-      <c r="F86" s="273"/>
-      <c r="G86" s="273"/>
-      <c r="H86" s="273"/>
-      <c r="I86" s="273"/>
-      <c r="J86" s="273"/>
-      <c r="K86" s="273"/>
-      <c r="L86" s="273"/>
-      <c r="M86" s="273"/>
-      <c r="N86" s="273"/>
-      <c r="O86" s="273"/>
-      <c r="P86" s="273"/>
-      <c r="Q86" s="273"/>
-      <c r="R86" s="273"/>
-      <c r="S86" s="273"/>
-      <c r="T86" s="273"/>
-      <c r="U86" s="273"/>
+      <c r="C86" s="200" t="s">
+        <v>123</v>
+      </c>
+      <c r="D86" s="200"/>
+      <c r="E86" s="200"/>
+      <c r="F86" s="200"/>
+      <c r="G86" s="200"/>
+      <c r="H86" s="200"/>
+      <c r="I86" s="200"/>
+      <c r="J86" s="200"/>
+      <c r="K86" s="200"/>
+      <c r="L86" s="200"/>
+      <c r="M86" s="200"/>
+      <c r="N86" s="200"/>
+      <c r="O86" s="200"/>
+      <c r="P86" s="200"/>
+      <c r="Q86" s="200"/>
+      <c r="R86" s="200"/>
+      <c r="S86" s="200"/>
+      <c r="T86" s="200"/>
+      <c r="U86" s="200"/>
     </row>
     <row r="87" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C87" s="273" t="s">
-        <v>84</v>
-      </c>
-      <c r="D87" s="273"/>
-      <c r="E87" s="273"/>
-      <c r="F87" s="273"/>
-      <c r="G87" s="273"/>
-      <c r="H87" s="273"/>
-      <c r="I87" s="273"/>
-      <c r="J87" s="273"/>
-      <c r="K87" s="273"/>
-      <c r="L87" s="273"/>
-      <c r="M87" s="273"/>
-      <c r="N87" s="273"/>
-      <c r="O87" s="273"/>
-      <c r="P87" s="273"/>
-      <c r="Q87" s="273"/>
-      <c r="R87" s="273"/>
-      <c r="S87" s="273"/>
-      <c r="T87" s="273"/>
-      <c r="U87" s="273"/>
+      <c r="C87" s="200" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" s="200"/>
+      <c r="E87" s="200"/>
+      <c r="F87" s="200"/>
+      <c r="G87" s="200"/>
+      <c r="H87" s="200"/>
+      <c r="I87" s="200"/>
+      <c r="J87" s="200"/>
+      <c r="K87" s="200"/>
+      <c r="L87" s="200"/>
+      <c r="M87" s="200"/>
+      <c r="N87" s="200"/>
+      <c r="O87" s="200"/>
+      <c r="P87" s="200"/>
+      <c r="Q87" s="200"/>
+      <c r="R87" s="200"/>
+      <c r="S87" s="200"/>
+      <c r="T87" s="200"/>
+      <c r="U87" s="200"/>
     </row>
     <row r="88" spans="2:21" ht="16.5" customHeight="1">
       <c r="C88" s="34"/>
-      <c r="D88" s="273" t="s">
-        <v>98</v>
-      </c>
-      <c r="E88" s="273"/>
-      <c r="F88" s="273"/>
-      <c r="G88" s="273"/>
-      <c r="H88" s="273"/>
-      <c r="I88" s="273"/>
-      <c r="J88" s="273"/>
-      <c r="K88" s="273"/>
-      <c r="L88" s="273"/>
-      <c r="M88" s="273"/>
-      <c r="N88" s="273"/>
-      <c r="O88" s="273"/>
-      <c r="P88" s="273"/>
-      <c r="Q88" s="273"/>
-      <c r="R88" s="273"/>
-      <c r="S88" s="273"/>
-      <c r="T88" s="273"/>
-      <c r="U88" s="273"/>
+      <c r="D88" s="200" t="s">
+        <v>96</v>
+      </c>
+      <c r="E88" s="200"/>
+      <c r="F88" s="200"/>
+      <c r="G88" s="200"/>
+      <c r="H88" s="200"/>
+      <c r="I88" s="200"/>
+      <c r="J88" s="200"/>
+      <c r="K88" s="200"/>
+      <c r="L88" s="200"/>
+      <c r="M88" s="200"/>
+      <c r="N88" s="200"/>
+      <c r="O88" s="200"/>
+      <c r="P88" s="200"/>
+      <c r="Q88" s="200"/>
+      <c r="R88" s="200"/>
+      <c r="S88" s="200"/>
+      <c r="T88" s="200"/>
+      <c r="U88" s="200"/>
     </row>
     <row r="89" spans="2:21" ht="16.5" customHeight="1">
       <c r="C89" s="34"/>
-      <c r="D89" s="273" t="s">
-        <v>122</v>
-      </c>
-      <c r="E89" s="273"/>
-      <c r="F89" s="273"/>
-      <c r="G89" s="273"/>
-      <c r="H89" s="273"/>
-      <c r="I89" s="273"/>
-      <c r="J89" s="273"/>
-      <c r="K89" s="273"/>
-      <c r="L89" s="273"/>
-      <c r="M89" s="273"/>
-      <c r="N89" s="273"/>
-      <c r="O89" s="273"/>
-      <c r="P89" s="273"/>
-      <c r="Q89" s="273"/>
-      <c r="R89" s="273"/>
-      <c r="S89" s="273"/>
-      <c r="T89" s="273"/>
-      <c r="U89" s="273"/>
+      <c r="D89" s="200" t="s">
+        <v>118</v>
+      </c>
+      <c r="E89" s="200"/>
+      <c r="F89" s="200"/>
+      <c r="G89" s="200"/>
+      <c r="H89" s="200"/>
+      <c r="I89" s="200"/>
+      <c r="J89" s="200"/>
+      <c r="K89" s="200"/>
+      <c r="L89" s="200"/>
+      <c r="M89" s="200"/>
+      <c r="N89" s="200"/>
+      <c r="O89" s="200"/>
+      <c r="P89" s="200"/>
+      <c r="Q89" s="200"/>
+      <c r="R89" s="200"/>
+      <c r="S89" s="200"/>
+      <c r="T89" s="200"/>
+      <c r="U89" s="200"/>
     </row>
     <row r="90" spans="2:21" ht="16.5" customHeight="1">
       <c r="C90" s="34"/>
-      <c r="D90" s="273" t="s">
-        <v>99</v>
-      </c>
-      <c r="E90" s="273"/>
-      <c r="F90" s="273"/>
-      <c r="G90" s="273"/>
-      <c r="H90" s="273"/>
-      <c r="I90" s="273"/>
-      <c r="J90" s="273"/>
-      <c r="K90" s="273"/>
-      <c r="L90" s="273"/>
-      <c r="M90" s="273"/>
-      <c r="N90" s="273"/>
-      <c r="O90" s="273"/>
-      <c r="P90" s="273"/>
-      <c r="Q90" s="273"/>
-      <c r="R90" s="273"/>
-      <c r="S90" s="273"/>
-      <c r="T90" s="273"/>
-      <c r="U90" s="273"/>
+      <c r="D90" s="200" t="s">
+        <v>97</v>
+      </c>
+      <c r="E90" s="200"/>
+      <c r="F90" s="200"/>
+      <c r="G90" s="200"/>
+      <c r="H90" s="200"/>
+      <c r="I90" s="200"/>
+      <c r="J90" s="200"/>
+      <c r="K90" s="200"/>
+      <c r="L90" s="200"/>
+      <c r="M90" s="200"/>
+      <c r="N90" s="200"/>
+      <c r="O90" s="200"/>
+      <c r="P90" s="200"/>
+      <c r="Q90" s="200"/>
+      <c r="R90" s="200"/>
+      <c r="S90" s="200"/>
+      <c r="T90" s="200"/>
+      <c r="U90" s="200"/>
     </row>
     <row r="91" spans="2:21" ht="16.5" customHeight="1">
       <c r="C91" s="34"/>
-      <c r="D91" s="273" t="s">
-        <v>123</v>
-      </c>
-      <c r="E91" s="273"/>
-      <c r="F91" s="273"/>
-      <c r="G91" s="273"/>
-      <c r="H91" s="273"/>
-      <c r="I91" s="273"/>
-      <c r="J91" s="273"/>
-      <c r="K91" s="273"/>
-      <c r="L91" s="273"/>
-      <c r="M91" s="273"/>
-      <c r="N91" s="273"/>
-      <c r="O91" s="273"/>
-      <c r="P91" s="273"/>
-      <c r="Q91" s="273"/>
-      <c r="R91" s="273"/>
-      <c r="S91" s="273"/>
-      <c r="T91" s="273"/>
-      <c r="U91" s="273"/>
+      <c r="D91" s="200" t="s">
+        <v>119</v>
+      </c>
+      <c r="E91" s="200"/>
+      <c r="F91" s="200"/>
+      <c r="G91" s="200"/>
+      <c r="H91" s="200"/>
+      <c r="I91" s="200"/>
+      <c r="J91" s="200"/>
+      <c r="K91" s="200"/>
+      <c r="L91" s="200"/>
+      <c r="M91" s="200"/>
+      <c r="N91" s="200"/>
+      <c r="O91" s="200"/>
+      <c r="P91" s="200"/>
+      <c r="Q91" s="200"/>
+      <c r="R91" s="200"/>
+      <c r="S91" s="200"/>
+      <c r="T91" s="200"/>
+      <c r="U91" s="200"/>
     </row>
     <row r="92" spans="2:21" ht="16.5" customHeight="1">
       <c r="C92" s="34"/>
-      <c r="D92" s="273" t="s">
-        <v>159</v>
-      </c>
-      <c r="E92" s="273"/>
-      <c r="F92" s="273"/>
-      <c r="G92" s="273"/>
-      <c r="H92" s="273"/>
-      <c r="I92" s="273"/>
-      <c r="J92" s="273"/>
-      <c r="K92" s="273"/>
-      <c r="L92" s="273"/>
-      <c r="M92" s="273"/>
-      <c r="N92" s="273"/>
-      <c r="O92" s="273"/>
-      <c r="P92" s="273"/>
-      <c r="Q92" s="273"/>
-      <c r="R92" s="273"/>
-      <c r="S92" s="273"/>
-      <c r="T92" s="273"/>
-      <c r="U92" s="273"/>
+      <c r="D92" s="200" t="s">
+        <v>150</v>
+      </c>
+      <c r="E92" s="200"/>
+      <c r="F92" s="200"/>
+      <c r="G92" s="200"/>
+      <c r="H92" s="200"/>
+      <c r="I92" s="200"/>
+      <c r="J92" s="200"/>
+      <c r="K92" s="200"/>
+      <c r="L92" s="200"/>
+      <c r="M92" s="200"/>
+      <c r="N92" s="200"/>
+      <c r="O92" s="200"/>
+      <c r="P92" s="200"/>
+      <c r="Q92" s="200"/>
+      <c r="R92" s="200"/>
+      <c r="S92" s="200"/>
+      <c r="T92" s="200"/>
+      <c r="U92" s="200"/>
     </row>
     <row r="93" spans="2:21" ht="36" customHeight="1">
-      <c r="C93" s="273" t="s">
-        <v>100</v>
-      </c>
-      <c r="D93" s="273"/>
-      <c r="E93" s="273"/>
-      <c r="F93" s="273"/>
-      <c r="G93" s="273"/>
-      <c r="H93" s="273"/>
-      <c r="I93" s="273"/>
-      <c r="J93" s="273"/>
-      <c r="K93" s="273"/>
-      <c r="L93" s="273"/>
-      <c r="M93" s="273"/>
-      <c r="N93" s="273"/>
-      <c r="O93" s="273"/>
-      <c r="P93" s="273"/>
-      <c r="Q93" s="273"/>
-      <c r="R93" s="273"/>
-      <c r="S93" s="273"/>
-      <c r="T93" s="273"/>
-      <c r="U93" s="273"/>
+      <c r="C93" s="200" t="s">
+        <v>98</v>
+      </c>
+      <c r="D93" s="200"/>
+      <c r="E93" s="200"/>
+      <c r="F93" s="200"/>
+      <c r="G93" s="200"/>
+      <c r="H93" s="200"/>
+      <c r="I93" s="200"/>
+      <c r="J93" s="200"/>
+      <c r="K93" s="200"/>
+      <c r="L93" s="200"/>
+      <c r="M93" s="200"/>
+      <c r="N93" s="200"/>
+      <c r="O93" s="200"/>
+      <c r="P93" s="200"/>
+      <c r="Q93" s="200"/>
+      <c r="R93" s="200"/>
+      <c r="S93" s="200"/>
+      <c r="T93" s="200"/>
+      <c r="U93" s="200"/>
     </row>
     <row r="94" spans="2:21" ht="20" customHeight="1">
       <c r="B94" s="35"/>
@@ -22776,40 +22786,40 @@
       <c r="I94" s="16"/>
     </row>
     <row r="95" spans="2:21" ht="20" customHeight="1">
-      <c r="B95" s="311" t="s">
-        <v>86</v>
-      </c>
-      <c r="C95" s="311"/>
-      <c r="D95" s="311"/>
-      <c r="E95" s="311"/>
-      <c r="F95" s="311"/>
-      <c r="G95" s="311"/>
-      <c r="H95" s="311"/>
-      <c r="I95" s="311"/>
-      <c r="J95" s="311"/>
+      <c r="B95" s="231" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" s="231"/>
+      <c r="D95" s="231"/>
+      <c r="E95" s="231"/>
+      <c r="F95" s="231"/>
+      <c r="G95" s="231"/>
+      <c r="H95" s="231"/>
+      <c r="I95" s="231"/>
+      <c r="J95" s="231"/>
     </row>
     <row r="96" spans="2:21" ht="33" customHeight="1">
-      <c r="C96" s="273" t="s">
-        <v>85</v>
-      </c>
-      <c r="D96" s="273"/>
-      <c r="E96" s="273"/>
-      <c r="F96" s="273"/>
-      <c r="G96" s="273"/>
-      <c r="H96" s="273"/>
-      <c r="I96" s="273"/>
-      <c r="J96" s="273"/>
-      <c r="K96" s="273"/>
-      <c r="L96" s="273"/>
-      <c r="M96" s="273"/>
-      <c r="N96" s="273"/>
-      <c r="O96" s="273"/>
-      <c r="P96" s="273"/>
-      <c r="Q96" s="273"/>
-      <c r="R96" s="273"/>
-      <c r="S96" s="273"/>
-      <c r="T96" s="273"/>
-      <c r="U96" s="273"/>
+      <c r="C96" s="200" t="s">
+        <v>83</v>
+      </c>
+      <c r="D96" s="200"/>
+      <c r="E96" s="200"/>
+      <c r="F96" s="200"/>
+      <c r="G96" s="200"/>
+      <c r="H96" s="200"/>
+      <c r="I96" s="200"/>
+      <c r="J96" s="200"/>
+      <c r="K96" s="200"/>
+      <c r="L96" s="200"/>
+      <c r="M96" s="200"/>
+      <c r="N96" s="200"/>
+      <c r="O96" s="200"/>
+      <c r="P96" s="200"/>
+      <c r="Q96" s="200"/>
+      <c r="R96" s="200"/>
+      <c r="S96" s="200"/>
+      <c r="T96" s="200"/>
+      <c r="U96" s="200"/>
     </row>
     <row r="97" spans="2:21" ht="20" customHeight="1">
       <c r="B97" s="35"/>
@@ -22818,87 +22828,87 @@
       <c r="I97" s="16"/>
     </row>
     <row r="98" spans="2:21" ht="20" customHeight="1">
-      <c r="B98" s="311" t="s">
-        <v>87</v>
-      </c>
-      <c r="C98" s="311"/>
-      <c r="D98" s="311"/>
-      <c r="E98" s="311"/>
-      <c r="F98" s="311"/>
-      <c r="G98" s="311"/>
-      <c r="H98" s="311"/>
-      <c r="I98" s="311"/>
-      <c r="J98" s="311"/>
+      <c r="B98" s="231" t="s">
+        <v>85</v>
+      </c>
+      <c r="C98" s="231"/>
+      <c r="D98" s="231"/>
+      <c r="E98" s="231"/>
+      <c r="F98" s="231"/>
+      <c r="G98" s="231"/>
+      <c r="H98" s="231"/>
+      <c r="I98" s="231"/>
+      <c r="J98" s="231"/>
     </row>
     <row r="99" spans="2:21" s="40" customFormat="1" ht="37" customHeight="1">
       <c r="B99" s="41"/>
-      <c r="C99" s="273" t="s">
-        <v>88</v>
-      </c>
-      <c r="D99" s="273"/>
-      <c r="E99" s="273"/>
-      <c r="F99" s="273"/>
-      <c r="G99" s="273"/>
-      <c r="H99" s="273"/>
-      <c r="I99" s="273"/>
-      <c r="J99" s="273"/>
-      <c r="K99" s="273"/>
-      <c r="L99" s="273"/>
-      <c r="M99" s="273"/>
-      <c r="N99" s="273"/>
-      <c r="O99" s="273"/>
-      <c r="P99" s="273"/>
-      <c r="Q99" s="273"/>
-      <c r="R99" s="273"/>
-      <c r="S99" s="273"/>
-      <c r="T99" s="273"/>
-      <c r="U99" s="273"/>
+      <c r="C99" s="200" t="s">
+        <v>86</v>
+      </c>
+      <c r="D99" s="200"/>
+      <c r="E99" s="200"/>
+      <c r="F99" s="200"/>
+      <c r="G99" s="200"/>
+      <c r="H99" s="200"/>
+      <c r="I99" s="200"/>
+      <c r="J99" s="200"/>
+      <c r="K99" s="200"/>
+      <c r="L99" s="200"/>
+      <c r="M99" s="200"/>
+      <c r="N99" s="200"/>
+      <c r="O99" s="200"/>
+      <c r="P99" s="200"/>
+      <c r="Q99" s="200"/>
+      <c r="R99" s="200"/>
+      <c r="S99" s="200"/>
+      <c r="T99" s="200"/>
+      <c r="U99" s="200"/>
     </row>
     <row r="100" spans="2:21" ht="37" customHeight="1">
-      <c r="C100" s="273" t="s">
-        <v>117</v>
-      </c>
-      <c r="D100" s="273"/>
-      <c r="E100" s="273"/>
-      <c r="F100" s="273"/>
-      <c r="G100" s="273"/>
-      <c r="H100" s="273"/>
-      <c r="I100" s="273"/>
-      <c r="J100" s="273"/>
-      <c r="K100" s="273"/>
-      <c r="L100" s="273"/>
-      <c r="M100" s="273"/>
-      <c r="N100" s="273"/>
-      <c r="O100" s="273"/>
-      <c r="P100" s="273"/>
-      <c r="Q100" s="273"/>
-      <c r="R100" s="273"/>
-      <c r="S100" s="273"/>
-      <c r="T100" s="273"/>
-      <c r="U100" s="273"/>
+      <c r="C100" s="200" t="s">
+        <v>114</v>
+      </c>
+      <c r="D100" s="200"/>
+      <c r="E100" s="200"/>
+      <c r="F100" s="200"/>
+      <c r="G100" s="200"/>
+      <c r="H100" s="200"/>
+      <c r="I100" s="200"/>
+      <c r="J100" s="200"/>
+      <c r="K100" s="200"/>
+      <c r="L100" s="200"/>
+      <c r="M100" s="200"/>
+      <c r="N100" s="200"/>
+      <c r="O100" s="200"/>
+      <c r="P100" s="200"/>
+      <c r="Q100" s="200"/>
+      <c r="R100" s="200"/>
+      <c r="S100" s="200"/>
+      <c r="T100" s="200"/>
+      <c r="U100" s="200"/>
     </row>
     <row r="101" spans="2:21" ht="37" customHeight="1">
-      <c r="C101" s="273" t="s">
-        <v>135</v>
-      </c>
-      <c r="D101" s="273"/>
-      <c r="E101" s="273"/>
-      <c r="F101" s="273"/>
-      <c r="G101" s="273"/>
-      <c r="H101" s="273"/>
-      <c r="I101" s="273"/>
-      <c r="J101" s="273"/>
-      <c r="K101" s="273"/>
-      <c r="L101" s="273"/>
-      <c r="M101" s="273"/>
-      <c r="N101" s="273"/>
-      <c r="O101" s="273"/>
-      <c r="P101" s="273"/>
-      <c r="Q101" s="273"/>
-      <c r="R101" s="273"/>
-      <c r="S101" s="273"/>
-      <c r="T101" s="273"/>
-      <c r="U101" s="273"/>
+      <c r="C101" s="200" t="s">
+        <v>131</v>
+      </c>
+      <c r="D101" s="200"/>
+      <c r="E101" s="200"/>
+      <c r="F101" s="200"/>
+      <c r="G101" s="200"/>
+      <c r="H101" s="200"/>
+      <c r="I101" s="200"/>
+      <c r="J101" s="200"/>
+      <c r="K101" s="200"/>
+      <c r="L101" s="200"/>
+      <c r="M101" s="200"/>
+      <c r="N101" s="200"/>
+      <c r="O101" s="200"/>
+      <c r="P101" s="200"/>
+      <c r="Q101" s="200"/>
+      <c r="R101" s="200"/>
+      <c r="S101" s="200"/>
+      <c r="T101" s="200"/>
+      <c r="U101" s="200"/>
     </row>
     <row r="102" spans="2:21" ht="20" customHeight="1">
       <c r="B102" s="35"/>
@@ -22907,190 +22917,190 @@
       <c r="I102" s="16"/>
     </row>
     <row r="103" spans="2:21" ht="20" customHeight="1">
-      <c r="B103" s="311" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" s="311"/>
-      <c r="D103" s="311"/>
-      <c r="E103" s="311"/>
-      <c r="F103" s="311"/>
-      <c r="G103" s="311"/>
-      <c r="H103" s="311"/>
-      <c r="I103" s="311"/>
-      <c r="J103" s="311"/>
+      <c r="B103" s="231" t="s">
+        <v>87</v>
+      </c>
+      <c r="C103" s="231"/>
+      <c r="D103" s="231"/>
+      <c r="E103" s="231"/>
+      <c r="F103" s="231"/>
+      <c r="G103" s="231"/>
+      <c r="H103" s="231"/>
+      <c r="I103" s="231"/>
+      <c r="J103" s="231"/>
     </row>
     <row r="104" spans="2:21" ht="29.25" customHeight="1">
       <c r="B104" s="38"/>
-      <c r="C104" s="273" t="s">
-        <v>90</v>
-      </c>
-      <c r="D104" s="273"/>
-      <c r="E104" s="273"/>
-      <c r="F104" s="273"/>
-      <c r="G104" s="273"/>
-      <c r="H104" s="273"/>
-      <c r="I104" s="273"/>
-      <c r="J104" s="273"/>
-      <c r="K104" s="273"/>
-      <c r="L104" s="273"/>
-      <c r="M104" s="273"/>
-      <c r="N104" s="273"/>
-      <c r="O104" s="273"/>
-      <c r="P104" s="273"/>
-      <c r="Q104" s="273"/>
-      <c r="R104" s="273"/>
-      <c r="S104" s="273"/>
-      <c r="T104" s="273"/>
-      <c r="U104" s="273"/>
+      <c r="C104" s="200" t="s">
+        <v>88</v>
+      </c>
+      <c r="D104" s="200"/>
+      <c r="E104" s="200"/>
+      <c r="F104" s="200"/>
+      <c r="G104" s="200"/>
+      <c r="H104" s="200"/>
+      <c r="I104" s="200"/>
+      <c r="J104" s="200"/>
+      <c r="K104" s="200"/>
+      <c r="L104" s="200"/>
+      <c r="M104" s="200"/>
+      <c r="N104" s="200"/>
+      <c r="O104" s="200"/>
+      <c r="P104" s="200"/>
+      <c r="Q104" s="200"/>
+      <c r="R104" s="200"/>
+      <c r="S104" s="200"/>
+      <c r="T104" s="200"/>
+      <c r="U104" s="200"/>
     </row>
     <row r="105" spans="2:21" ht="49" customHeight="1">
       <c r="B105" s="38"/>
-      <c r="C105" s="273" t="s">
-        <v>91</v>
-      </c>
-      <c r="D105" s="273"/>
-      <c r="E105" s="273"/>
-      <c r="F105" s="273"/>
-      <c r="G105" s="273"/>
-      <c r="H105" s="273"/>
-      <c r="I105" s="273"/>
-      <c r="J105" s="273"/>
-      <c r="K105" s="273"/>
-      <c r="L105" s="273"/>
-      <c r="M105" s="273"/>
-      <c r="N105" s="273"/>
-      <c r="O105" s="273"/>
-      <c r="P105" s="273"/>
-      <c r="Q105" s="273"/>
-      <c r="R105" s="273"/>
-      <c r="S105" s="273"/>
-      <c r="T105" s="273"/>
-      <c r="U105" s="273"/>
+      <c r="C105" s="200" t="s">
+        <v>89</v>
+      </c>
+      <c r="D105" s="200"/>
+      <c r="E105" s="200"/>
+      <c r="F105" s="200"/>
+      <c r="G105" s="200"/>
+      <c r="H105" s="200"/>
+      <c r="I105" s="200"/>
+      <c r="J105" s="200"/>
+      <c r="K105" s="200"/>
+      <c r="L105" s="200"/>
+      <c r="M105" s="200"/>
+      <c r="N105" s="200"/>
+      <c r="O105" s="200"/>
+      <c r="P105" s="200"/>
+      <c r="Q105" s="200"/>
+      <c r="R105" s="200"/>
+      <c r="S105" s="200"/>
+      <c r="T105" s="200"/>
+      <c r="U105" s="200"/>
     </row>
     <row r="106" spans="2:21" ht="36.75" customHeight="1">
       <c r="B106" s="38"/>
-      <c r="C106" s="273" t="s">
-        <v>118</v>
-      </c>
-      <c r="D106" s="273"/>
-      <c r="E106" s="273"/>
-      <c r="F106" s="273"/>
-      <c r="G106" s="273"/>
-      <c r="H106" s="273"/>
-      <c r="I106" s="273"/>
-      <c r="J106" s="273"/>
-      <c r="K106" s="273"/>
-      <c r="L106" s="273"/>
-      <c r="M106" s="273"/>
-      <c r="N106" s="273"/>
-      <c r="O106" s="273"/>
-      <c r="P106" s="273"/>
-      <c r="Q106" s="273"/>
-      <c r="R106" s="273"/>
-      <c r="S106" s="273"/>
-      <c r="T106" s="273"/>
-      <c r="U106" s="273"/>
+      <c r="C106" s="200" t="s">
+        <v>115</v>
+      </c>
+      <c r="D106" s="200"/>
+      <c r="E106" s="200"/>
+      <c r="F106" s="200"/>
+      <c r="G106" s="200"/>
+      <c r="H106" s="200"/>
+      <c r="I106" s="200"/>
+      <c r="J106" s="200"/>
+      <c r="K106" s="200"/>
+      <c r="L106" s="200"/>
+      <c r="M106" s="200"/>
+      <c r="N106" s="200"/>
+      <c r="O106" s="200"/>
+      <c r="P106" s="200"/>
+      <c r="Q106" s="200"/>
+      <c r="R106" s="200"/>
+      <c r="S106" s="200"/>
+      <c r="T106" s="200"/>
+      <c r="U106" s="200"/>
     </row>
     <row r="107" spans="2:21" s="40" customFormat="1" ht="37" customHeight="1">
       <c r="B107" s="42"/>
-      <c r="C107" s="273" t="s">
-        <v>92</v>
-      </c>
-      <c r="D107" s="273"/>
-      <c r="E107" s="273"/>
-      <c r="F107" s="273"/>
-      <c r="G107" s="273"/>
-      <c r="H107" s="273"/>
-      <c r="I107" s="273"/>
-      <c r="J107" s="273"/>
-      <c r="K107" s="273"/>
-      <c r="L107" s="273"/>
-      <c r="M107" s="273"/>
-      <c r="N107" s="273"/>
-      <c r="O107" s="273"/>
-      <c r="P107" s="273"/>
-      <c r="Q107" s="273"/>
-      <c r="R107" s="273"/>
-      <c r="S107" s="273"/>
-      <c r="T107" s="273"/>
-      <c r="U107" s="273"/>
+      <c r="C107" s="200" t="s">
+        <v>90</v>
+      </c>
+      <c r="D107" s="200"/>
+      <c r="E107" s="200"/>
+      <c r="F107" s="200"/>
+      <c r="G107" s="200"/>
+      <c r="H107" s="200"/>
+      <c r="I107" s="200"/>
+      <c r="J107" s="200"/>
+      <c r="K107" s="200"/>
+      <c r="L107" s="200"/>
+      <c r="M107" s="200"/>
+      <c r="N107" s="200"/>
+      <c r="O107" s="200"/>
+      <c r="P107" s="200"/>
+      <c r="Q107" s="200"/>
+      <c r="R107" s="200"/>
+      <c r="S107" s="200"/>
+      <c r="T107" s="200"/>
+      <c r="U107" s="200"/>
     </row>
     <row r="108" spans="2:21" ht="52.75" customHeight="1">
-      <c r="C108" s="273" t="s">
-        <v>136</v>
-      </c>
-      <c r="D108" s="273"/>
-      <c r="E108" s="273"/>
-      <c r="F108" s="273"/>
-      <c r="G108" s="273"/>
-      <c r="H108" s="273"/>
-      <c r="I108" s="273"/>
-      <c r="J108" s="273"/>
-      <c r="K108" s="273"/>
-      <c r="L108" s="273"/>
-      <c r="M108" s="273"/>
-      <c r="N108" s="273"/>
-      <c r="O108" s="273"/>
-      <c r="P108" s="273"/>
-      <c r="Q108" s="273"/>
-      <c r="R108" s="273"/>
-      <c r="S108" s="273"/>
-      <c r="T108" s="273"/>
-      <c r="U108" s="273"/>
+      <c r="C108" s="200" t="s">
+        <v>132</v>
+      </c>
+      <c r="D108" s="200"/>
+      <c r="E108" s="200"/>
+      <c r="F108" s="200"/>
+      <c r="G108" s="200"/>
+      <c r="H108" s="200"/>
+      <c r="I108" s="200"/>
+      <c r="J108" s="200"/>
+      <c r="K108" s="200"/>
+      <c r="L108" s="200"/>
+      <c r="M108" s="200"/>
+      <c r="N108" s="200"/>
+      <c r="O108" s="200"/>
+      <c r="P108" s="200"/>
+      <c r="Q108" s="200"/>
+      <c r="R108" s="200"/>
+      <c r="S108" s="200"/>
+      <c r="T108" s="200"/>
+      <c r="U108" s="200"/>
     </row>
     <row r="109" spans="2:21" ht="37" customHeight="1">
-      <c r="C109" s="273" t="s">
-        <v>93</v>
-      </c>
-      <c r="D109" s="273"/>
-      <c r="E109" s="273"/>
-      <c r="F109" s="273"/>
-      <c r="G109" s="273"/>
-      <c r="H109" s="273"/>
-      <c r="I109" s="273"/>
-      <c r="J109" s="273"/>
-      <c r="K109" s="273"/>
-      <c r="L109" s="273"/>
-      <c r="M109" s="273"/>
-      <c r="N109" s="273"/>
-      <c r="O109" s="273"/>
-      <c r="P109" s="273"/>
-      <c r="Q109" s="273"/>
-      <c r="R109" s="273"/>
-      <c r="S109" s="273"/>
-      <c r="T109" s="273"/>
-      <c r="U109" s="273"/>
+      <c r="C109" s="200" t="s">
+        <v>91</v>
+      </c>
+      <c r="D109" s="200"/>
+      <c r="E109" s="200"/>
+      <c r="F109" s="200"/>
+      <c r="G109" s="200"/>
+      <c r="H109" s="200"/>
+      <c r="I109" s="200"/>
+      <c r="J109" s="200"/>
+      <c r="K109" s="200"/>
+      <c r="L109" s="200"/>
+      <c r="M109" s="200"/>
+      <c r="N109" s="200"/>
+      <c r="O109" s="200"/>
+      <c r="P109" s="200"/>
+      <c r="Q109" s="200"/>
+      <c r="R109" s="200"/>
+      <c r="S109" s="200"/>
+      <c r="T109" s="200"/>
+      <c r="U109" s="200"/>
     </row>
     <row r="110" spans="2:21" ht="48.75" customHeight="1">
-      <c r="C110" s="273" t="s">
-        <v>128</v>
-      </c>
-      <c r="D110" s="273"/>
-      <c r="E110" s="273"/>
-      <c r="F110" s="273"/>
-      <c r="G110" s="273"/>
-      <c r="H110" s="273"/>
-      <c r="I110" s="273"/>
-      <c r="J110" s="273"/>
-      <c r="K110" s="273"/>
-      <c r="L110" s="273"/>
-      <c r="M110" s="273"/>
-      <c r="N110" s="273"/>
-      <c r="O110" s="273"/>
-      <c r="P110" s="273"/>
-      <c r="Q110" s="273"/>
-      <c r="R110" s="273"/>
-      <c r="S110" s="273"/>
-      <c r="T110" s="273"/>
-      <c r="U110" s="273"/>
-    </row>
-    <row r="111" spans="2:21" ht="300" customHeight="1"/>
+      <c r="C110" s="200" t="s">
+        <v>124</v>
+      </c>
+      <c r="D110" s="200"/>
+      <c r="E110" s="200"/>
+      <c r="F110" s="200"/>
+      <c r="G110" s="200"/>
+      <c r="H110" s="200"/>
+      <c r="I110" s="200"/>
+      <c r="J110" s="200"/>
+      <c r="K110" s="200"/>
+      <c r="L110" s="200"/>
+      <c r="M110" s="200"/>
+      <c r="N110" s="200"/>
+      <c r="O110" s="200"/>
+      <c r="P110" s="200"/>
+      <c r="Q110" s="200"/>
+      <c r="R110" s="200"/>
+      <c r="S110" s="200"/>
+      <c r="T110" s="200"/>
+      <c r="U110" s="200"/>
+    </row>
+    <row r="111" spans="2:21" ht="127" customHeight="1"/>
     <row r="112" spans="2:21" ht="50" customHeight="1"/>
     <row r="113" ht="25" customHeight="1"/>
     <row r="114" ht="25" customHeight="1"/>
     <row r="115" ht="25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="110">
+  <mergeCells count="108">
     <mergeCell ref="C107:U107"/>
     <mergeCell ref="C108:U108"/>
     <mergeCell ref="C109:U109"/>
@@ -23122,7 +23132,6 @@
     <mergeCell ref="B82:J82"/>
     <mergeCell ref="C83:U83"/>
     <mergeCell ref="B85:U85"/>
-    <mergeCell ref="B62:U62"/>
     <mergeCell ref="B64:J64"/>
     <mergeCell ref="C65:U65"/>
     <mergeCell ref="B67:U67"/>
@@ -23131,16 +23140,16 @@
     <mergeCell ref="D70:U70"/>
     <mergeCell ref="D71:U71"/>
     <mergeCell ref="B73:U73"/>
+    <mergeCell ref="C62:U62"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="F55:J55"/>
     <mergeCell ref="L55:O55"/>
     <mergeCell ref="P55:T55"/>
     <mergeCell ref="B56:U56"/>
     <mergeCell ref="B57:U57"/>
-    <mergeCell ref="B59:U59"/>
-    <mergeCell ref="B60:U60"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="I61:U61"/>
+    <mergeCell ref="C59:U59"/>
+    <mergeCell ref="C60:U60"/>
+    <mergeCell ref="C61:U61"/>
     <mergeCell ref="B52:K52"/>
     <mergeCell ref="L52:U52"/>
     <mergeCell ref="B53:E53"/>
@@ -23162,8 +23171,6 @@
     <mergeCell ref="G51:U51"/>
     <mergeCell ref="B35:C43"/>
     <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="M35:U35"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="G36:U36"/>
     <mergeCell ref="D37:F37"/>
@@ -23182,6 +23189,7 @@
     <mergeCell ref="G42:U42"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="G43:U43"/>
+    <mergeCell ref="G35:U35"/>
     <mergeCell ref="B28:U28"/>
     <mergeCell ref="B29:C34"/>
     <mergeCell ref="D29:F29"/>

--- a/repair/back/doc/estimate/repair1.xlsx
+++ b/repair/back/doc/estimate/repair1.xlsx
@@ -357,7 +357,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t xml:space="preserve">㈜ 에 이 앤 비 </t>
   </si>
@@ -1165,6 +1165,9 @@
       </rPr>
       <t>7. 참 고 사 항</t>
     </r>
+  </si>
+  <si>
+    <t>② 지급시기는 계약일로 부터 60일 이내에 지급하여야 한다.</t>
   </si>
 </sst>
 </file>
@@ -1994,21 +1997,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="16.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="36.0"/>
       <name val="맑은 고딕"/>
@@ -2091,6 +2079,21 @@
       <b/>
       <sz val="17.0"/>
       <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -22202,7 +22205,7 @@
       <c r="T48" s="34"/>
       <c r="U48" s="276"/>
     </row>
-    <row r="49" spans="1:21" ht="24.950000" customHeight="1">
+    <row r="49" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B49" s="32"/>
       <c r="C49" s="27"/>
       <c r="D49" s="27"/>
@@ -22224,14 +22227,14 @@
       <c r="T49" s="34"/>
       <c r="U49" s="276"/>
     </row>
-    <row r="50" spans="1:21" ht="13.500000">
+    <row r="50" spans="2:21" ht="13.500000">
       <c r="B50" s="273"/>
       <c r="C50" s="274"/>
       <c r="D50" s="274"/>
       <c r="E50" s="274"/>
       <c r="U50" s="29"/>
     </row>
-    <row r="51" spans="1:21" ht="24.950000" customHeight="1">
+    <row r="51" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B51" s="279" t="s">
         <v>65</v>
       </c>
@@ -22257,8 +22260,7 @@
       <c r="T51" s="281"/>
       <c r="U51" s="282"/>
     </row>
-    <row r="52" spans="1:21" ht="40.500000" customHeight="1">
-      <c r="A52" s="15"/>
+    <row r="52" spans="2:21" ht="40.500000" customHeight="1">
       <c r="B52" s="283" t="s">
         <v>104</v>
       </c>
@@ -22284,8 +22286,7 @@
       <c r="T52" s="284"/>
       <c r="U52" s="285"/>
     </row>
-    <row r="53" spans="1:21" ht="40.500000" customHeight="1">
-      <c r="A53" s="15"/>
+    <row r="53" spans="2:21" ht="40.500000" customHeight="1">
       <c r="B53" s="292" t="s">
         <v>106</v>
       </c>
@@ -22316,8 +22317,7 @@
       <c r="T53" s="34"/>
       <c r="U53" s="276"/>
     </row>
-    <row r="54" spans="1:21" ht="40.500000" customHeight="1">
-      <c r="A54" s="15"/>
+    <row r="54" spans="2:21" ht="40.500000" customHeight="1">
       <c r="B54" s="292" t="s">
         <v>109</v>
       </c>
@@ -22348,8 +22348,7 @@
       <c r="T54" s="295"/>
       <c r="U54" s="296"/>
     </row>
-    <row r="55" spans="1:21" ht="40.500000" customHeight="1">
-      <c r="A55" s="15"/>
+    <row r="55" spans="2:21" ht="40.500000" customHeight="1">
       <c r="B55" s="293" t="s">
         <v>170</v>
       </c>
@@ -22381,7 +22380,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="16.500000">
+    <row r="56" spans="2:21" ht="16.500000">
       <c r="B56" s="286" t="s">
         <v>66</v>
       </c>
@@ -22405,7 +22404,7 @@
       <c r="T56" s="286"/>
       <c r="U56" s="286"/>
     </row>
-    <row r="57" spans="1:21" ht="25.500000">
+    <row r="57" spans="2:21" ht="25.500000">
       <c r="B57" s="287" t="s">
         <v>94</v>
       </c>
@@ -22429,13 +22428,13 @@
       <c r="T57" s="287"/>
       <c r="U57" s="287"/>
     </row>
-    <row r="58" spans="1:21" ht="14.250000">
+    <row r="58" spans="2:21" ht="14.250000">
       <c r="B58" s="33"/>
       <c r="F58" s="17"/>
       <c r="G58" s="23"/>
       <c r="I58" s="16"/>
     </row>
-    <row r="59" spans="1:21" ht="20.000000" customHeight="1">
+    <row r="59" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B59" s="288" t="s">
         <v>165</v>
       </c>
@@ -22459,7 +22458,7 @@
       <c r="T59" s="288"/>
       <c r="U59" s="288"/>
     </row>
-    <row r="60" spans="1:21" ht="20.000000" customHeight="1">
+    <row r="60" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B60" s="34" t="s">
         <v>166</v>
       </c>
@@ -22483,7 +22482,7 @@
       <c r="T60" s="34"/>
       <c r="U60" s="34"/>
     </row>
-    <row r="61" spans="1:21" ht="20.000000" customHeight="1">
+    <row r="61" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B61" s="291" t="str">
         <f>E53</f>
         <v>마곡엠밸리4단지아파트</v>
@@ -22510,7 +22509,7 @@
       <c r="T61" s="34"/>
       <c r="U61" s="34"/>
     </row>
-    <row r="62" spans="1:21" ht="20.000000" customHeight="1">
+    <row r="62" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B62" s="290" t="s">
         <v>168</v>
       </c>
@@ -22534,7 +22533,7 @@
       <c r="T62" s="290"/>
       <c r="U62" s="290"/>
     </row>
-    <row r="63" spans="1:21" ht="20.000000" customHeight="1">
+    <row r="63" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B63" s="34"/>
       <c r="C63" s="34"/>
       <c r="D63" s="34"/>
@@ -22545,7 +22544,7 @@
       <c r="I63" s="34"/>
       <c r="J63" s="34"/>
     </row>
-    <row r="64" spans="1:21" ht="20.000000" customHeight="1">
+    <row r="64" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B64" s="289" t="s">
         <v>146</v>
       </c>
@@ -22801,7 +22800,7 @@
     <row r="78" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B78" s="37"/>
       <c r="C78" s="34" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="34"/>

--- a/repair/back/doc/estimate/repair1.xlsx
+++ b/repair/back/doc/estimate/repair1.xlsx
@@ -357,7 +357,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t xml:space="preserve">㈜ 에 이 앤 비 </t>
   </si>
@@ -1168,6 +1168,9 @@
   </si>
   <si>
     <t>② 지급시기는 계약일로 부터 60일 이내에 지급하여야 한다.</t>
+  </si>
+  <si>
+    <t>㈜ 에이앤비 (이하 "수주자"라 한다)는 다음과같이 계약을 체결한다.</t>
   </si>
 </sst>
 </file>
@@ -12925,7 +12928,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -13836,6 +13839,60 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="91" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="59" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3167">
@@ -17308,15 +17365,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>387350</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>182245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>438785</xdr:colOff>
+      <xdr:colOff>440055</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:rowOff>41275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -17346,8 +17403,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7586980" y="7896860"/>
-          <a:ext cx="794385" cy="578485"/>
+          <a:off x="7588250" y="7739380"/>
+          <a:ext cx="794385" cy="735330"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -20882,7 +20939,7 @@
   <sheetPr>
     <tabColor rgb="92d050"/>
   </sheetPr>
-  <dimension ref="B1:U112"/>
+  <dimension ref="B1:U110"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="12.000000"/>
   <cols>
     <col min="1" max="1" style="15" width="11.29071413" customWidth="1" outlineLevel="0"/>
@@ -22047,13 +22104,13 @@
         <v>138</v>
       </c>
       <c r="H41" s="150"/>
-      <c r="I41" s="150" t="s">
+      <c r="I41" s="265" t="s">
         <v>135</v>
       </c>
-      <c r="J41" s="150"/>
-      <c r="K41" s="150"/>
-      <c r="L41" s="150"/>
-      <c r="M41" s="150"/>
+      <c r="J41" s="265"/>
+      <c r="K41" s="265"/>
+      <c r="L41" s="265"/>
+      <c r="M41" s="265"/>
       <c r="N41" s="150" t="s">
         <v>13</v>
       </c>
@@ -22061,13 +22118,13 @@
         <v>136</v>
       </c>
       <c r="P41" s="150"/>
-      <c r="Q41" s="150" t="s">
+      <c r="Q41" s="305" t="s">
         <v>137</v>
       </c>
-      <c r="R41" s="150"/>
-      <c r="S41" s="150"/>
-      <c r="T41" s="150"/>
-      <c r="U41" s="260"/>
+      <c r="R41" s="305"/>
+      <c r="S41" s="305"/>
+      <c r="T41" s="305"/>
+      <c r="U41" s="306"/>
     </row>
     <row r="42" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B42" s="249"/>
@@ -22368,14 +22425,14 @@
       </c>
       <c r="M55" s="294"/>
       <c r="N55" s="294"/>
-      <c r="O55" s="294" t="s">
+      <c r="O55" s="307" t="s">
         <v>70</v>
       </c>
-      <c r="P55" s="294"/>
-      <c r="Q55" s="294"/>
-      <c r="R55" s="294"/>
-      <c r="S55" s="294"/>
-      <c r="T55" s="294"/>
+      <c r="P55" s="307"/>
+      <c r="Q55" s="307"/>
+      <c r="R55" s="307"/>
+      <c r="S55" s="307"/>
+      <c r="T55" s="307"/>
       <c r="U55" s="153" t="s">
         <v>69</v>
       </c>
@@ -22435,64 +22492,64 @@
       <c r="I58" s="16"/>
     </row>
     <row r="59" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B59" s="288" t="s">
+      <c r="B59" s="309"/>
+      <c r="C59" s="311" t="s">
         <v>165</v>
       </c>
-      <c r="C59" s="288"/>
-      <c r="D59" s="288"/>
-      <c r="E59" s="288"/>
-      <c r="F59" s="288"/>
-      <c r="G59" s="288"/>
-      <c r="H59" s="288"/>
-      <c r="I59" s="288"/>
-      <c r="J59" s="288"/>
-      <c r="K59" s="288"/>
-      <c r="L59" s="288"/>
-      <c r="M59" s="288"/>
-      <c r="N59" s="288"/>
-      <c r="O59" s="288"/>
-      <c r="P59" s="288"/>
-      <c r="Q59" s="288"/>
-      <c r="R59" s="288"/>
-      <c r="S59" s="288"/>
-      <c r="T59" s="288"/>
-      <c r="U59" s="288"/>
+      <c r="D59" s="311"/>
+      <c r="E59" s="311"/>
+      <c r="F59" s="311"/>
+      <c r="G59" s="311"/>
+      <c r="H59" s="311"/>
+      <c r="I59" s="311"/>
+      <c r="J59" s="311"/>
+      <c r="K59" s="311"/>
+      <c r="L59" s="311"/>
+      <c r="M59" s="311"/>
+      <c r="N59" s="311"/>
+      <c r="O59" s="311"/>
+      <c r="P59" s="311"/>
+      <c r="Q59" s="311"/>
+      <c r="R59" s="311"/>
+      <c r="S59" s="311"/>
+      <c r="T59" s="311"/>
+      <c r="U59" s="311"/>
     </row>
     <row r="60" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B60" s="34" t="s">
+      <c r="B60" s="312"/>
+      <c r="C60" s="314" t="s">
         <v>166</v>
       </c>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="34"/>
-      <c r="N60" s="34"/>
-      <c r="O60" s="34"/>
-      <c r="P60" s="34"/>
-      <c r="Q60" s="34"/>
-      <c r="R60" s="34"/>
-      <c r="S60" s="34"/>
-      <c r="T60" s="34"/>
-      <c r="U60" s="34"/>
+      <c r="D60" s="314"/>
+      <c r="E60" s="314"/>
+      <c r="F60" s="314"/>
+      <c r="G60" s="314"/>
+      <c r="H60" s="314"/>
+      <c r="I60" s="314"/>
+      <c r="J60" s="314"/>
+      <c r="K60" s="314"/>
+      <c r="L60" s="314"/>
+      <c r="M60" s="314"/>
+      <c r="N60" s="314"/>
+      <c r="O60" s="314"/>
+      <c r="P60" s="314"/>
+      <c r="Q60" s="314"/>
+      <c r="R60" s="314"/>
+      <c r="S60" s="314"/>
+      <c r="T60" s="314"/>
+      <c r="U60" s="314"/>
     </row>
     <row r="61" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B61" s="291" t="str">
+      <c r="B61" s="316"/>
+      <c r="C61" s="319" t="str">
         <f>E53</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="C61" s="291"/>
-      <c r="D61" s="291"/>
-      <c r="E61" s="291"/>
-      <c r="F61" s="291"/>
-      <c r="G61" s="291"/>
-      <c r="H61" s="291"/>
+      <c r="D61" s="319"/>
+      <c r="E61" s="319"/>
+      <c r="F61" s="319"/>
+      <c r="G61" s="319"/>
+      <c r="H61" s="319"/>
       <c r="I61" s="34" t="s">
         <v>167</v>
       </c>
@@ -22510,28 +22567,28 @@
       <c r="U61" s="34"/>
     </row>
     <row r="62" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B62" s="290" t="s">
-        <v>168</v>
-      </c>
-      <c r="C62" s="290"/>
-      <c r="D62" s="290"/>
-      <c r="E62" s="290"/>
-      <c r="F62" s="290"/>
-      <c r="G62" s="290"/>
-      <c r="H62" s="290"/>
-      <c r="I62" s="290"/>
-      <c r="J62" s="290"/>
-      <c r="K62" s="290"/>
-      <c r="L62" s="290"/>
-      <c r="M62" s="290"/>
-      <c r="N62" s="290"/>
-      <c r="O62" s="290"/>
-      <c r="P62" s="290"/>
-      <c r="Q62" s="290"/>
-      <c r="R62" s="290"/>
-      <c r="S62" s="290"/>
-      <c r="T62" s="290"/>
-      <c r="U62" s="290"/>
+      <c r="B62" s="320"/>
+      <c r="C62" s="322" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" s="322"/>
+      <c r="E62" s="322"/>
+      <c r="F62" s="322"/>
+      <c r="G62" s="322"/>
+      <c r="H62" s="322"/>
+      <c r="I62" s="322"/>
+      <c r="J62" s="322"/>
+      <c r="K62" s="322"/>
+      <c r="L62" s="322"/>
+      <c r="M62" s="322"/>
+      <c r="N62" s="322"/>
+      <c r="O62" s="322"/>
+      <c r="P62" s="322"/>
+      <c r="Q62" s="322"/>
+      <c r="R62" s="322"/>
+      <c r="S62" s="322"/>
+      <c r="T62" s="322"/>
+      <c r="U62" s="322"/>
     </row>
     <row r="63" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B63" s="34"/>
@@ -23531,11 +23588,11 @@
     <mergeCell ref="O55:T55"/>
     <mergeCell ref="B56:U56"/>
     <mergeCell ref="B57:U57"/>
-    <mergeCell ref="B59:U59"/>
-    <mergeCell ref="B60:U60"/>
-    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="C59:U59"/>
+    <mergeCell ref="C60:U60"/>
+    <mergeCell ref="C61:H61"/>
     <mergeCell ref="I61:U61"/>
-    <mergeCell ref="B62:U62"/>
+    <mergeCell ref="C62:U62"/>
     <mergeCell ref="B64:J64"/>
     <mergeCell ref="C65:U65"/>
     <mergeCell ref="B67:U67"/>
